--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M327220\Documents\GitHub\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B4006C8-C593-494E-BEF5-5E3EA7053EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2344E3D-DB40-4610-9451-59EEC77436C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4755" yWindow="3210" windowWidth="20910" windowHeight="11835" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28110" windowHeight="16440" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
   <si>
     <t>Child</t>
   </si>
@@ -117,46 +117,28 @@
     <t>sd</t>
   </si>
   <si>
-    <t>DE10622600</t>
-  </si>
-  <si>
-    <t>DE10513301</t>
-  </si>
-  <si>
-    <t>DE10533004</t>
-  </si>
-  <si>
-    <t>DE65GIT032</t>
-  </si>
-  <si>
-    <t>VN50GIT050</t>
-  </si>
-  <si>
-    <t>ZA50GIT11B</t>
-  </si>
-  <si>
-    <t>US10GIT044</t>
-  </si>
-  <si>
-    <t>DE10600870</t>
-  </si>
-  <si>
-    <t>G000000392</t>
-  </si>
-  <si>
-    <t>G000001356</t>
-  </si>
-  <si>
-    <t>G000001123</t>
-  </si>
-  <si>
-    <t>G000000256</t>
-  </si>
-  <si>
-    <t>H000004183</t>
-  </si>
-  <si>
-    <t>G000000279</t>
+    <t>DE10300049</t>
+  </si>
+  <si>
+    <t>2013OFIBM1</t>
+  </si>
+  <si>
+    <t>2123C00001</t>
+  </si>
+  <si>
+    <t>2128TMCZ95</t>
+  </si>
+  <si>
+    <t>L000013118</t>
+  </si>
+  <si>
+    <t>L000011139</t>
+  </si>
+  <si>
+    <t>L000013457</t>
+  </si>
+  <si>
+    <t>G000000229</t>
   </si>
 </sst>
 </file>
@@ -514,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -535,7 +517,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -543,7 +525,7 @@
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -551,7 +533,7 @@
         <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -559,39 +541,7 @@
         <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
         <v>30</v>
-      </c>
-      <c r="B8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" t="s">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -735,26 +685,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -931,26 +861,27 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
-    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -967,4 +898,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
+    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M327220\Documents\GitHub\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2344E3D-DB40-4610-9451-59EEC77436C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935C7EDA-9BDF-4CC4-9557-4203D4FE0769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="28110" windowHeight="16440" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="43">
   <si>
     <t>Child</t>
   </si>
@@ -117,28 +117,61 @@
     <t>sd</t>
   </si>
   <si>
-    <t>DE10300049</t>
-  </si>
-  <si>
-    <t>2013OFIBM1</t>
-  </si>
-  <si>
-    <t>2123C00001</t>
-  </si>
-  <si>
-    <t>2128TMCZ95</t>
-  </si>
-  <si>
-    <t>L000013118</t>
-  </si>
-  <si>
-    <t>L000011139</t>
-  </si>
-  <si>
-    <t>L000013457</t>
-  </si>
-  <si>
-    <t>G000000229</t>
+    <t>ZA50GM1000</t>
+  </si>
+  <si>
+    <t>ZA50GIT10D</t>
+  </si>
+  <si>
+    <t>ZA50GHR014</t>
+  </si>
+  <si>
+    <t>KE50GM2100</t>
+  </si>
+  <si>
+    <t>CZ50GM2100</t>
+  </si>
+  <si>
+    <t>CZ50GM2101</t>
+  </si>
+  <si>
+    <t>DE20569502</t>
+  </si>
+  <si>
+    <t>DZ50GM1100</t>
+  </si>
+  <si>
+    <t>2053OF0000</t>
+  </si>
+  <si>
+    <t>IT50C02000</t>
+  </si>
+  <si>
+    <t>IT50C02004</t>
+  </si>
+  <si>
+    <t>IT50C03005</t>
+  </si>
+  <si>
+    <t>IT50C03004</t>
+  </si>
+  <si>
+    <t>IT50C02009</t>
+  </si>
+  <si>
+    <t>IT50C02010</t>
+  </si>
+  <si>
+    <t>IT50C03007</t>
+  </si>
+  <si>
+    <t>IT50C02011</t>
+  </si>
+  <si>
+    <t>G000000686</t>
+  </si>
+  <si>
+    <t>H000000000</t>
   </si>
 </sst>
 </file>
@@ -496,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -517,7 +550,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -525,7 +558,7 @@
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -533,7 +566,7 @@
         <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -541,7 +574,111 @@
         <v>27</v>
       </c>
       <c r="B5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>30</v>
+      </c>
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -685,6 +822,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -861,27 +1018,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
+    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -898,23 +1054,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
-    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M327220\Documents\GitHub\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935C7EDA-9BDF-4CC4-9557-4203D4FE0769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65DB7BB2-2FD1-4424-95F6-646BB4EF8E30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28110" windowHeight="16440" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="2505" yWindow="1935" windowWidth="20910" windowHeight="11835" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
   <si>
     <t>Child</t>
   </si>
@@ -117,61 +117,25 @@
     <t>sd</t>
   </si>
   <si>
-    <t>ZA50GM1000</t>
-  </si>
-  <si>
-    <t>ZA50GIT10D</t>
-  </si>
-  <si>
-    <t>ZA50GHR014</t>
-  </si>
-  <si>
-    <t>KE50GM2100</t>
-  </si>
-  <si>
-    <t>CZ50GM2100</t>
-  </si>
-  <si>
-    <t>CZ50GM2101</t>
-  </si>
-  <si>
-    <t>DE20569502</t>
-  </si>
-  <si>
-    <t>DZ50GM1100</t>
-  </si>
-  <si>
-    <t>2053OF0000</t>
-  </si>
-  <si>
-    <t>IT50C02000</t>
-  </si>
-  <si>
-    <t>IT50C02004</t>
-  </si>
-  <si>
-    <t>IT50C03005</t>
-  </si>
-  <si>
-    <t>IT50C03004</t>
-  </si>
-  <si>
-    <t>IT50C02009</t>
-  </si>
-  <si>
-    <t>IT50C02010</t>
-  </si>
-  <si>
-    <t>IT50C03007</t>
-  </si>
-  <si>
-    <t>IT50C02011</t>
-  </si>
-  <si>
-    <t>G000000686</t>
-  </si>
-  <si>
-    <t>H000000000</t>
+    <t>ES50GPO794</t>
+  </si>
+  <si>
+    <t>CH75GM8300</t>
+  </si>
+  <si>
+    <t>CH50GM4010</t>
+  </si>
+  <si>
+    <t>CN95GM4000</t>
+  </si>
+  <si>
+    <t>CN96GM4002</t>
+  </si>
+  <si>
+    <t>H000004174</t>
+  </si>
+  <si>
+    <t>G000000636</t>
   </si>
 </sst>
 </file>
@@ -529,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -550,7 +514,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -558,7 +522,7 @@
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -566,7 +530,7 @@
         <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -574,7 +538,7 @@
         <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -582,103 +546,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
         <v>30</v>
-      </c>
-      <c r="B8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" t="s">
-        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -822,26 +690,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -1018,26 +866,27 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
-    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1054,4 +903,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
+    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M327220\Documents\GitHub\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65DB7BB2-2FD1-4424-95F6-646BB4EF8E30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E039BF9-9FFC-46DC-B7CA-9C629E0B9700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2505" yWindow="1935" windowWidth="20910" windowHeight="11835" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="3720" yWindow="3705" windowWidth="20910" windowHeight="11835" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="37">
   <si>
     <t>Child</t>
   </si>
@@ -117,25 +117,43 @@
     <t>sd</t>
   </si>
   <si>
-    <t>ES50GPO794</t>
-  </si>
-  <si>
-    <t>CH75GM8300</t>
-  </si>
-  <si>
-    <t>CH50GM4010</t>
-  </si>
-  <si>
-    <t>CN95GM4000</t>
-  </si>
-  <si>
-    <t>CN96GM4002</t>
-  </si>
-  <si>
-    <t>H000004174</t>
-  </si>
-  <si>
-    <t>G000000636</t>
+    <t>CH50GIT032</t>
+  </si>
+  <si>
+    <t>IT50C02000</t>
+  </si>
+  <si>
+    <t>IT50C02004</t>
+  </si>
+  <si>
+    <t>IT50C03005</t>
+  </si>
+  <si>
+    <t>IT50C03004</t>
+  </si>
+  <si>
+    <t>IT50C02009</t>
+  </si>
+  <si>
+    <t>IT50C02010</t>
+  </si>
+  <si>
+    <t>IT50C03007</t>
+  </si>
+  <si>
+    <t>IT50C02011</t>
+  </si>
+  <si>
+    <t>US10GM4058</t>
+  </si>
+  <si>
+    <t>G000001121</t>
+  </si>
+  <si>
+    <t>H000000181</t>
+  </si>
+  <si>
+    <t>G000000633</t>
   </si>
 </sst>
 </file>
@@ -493,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -514,7 +532,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -522,7 +540,7 @@
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -530,7 +548,7 @@
         <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -538,7 +556,7 @@
         <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -546,7 +564,47 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>30</v>
+      </c>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -867,15 +925,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
@@ -884,6 +933,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -906,14 +964,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -922,4 +972,12 @@
     <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M327220\Documents\GitHub\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E039BF9-9FFC-46DC-B7CA-9C629E0B9700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA41DA3-CD81-4DF5-8AD1-D1074AA34F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="3705" windowWidth="20910" windowHeight="11835" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28110" windowHeight="16440" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <definedName name="ID" localSheetId="0" hidden="1">"a5f5822f-2145-4cc3-aa32-d164ed237772"</definedName>
     <definedName name="ID" localSheetId="1" hidden="1">"fff7d4e2-cafa-4da0-a3ee-fa93757f1b68"</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="42">
   <si>
     <t>Child</t>
   </si>
@@ -117,43 +117,58 @@
     <t>sd</t>
   </si>
   <si>
-    <t>CH50GIT032</t>
-  </si>
-  <si>
-    <t>IT50C02000</t>
-  </si>
-  <si>
-    <t>IT50C02004</t>
-  </si>
-  <si>
-    <t>IT50C03005</t>
-  </si>
-  <si>
-    <t>IT50C03004</t>
-  </si>
-  <si>
-    <t>IT50C02009</t>
-  </si>
-  <si>
-    <t>IT50C02010</t>
-  </si>
-  <si>
-    <t>IT50C03007</t>
-  </si>
-  <si>
-    <t>IT50C02011</t>
-  </si>
-  <si>
-    <t>US10GM4058</t>
-  </si>
-  <si>
-    <t>G000001121</t>
-  </si>
-  <si>
-    <t>H000000181</t>
-  </si>
-  <si>
-    <t>G000000633</t>
+    <t>DE10N12380</t>
+  </si>
+  <si>
+    <t>DE10N12340</t>
+  </si>
+  <si>
+    <t>DE10N11170</t>
+  </si>
+  <si>
+    <t>DE10N11115</t>
+  </si>
+  <si>
+    <t>DE10N11181</t>
+  </si>
+  <si>
+    <t>DE10N11160</t>
+  </si>
+  <si>
+    <t>DE10N11180</t>
+  </si>
+  <si>
+    <t>DE10N11131</t>
+  </si>
+  <si>
+    <t>DE10N11116</t>
+  </si>
+  <si>
+    <t>DE10N12312</t>
+  </si>
+  <si>
+    <t>DE10N12313</t>
+  </si>
+  <si>
+    <t>DE10N12321</t>
+  </si>
+  <si>
+    <t>DE10N12323</t>
+  </si>
+  <si>
+    <t>DE10N12395</t>
+  </si>
+  <si>
+    <t>DE10N11195</t>
+  </si>
+  <si>
+    <t>P000000196</t>
+  </si>
+  <si>
+    <t>P000000198</t>
+  </si>
+  <si>
+    <t>P000000197</t>
   </si>
 </sst>
 </file>
@@ -511,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -532,7 +547,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -540,7 +555,7 @@
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -548,7 +563,7 @@
         <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -556,7 +571,7 @@
         <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -564,7 +579,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -572,7 +587,7 @@
         <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -580,7 +595,7 @@
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -588,7 +603,7 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -596,7 +611,7 @@
         <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -604,7 +619,47 @@
         <v>33</v>
       </c>
       <c r="B11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>36</v>
+      </c>
+      <c r="B14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -748,6 +803,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -924,17 +990,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -945,6 +1000,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
+    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -963,17 +1029,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
-    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
   <ds:schemaRefs>

--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M327220\Documents\GitHub\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA41DA3-CD81-4DF5-8AD1-D1074AA34F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0FE6966-B3DC-41D3-8B5F-2206F9957FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="28110" windowHeight="16440" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
   <si>
     <t>Child</t>
   </si>
@@ -117,58 +117,37 @@
     <t>sd</t>
   </si>
   <si>
-    <t>DE10N12380</t>
-  </si>
-  <si>
-    <t>DE10N12340</t>
-  </si>
-  <si>
-    <t>DE10N11170</t>
-  </si>
-  <si>
-    <t>DE10N11115</t>
-  </si>
-  <si>
-    <t>DE10N11181</t>
-  </si>
-  <si>
-    <t>DE10N11160</t>
-  </si>
-  <si>
-    <t>DE10N11180</t>
-  </si>
-  <si>
-    <t>DE10N11131</t>
-  </si>
-  <si>
-    <t>DE10N11116</t>
-  </si>
-  <si>
-    <t>DE10N12312</t>
-  </si>
-  <si>
-    <t>DE10N12313</t>
-  </si>
-  <si>
-    <t>DE10N12321</t>
-  </si>
-  <si>
-    <t>DE10N12323</t>
-  </si>
-  <si>
-    <t>DE10N12395</t>
-  </si>
-  <si>
-    <t>DE10N11195</t>
-  </si>
-  <si>
-    <t>P000000196</t>
-  </si>
-  <si>
-    <t>P000000198</t>
-  </si>
-  <si>
-    <t>P000000197</t>
+    <t>KE50C0FF11</t>
+  </si>
+  <si>
+    <t>KE50C0IM11</t>
+  </si>
+  <si>
+    <t>2029C00004</t>
+  </si>
+  <si>
+    <t>2031C00005</t>
+  </si>
+  <si>
+    <t>2034C00012</t>
+  </si>
+  <si>
+    <t>2123OF0027</t>
+  </si>
+  <si>
+    <t>2102TPSZ93</t>
+  </si>
+  <si>
+    <t>L000005617</t>
+  </si>
+  <si>
+    <t>L000013183</t>
+  </si>
+  <si>
+    <t>G000001338</t>
+  </si>
+  <si>
+    <t>L000013788</t>
   </si>
 </sst>
 </file>
@@ -526,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -547,7 +526,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -555,7 +534,7 @@
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -563,7 +542,7 @@
         <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -571,7 +550,7 @@
         <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -579,7 +558,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -587,7 +566,7 @@
         <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -595,71 +574,7 @@
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
         <v>34</v>
-      </c>
-      <c r="B12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -803,17 +718,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -990,6 +894,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1000,17 +915,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
-    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1029,6 +933,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
+    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
   <ds:schemaRefs>

--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M327220\Documents\GitHub\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0FE6966-B3DC-41D3-8B5F-2206F9957FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464310CA-F9BF-4B8A-BD1E-A85CAE209E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="28110" windowHeight="16440" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
   <si>
     <t>Child</t>
   </si>
@@ -117,37 +117,19 @@
     <t>sd</t>
   </si>
   <si>
-    <t>KE50C0FF11</t>
-  </si>
-  <si>
-    <t>KE50C0IM11</t>
-  </si>
-  <si>
-    <t>2029C00004</t>
-  </si>
-  <si>
-    <t>2031C00005</t>
-  </si>
-  <si>
-    <t>2034C00012</t>
-  </si>
-  <si>
-    <t>2123OF0027</t>
-  </si>
-  <si>
-    <t>2102TPSZ93</t>
-  </si>
-  <si>
-    <t>L000005617</t>
-  </si>
-  <si>
-    <t>L000013183</t>
-  </si>
-  <si>
-    <t>G000001338</t>
-  </si>
-  <si>
-    <t>L000013788</t>
+    <t>CH65R00020</t>
+  </si>
+  <si>
+    <t>CH65R00048</t>
+  </si>
+  <si>
+    <t>CH65R00050</t>
+  </si>
+  <si>
+    <t>CH65R00052</t>
+  </si>
+  <si>
+    <t>H000000878</t>
   </si>
 </sst>
 </file>
@@ -505,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -526,7 +508,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -534,7 +516,7 @@
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -542,7 +524,7 @@
         <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -550,31 +532,7 @@
         <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
         <v>28</v>
-      </c>
-      <c r="B6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -718,6 +676,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -894,27 +872,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
+    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -931,23 +908,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
-    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M327220\Documents\GitHub\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464310CA-F9BF-4B8A-BD1E-A85CAE209E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D4ADC60-A107-48A0-BAD0-31604B87D3D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28110" windowHeight="16440" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="3990" yWindow="3585" windowWidth="20910" windowHeight="11835" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <definedName name="ID" localSheetId="0" hidden="1">"a5f5822f-2145-4cc3-aa32-d164ed237772"</definedName>
     <definedName name="ID" localSheetId="1" hidden="1">"fff7d4e2-cafa-4da0-a3ee-fa93757f1b68"</definedName>
   </definedNames>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
   <si>
     <t>Child</t>
   </si>
@@ -117,19 +117,25 @@
     <t>sd</t>
   </si>
   <si>
-    <t>CH65R00020</t>
-  </si>
-  <si>
-    <t>CH65R00048</t>
-  </si>
-  <si>
-    <t>CH65R00050</t>
-  </si>
-  <si>
-    <t>CH65R00052</t>
-  </si>
-  <si>
-    <t>H000000878</t>
+    <t>2029C00004</t>
+  </si>
+  <si>
+    <t>2031C00005</t>
+  </si>
+  <si>
+    <t>2034C00012</t>
+  </si>
+  <si>
+    <t>KE50C0FF11</t>
+  </si>
+  <si>
+    <t>KE50C0IM11</t>
+  </si>
+  <si>
+    <t>L000013814</t>
+  </si>
+  <si>
+    <t>L000013121</t>
   </si>
 </sst>
 </file>
@@ -487,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -508,7 +514,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -516,7 +522,7 @@
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -524,7 +530,7 @@
         <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -532,7 +538,15 @@
         <v>27</v>
       </c>
       <c r="B5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -676,15 +690,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
@@ -695,7 +700,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -872,15 +877,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -891,7 +897,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -908,4 +914,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M327220\Documents\GitHub\GCOHFilesTicketsEtc\GCOH Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D4ADC60-A107-48A0-BAD0-31604B87D3D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EB55C84-D060-4AD6-98AE-1203A8F4CE7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3990" yWindow="3585" windowWidth="20910" windowHeight="11835" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="-21645" yWindow="930" windowWidth="15645" windowHeight="13470" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -22,28 +22,17 @@
     <definedName name="ID" localSheetId="0" hidden="1">"a5f5822f-2145-4cc3-aa32-d164ed237772"</definedName>
     <definedName name="ID" localSheetId="1" hidden="1">"fff7d4e2-cafa-4da0-a3ee-fa93757f1b68"</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
   <si>
     <t>Child</t>
   </si>
@@ -117,25 +106,43 @@
     <t>sd</t>
   </si>
   <si>
-    <t>2029C00004</t>
-  </si>
-  <si>
-    <t>2031C00005</t>
-  </si>
-  <si>
-    <t>2034C00012</t>
-  </si>
-  <si>
-    <t>KE50C0FF11</t>
-  </si>
-  <si>
-    <t>KE50C0IM11</t>
-  </si>
-  <si>
-    <t>L000013814</t>
-  </si>
-  <si>
-    <t>L000013121</t>
+    <t>G000000918</t>
+  </si>
+  <si>
+    <t>G000000537</t>
+  </si>
+  <si>
+    <t>G000000474</t>
+  </si>
+  <si>
+    <t>G000000478</t>
+  </si>
+  <si>
+    <t>G000000443</t>
+  </si>
+  <si>
+    <t>G000000446</t>
+  </si>
+  <si>
+    <t>G000000447</t>
+  </si>
+  <si>
+    <t>G000000472</t>
+  </si>
+  <si>
+    <t>G000000563</t>
+  </si>
+  <si>
+    <t>G000000392</t>
+  </si>
+  <si>
+    <t>G000000873</t>
+  </si>
+  <si>
+    <t>G000000359</t>
+  </si>
+  <si>
+    <t>O000000007</t>
   </si>
 </sst>
 </file>
@@ -197,9 +204,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -237,7 +244,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -343,7 +350,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -485,7 +492,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -493,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -514,7 +521,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -522,7 +529,7 @@
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -530,7 +537,7 @@
         <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -538,7 +545,7 @@
         <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -546,10 +553,43 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>30</v>
       </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B1" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -701,6 +741,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -877,15 +926,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>
@@ -898,6 +938,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -914,12 +962,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EB55C84-D060-4AD6-98AE-1203A8F4CE7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7509593-C14B-4741-8E0E-2BB3672AEF58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21645" yWindow="930" windowWidth="15645" windowHeight="13470" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="-28395" yWindow="540" windowWidth="15645" windowHeight="13470" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="56">
   <si>
     <t>Child</t>
   </si>
@@ -106,43 +106,100 @@
     <t>sd</t>
   </si>
   <si>
-    <t>G000000918</t>
-  </si>
-  <si>
     <t>G000000537</t>
   </si>
   <si>
-    <t>G000000474</t>
-  </si>
-  <si>
-    <t>G000000478</t>
-  </si>
-  <si>
     <t>G000000443</t>
   </si>
   <si>
     <t>G000000446</t>
   </si>
   <si>
-    <t>G000000447</t>
-  </si>
-  <si>
-    <t>G000000472</t>
-  </si>
-  <si>
-    <t>G000000563</t>
-  </si>
-  <si>
-    <t>G000000392</t>
-  </si>
-  <si>
-    <t>G000000873</t>
-  </si>
-  <si>
-    <t>G000000359</t>
-  </si>
-  <si>
-    <t>O000000007</t>
+    <t>G000000400</t>
+  </si>
+  <si>
+    <t>G000000404</t>
+  </si>
+  <si>
+    <t>G000000414</t>
+  </si>
+  <si>
+    <t>G000000415</t>
+  </si>
+  <si>
+    <t>G000000417</t>
+  </si>
+  <si>
+    <t>G000000463</t>
+  </si>
+  <si>
+    <t>G000000464</t>
+  </si>
+  <si>
+    <t>G000000467</t>
+  </si>
+  <si>
+    <t>G000000468</t>
+  </si>
+  <si>
+    <t>G000000471</t>
+  </si>
+  <si>
+    <t>G000000511</t>
+  </si>
+  <si>
+    <t>G000000512</t>
+  </si>
+  <si>
+    <t>G000000513</t>
+  </si>
+  <si>
+    <t>G000000514</t>
+  </si>
+  <si>
+    <t>G000000869</t>
+  </si>
+  <si>
+    <t>G000000870</t>
+  </si>
+  <si>
+    <t>G000000871</t>
+  </si>
+  <si>
+    <t>G000000872</t>
+  </si>
+  <si>
+    <t>G000000879</t>
+  </si>
+  <si>
+    <t>G000000880</t>
+  </si>
+  <si>
+    <t>G000000881</t>
+  </si>
+  <si>
+    <t>G000000887</t>
+  </si>
+  <si>
+    <t>G000000888</t>
+  </si>
+  <si>
+    <t>G000000915</t>
+  </si>
+  <si>
+    <t>G000000949</t>
+  </si>
+  <si>
+    <t>G000000950</t>
+  </si>
+  <si>
+    <t>G000000993</t>
+  </si>
+  <si>
+    <t>G000000996</t>
+  </si>
+  <si>
+    <t>G000000846</t>
   </si>
 </sst>
 </file>
@@ -500,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -518,74 +575,266 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
         <v>30</v>
-      </c>
-      <c r="B8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
         <v>32</v>
       </c>
-      <c r="B10" t="s">
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>36</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>50</v>
+      </c>
+      <c r="B28" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -730,26 +979,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -926,26 +1155,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
-    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -962,4 +1192,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
+    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7509593-C14B-4741-8E0E-2BB3672AEF58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{625B0BBC-11F3-4FD7-895C-92E2EF9DD78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28395" yWindow="540" windowWidth="15645" windowHeight="13470" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="-26400" yWindow="1305" windowWidth="15645" windowHeight="13470" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="58">
   <si>
     <t>Child</t>
   </si>
@@ -200,6 +200,12 @@
   </si>
   <si>
     <t>G000000846</t>
+  </si>
+  <si>
+    <t>G000000997</t>
+  </si>
+  <si>
+    <t>G000000998</t>
   </si>
 </sst>
 </file>
@@ -823,7 +829,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B33" t="s">
         <v>41</v>
@@ -831,7 +837,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B34" t="s">
         <v>41</v>
@@ -1156,15 +1162,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
@@ -1173,6 +1170,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1195,14 +1201,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -1211,4 +1209,12 @@
     <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M327220\Documents\GitHub\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{625B0BBC-11F3-4FD7-895C-92E2EF9DD78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{264D34EF-9B33-4EB0-8CA6-1C42E0EB044D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26400" yWindow="1305" windowWidth="15645" windowHeight="13470" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="30090" yWindow="3855" windowWidth="20910" windowHeight="11835" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -22,17 +22,28 @@
     <definedName name="ID" localSheetId="0" hidden="1">"a5f5822f-2145-4cc3-aa32-d164ed237772"</definedName>
     <definedName name="ID" localSheetId="1" hidden="1">"fff7d4e2-cafa-4da0-a3ee-fa93757f1b68"</definedName>
   </definedNames>
-  <calcPr calcId="181029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
   <si>
     <t>Child</t>
   </si>
@@ -106,106 +117,40 @@
     <t>sd</t>
   </si>
   <si>
-    <t>G000000537</t>
-  </si>
-  <si>
-    <t>G000000443</t>
-  </si>
-  <si>
-    <t>G000000446</t>
-  </si>
-  <si>
-    <t>G000000400</t>
-  </si>
-  <si>
-    <t>G000000404</t>
-  </si>
-  <si>
-    <t>G000000414</t>
-  </si>
-  <si>
-    <t>G000000415</t>
-  </si>
-  <si>
-    <t>G000000417</t>
-  </si>
-  <si>
-    <t>G000000463</t>
-  </si>
-  <si>
-    <t>G000000464</t>
-  </si>
-  <si>
-    <t>G000000467</t>
-  </si>
-  <si>
-    <t>G000000468</t>
-  </si>
-  <si>
-    <t>G000000471</t>
-  </si>
-  <si>
-    <t>G000000511</t>
-  </si>
-  <si>
-    <t>G000000512</t>
-  </si>
-  <si>
-    <t>G000000513</t>
-  </si>
-  <si>
-    <t>G000000514</t>
-  </si>
-  <si>
-    <t>G000000869</t>
-  </si>
-  <si>
-    <t>G000000870</t>
-  </si>
-  <si>
-    <t>G000000871</t>
-  </si>
-  <si>
-    <t>G000000872</t>
-  </si>
-  <si>
-    <t>G000000879</t>
-  </si>
-  <si>
-    <t>G000000880</t>
-  </si>
-  <si>
-    <t>G000000881</t>
-  </si>
-  <si>
-    <t>G000000887</t>
-  </si>
-  <si>
-    <t>G000000888</t>
-  </si>
-  <si>
-    <t>G000000915</t>
-  </si>
-  <si>
-    <t>G000000949</t>
-  </si>
-  <si>
-    <t>G000000950</t>
-  </si>
-  <si>
-    <t>G000000993</t>
-  </si>
-  <si>
-    <t>G000000996</t>
-  </si>
-  <si>
-    <t>G000000846</t>
-  </si>
-  <si>
-    <t>G000000997</t>
-  </si>
-  <si>
-    <t>G000000998</t>
+    <t>DE10OF0003</t>
+  </si>
+  <si>
+    <t>1756OF0001</t>
+  </si>
+  <si>
+    <t>1756OF0006</t>
+  </si>
+  <si>
+    <t>1756OF7061</t>
+  </si>
+  <si>
+    <t>1756OF7094</t>
+  </si>
+  <si>
+    <t>2148OF0261</t>
+  </si>
+  <si>
+    <t>L000011150</t>
+  </si>
+  <si>
+    <t>L000012434</t>
+  </si>
+  <si>
+    <t>L000011146</t>
+  </si>
+  <si>
+    <t>L000011148</t>
+  </si>
+  <si>
+    <t>L000012995</t>
+  </si>
+  <si>
+    <t>L000011124</t>
   </si>
 </sst>
 </file>
@@ -267,9 +212,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -307,7 +252,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -413,7 +358,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -555,7 +500,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -563,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -581,266 +526,50 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
         <v>35</v>
-      </c>
-      <c r="B12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>47</v>
-      </c>
-      <c r="B25" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>48</v>
-      </c>
-      <c r="B26" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>49</v>
-      </c>
-      <c r="B27" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>50</v>
-      </c>
-      <c r="B28" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>51</v>
-      </c>
-      <c r="B29" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>52</v>
-      </c>
-      <c r="B30" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>53</v>
-      </c>
-      <c r="B31" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>54</v>
-      </c>
-      <c r="B32" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>56</v>
-      </c>
-      <c r="B33" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>57</v>
-      </c>
-      <c r="B34" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -985,6 +714,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -1161,27 +910,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
+    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1198,23 +946,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
-    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M327220\Documents\GitHub\GCOHFilesTicketsEtc\GCOH Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{264D34EF-9B33-4EB0-8CA6-1C42E0EB044D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D2996CB-D0FD-461C-833A-07FBBA555044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30090" yWindow="3855" windowWidth="20910" windowHeight="11835" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="-21615" yWindow="2235" windowWidth="15645" windowHeight="10575" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -22,28 +22,17 @@
     <definedName name="ID" localSheetId="0" hidden="1">"a5f5822f-2145-4cc3-aa32-d164ed237772"</definedName>
     <definedName name="ID" localSheetId="1" hidden="1">"fff7d4e2-cafa-4da0-a3ee-fa93757f1b68"</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="42">
   <si>
     <t>Child</t>
   </si>
@@ -117,40 +106,58 @@
     <t>sd</t>
   </si>
   <si>
-    <t>DE10OF0003</t>
-  </si>
-  <si>
-    <t>1756OF0001</t>
-  </si>
-  <si>
-    <t>1756OF0006</t>
-  </si>
-  <si>
-    <t>1756OF7061</t>
-  </si>
-  <si>
-    <t>1756OF7094</t>
-  </si>
-  <si>
-    <t>2148OF0261</t>
-  </si>
-  <si>
-    <t>L000011150</t>
-  </si>
-  <si>
-    <t>L000012434</t>
-  </si>
-  <si>
-    <t>L000011146</t>
-  </si>
-  <si>
-    <t>L000011148</t>
-  </si>
-  <si>
-    <t>L000012995</t>
-  </si>
-  <si>
-    <t>L000011124</t>
+    <t>2148TASA01</t>
+  </si>
+  <si>
+    <t>2148TASA99</t>
+  </si>
+  <si>
+    <t>2148TASB00</t>
+  </si>
+  <si>
+    <t>2148TASB01</t>
+  </si>
+  <si>
+    <t>2148TASB99</t>
+  </si>
+  <si>
+    <t>2148TBSZ20</t>
+  </si>
+  <si>
+    <t>2148TBSZ21</t>
+  </si>
+  <si>
+    <t>2148TFSZ64</t>
+  </si>
+  <si>
+    <t>2148TKSZ70</t>
+  </si>
+  <si>
+    <t>2148TQSZ91</t>
+  </si>
+  <si>
+    <t>2148TQSZ92</t>
+  </si>
+  <si>
+    <t>2148TCSZ30</t>
+  </si>
+  <si>
+    <t>2148TFSZ60</t>
+  </si>
+  <si>
+    <t>2148TFSZ61</t>
+  </si>
+  <si>
+    <t>2148TFSZ62</t>
+  </si>
+  <si>
+    <t>2148TFSZ63</t>
+  </si>
+  <si>
+    <t>2148TASA00</t>
+  </si>
+  <si>
+    <t>L000013816</t>
   </si>
 </sst>
 </file>
@@ -212,9 +219,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -252,7 +259,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -358,7 +365,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -500,7 +507,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -508,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -529,7 +536,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -537,7 +544,7 @@
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -545,7 +552,7 @@
         <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -553,7 +560,7 @@
         <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -561,7 +568,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -569,11 +576,99 @@
         <v>29</v>
       </c>
       <c r="B7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>35</v>
       </c>
+      <c r="B13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" t="s">
+        <v>41</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}"/>
+  <autoFilter ref="A1:B18" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -723,17 +818,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -910,6 +994,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
   <ds:schemaRefs>
@@ -919,17 +1014,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
-    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -946,4 +1030,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
+    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M327220\Documents\GitHub\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D2996CB-D0FD-461C-833A-07FBBA555044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AC76800-6DB8-4373-AF33-633C074FB6C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21615" yWindow="2235" windowWidth="15645" windowHeight="10575" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="2310" yWindow="1545" windowWidth="20910" windowHeight="11835" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -22,17 +22,28 @@
     <definedName name="ID" localSheetId="0" hidden="1">"a5f5822f-2145-4cc3-aa32-d164ed237772"</definedName>
     <definedName name="ID" localSheetId="1" hidden="1">"fff7d4e2-cafa-4da0-a3ee-fa93757f1b68"</definedName>
   </definedNames>
-  <calcPr calcId="181029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="45">
   <si>
     <t>Child</t>
   </si>
@@ -106,58 +117,67 @@
     <t>sd</t>
   </si>
   <si>
-    <t>2148TASA01</t>
-  </si>
-  <si>
-    <t>2148TASA99</t>
-  </si>
-  <si>
-    <t>2148TASB00</t>
-  </si>
-  <si>
-    <t>2148TASB01</t>
-  </si>
-  <si>
-    <t>2148TASB99</t>
-  </si>
-  <si>
-    <t>2148TBSZ20</t>
-  </si>
-  <si>
-    <t>2148TBSZ21</t>
-  </si>
-  <si>
-    <t>2148TFSZ64</t>
-  </si>
-  <si>
-    <t>2148TKSZ70</t>
-  </si>
-  <si>
-    <t>2148TQSZ91</t>
-  </si>
-  <si>
-    <t>2148TQSZ92</t>
-  </si>
-  <si>
-    <t>2148TCSZ30</t>
-  </si>
-  <si>
-    <t>2148TFSZ60</t>
-  </si>
-  <si>
-    <t>2148TFSZ61</t>
-  </si>
-  <si>
-    <t>2148TFSZ62</t>
-  </si>
-  <si>
-    <t>2148TFSZ63</t>
-  </si>
-  <si>
-    <t>2148TASA00</t>
-  </si>
-  <si>
-    <t>L000013816</t>
+    <t>AE50GCO220</t>
+  </si>
+  <si>
+    <t>CN90GMK003</t>
+  </si>
+  <si>
+    <t>DE10624905</t>
+  </si>
+  <si>
+    <t>DE10624906</t>
+  </si>
+  <si>
+    <t>DE10GM1057</t>
+  </si>
+  <si>
+    <t>DE10GMK003</t>
+  </si>
+  <si>
+    <t>DE10GMK004</t>
+  </si>
+  <si>
+    <t>DE10Z03107</t>
+  </si>
+  <si>
+    <t>DE10Z03108</t>
+  </si>
+  <si>
+    <t>DE10Z03109</t>
+  </si>
+  <si>
+    <t>DE10Z03110</t>
+  </si>
+  <si>
+    <t>1937GMK003</t>
+  </si>
+  <si>
+    <t>2025GMK003</t>
+  </si>
+  <si>
+    <t>2123Z03104</t>
+  </si>
+  <si>
+    <t>G000001361</t>
+  </si>
+  <si>
+    <t>G000001362</t>
+  </si>
+  <si>
+    <t>G000001366</t>
+  </si>
+  <si>
+    <t>G000001364</t>
+  </si>
+  <si>
+    <t>G000001365</t>
+  </si>
+  <si>
+    <t>G000001360</t>
+  </si>
+  <si>
+    <t>G000001363</t>
   </si>
 </sst>
 </file>
@@ -219,9 +239,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -259,7 +279,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -365,7 +385,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -507,7 +527,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -515,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -536,7 +556,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -544,7 +564,7 @@
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -552,7 +572,7 @@
         <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -560,7 +580,7 @@
         <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -568,7 +588,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -584,7 +604,7 @@
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -592,7 +612,7 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -600,7 +620,7 @@
         <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -608,7 +628,7 @@
         <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -616,7 +636,7 @@
         <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -624,7 +644,7 @@
         <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -632,7 +652,7 @@
         <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -640,31 +660,7 @@
         <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
         <v>39</v>
-      </c>
-      <c r="B17" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -809,15 +805,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -994,6 +981,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1006,14 +1002,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1032,6 +1020,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>

--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M327220\Documents\GitHub\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AC76800-6DB8-4373-AF33-633C074FB6C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAECB218-AA89-4258-8E4D-C033E33DF7A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2310" yWindow="1545" windowWidth="20910" windowHeight="11835" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="28110" windowHeight="16440" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="39">
   <si>
     <t>Child</t>
   </si>
@@ -117,67 +117,49 @@
     <t>sd</t>
   </si>
   <si>
-    <t>AE50GCO220</t>
-  </si>
-  <si>
-    <t>CN90GMK003</t>
-  </si>
-  <si>
-    <t>DE10624905</t>
-  </si>
-  <si>
-    <t>DE10624906</t>
-  </si>
-  <si>
-    <t>DE10GM1057</t>
-  </si>
-  <si>
-    <t>DE10GMK003</t>
-  </si>
-  <si>
-    <t>DE10GMK004</t>
-  </si>
-  <si>
-    <t>DE10Z03107</t>
-  </si>
-  <si>
-    <t>DE10Z03108</t>
-  </si>
-  <si>
-    <t>DE10Z03109</t>
-  </si>
-  <si>
-    <t>DE10Z03110</t>
-  </si>
-  <si>
-    <t>1937GMK003</t>
-  </si>
-  <si>
-    <t>2025GMK003</t>
-  </si>
-  <si>
-    <t>2123Z03104</t>
-  </si>
-  <si>
-    <t>G000001361</t>
-  </si>
-  <si>
-    <t>G000001362</t>
-  </si>
-  <si>
-    <t>G000001366</t>
-  </si>
-  <si>
-    <t>G000001364</t>
-  </si>
-  <si>
-    <t>G000001365</t>
-  </si>
-  <si>
-    <t>G000001360</t>
-  </si>
-  <si>
-    <t>G000001363</t>
+    <t>DE04G0IT99</t>
+  </si>
+  <si>
+    <t>DE04O01001</t>
+  </si>
+  <si>
+    <t>DE04O01002</t>
+  </si>
+  <si>
+    <t>DE04Z03110</t>
+  </si>
+  <si>
+    <t>CN01Z03105</t>
+  </si>
+  <si>
+    <t>DE04Z03108</t>
+  </si>
+  <si>
+    <t>DE10Z03113</t>
+  </si>
+  <si>
+    <t>IN01Z03101</t>
+  </si>
+  <si>
+    <t>JP01Z03103</t>
+  </si>
+  <si>
+    <t>US01Z03107</t>
+  </si>
+  <si>
+    <t>KR03Z03104</t>
+  </si>
+  <si>
+    <t>US10Z03102</t>
+  </si>
+  <si>
+    <t>P000001273</t>
+  </si>
+  <si>
+    <t>P000001268</t>
+  </si>
+  <si>
+    <t>P000001271</t>
   </si>
 </sst>
 </file>
@@ -535,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -556,7 +538,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -564,7 +546,7 @@
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -572,7 +554,7 @@
         <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -580,7 +562,7 @@
         <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -588,7 +570,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -596,7 +578,7 @@
         <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -604,7 +586,7 @@
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -612,7 +594,7 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -620,7 +602,7 @@
         <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -636,7 +618,7 @@
         <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -644,23 +626,7 @@
         <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -805,6 +771,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -981,27 +967,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
+    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1018,23 +1003,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
-    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M327220\Documents\GitHub\GCOHFilesTicketsEtc\GCOH Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAECB218-AA89-4258-8E4D-C033E33DF7A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6926FC97-AC68-4515-BFF9-7B2A7EB9BD26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="28110" windowHeight="16440" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="-21390" yWindow="2205" windowWidth="15645" windowHeight="10575" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="7" r:id="rId2"/>
+    <sheet name="Pierre to do" sheetId="8" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MDGF!$A$1:$B$1</definedName>
@@ -22,28 +23,17 @@
     <definedName name="ID" localSheetId="0" hidden="1">"a5f5822f-2145-4cc3-aa32-d164ed237772"</definedName>
     <definedName name="ID" localSheetId="1" hidden="1">"fff7d4e2-cafa-4da0-a3ee-fa93757f1b68"</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="58">
   <si>
     <t>Child</t>
   </si>
@@ -117,49 +107,106 @@
     <t>sd</t>
   </si>
   <si>
-    <t>DE04G0IT99</t>
-  </si>
-  <si>
-    <t>DE04O01001</t>
-  </si>
-  <si>
-    <t>DE04O01002</t>
-  </si>
-  <si>
-    <t>DE04Z03110</t>
-  </si>
-  <si>
-    <t>CN01Z03105</t>
-  </si>
-  <si>
-    <t>DE04Z03108</t>
-  </si>
-  <si>
-    <t>DE10Z03113</t>
-  </si>
-  <si>
-    <t>IN01Z03101</t>
-  </si>
-  <si>
-    <t>JP01Z03103</t>
-  </si>
-  <si>
-    <t>US01Z03107</t>
-  </si>
-  <si>
-    <t>KR03Z03104</t>
-  </si>
-  <si>
-    <t>US10Z03102</t>
-  </si>
-  <si>
-    <t>P000001273</t>
-  </si>
-  <si>
-    <t>P000001268</t>
-  </si>
-  <si>
-    <t>P000001271</t>
+    <t>G000000400</t>
+  </si>
+  <si>
+    <t>G000000846</t>
+  </si>
+  <si>
+    <t>G000000404</t>
+  </si>
+  <si>
+    <t>G000000414</t>
+  </si>
+  <si>
+    <t>G000000415</t>
+  </si>
+  <si>
+    <t>G000000417</t>
+  </si>
+  <si>
+    <t>G000000443</t>
+  </si>
+  <si>
+    <t>G000000446</t>
+  </si>
+  <si>
+    <t>G000000463</t>
+  </si>
+  <si>
+    <t>G000000464</t>
+  </si>
+  <si>
+    <t>G000000467</t>
+  </si>
+  <si>
+    <t>G000000468</t>
+  </si>
+  <si>
+    <t>G000000471</t>
+  </si>
+  <si>
+    <t>G000000511</t>
+  </si>
+  <si>
+    <t>G000000512</t>
+  </si>
+  <si>
+    <t>G000000513</t>
+  </si>
+  <si>
+    <t>G000000514</t>
+  </si>
+  <si>
+    <t>G000000537</t>
+  </si>
+  <si>
+    <t>G000000869</t>
+  </si>
+  <si>
+    <t>G000000870</t>
+  </si>
+  <si>
+    <t>G000000871</t>
+  </si>
+  <si>
+    <t>G000000872</t>
+  </si>
+  <si>
+    <t>G000000879</t>
+  </si>
+  <si>
+    <t>G000000880</t>
+  </si>
+  <si>
+    <t>G000000881</t>
+  </si>
+  <si>
+    <t>G000000887</t>
+  </si>
+  <si>
+    <t>G000000888</t>
+  </si>
+  <si>
+    <t>G000000915</t>
+  </si>
+  <si>
+    <t>G000000949</t>
+  </si>
+  <si>
+    <t>G000000950</t>
+  </si>
+  <si>
+    <t>G000000993</t>
+  </si>
+  <si>
+    <t>G000000996</t>
+  </si>
+  <si>
+    <t>G000000997</t>
+  </si>
+  <si>
+    <t>G000000998</t>
   </si>
 </sst>
 </file>
@@ -221,9 +268,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -261,7 +308,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -367,7 +414,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -509,7 +556,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -517,7 +564,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -538,99 +585,267 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
         <v>26</v>
-      </c>
-      <c r="B4" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
         <v>27</v>
-      </c>
-      <c r="B5" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
         <v>28</v>
-      </c>
-      <c r="B6" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
         <v>32</v>
-      </c>
-      <c r="B10" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>38</v>
       </c>
+      <c r="B15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>53</v>
+      </c>
+      <c r="B30" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>54</v>
+      </c>
+      <c r="B31" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>55</v>
+      </c>
+      <c r="B32" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>57</v>
+      </c>
+      <c r="B34" t="s">
+        <v>42</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B18" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}"/>
+  <autoFilter ref="A1:B6" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -770,27 +985,281 @@
 </worksheet>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DADB64C-1560-4418-AEF8-AFB915F63B31}">
+  <dimension ref="A1:B33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>55</v>
+      </c>
+      <c r="B31" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>56</v>
+      </c>
+      <c r="B32" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>57</v>
+      </c>
+      <c r="B33" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -967,26 +1436,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
-    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1003,4 +1473,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
+    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M327220\Documents\GitHub\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6926FC97-AC68-4515-BFF9-7B2A7EB9BD26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D135B1B6-527D-4792-8964-17B7683C3ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21390" yWindow="2205" windowWidth="15645" windowHeight="10575" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28110" windowHeight="16440" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -21,19 +21,31 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MDGF!$A$1:$B$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$A$5:$B$5</definedName>
     <definedName name="ID" localSheetId="0" hidden="1">"a5f5822f-2145-4cc3-aa32-d164ed237772"</definedName>
+    <definedName name="ID" localSheetId="2" hidden="1">"2b5e4bcf-a0bb-4962-aef7-0fa656cb902f"</definedName>
     <definedName name="ID" localSheetId="1" hidden="1">"fff7d4e2-cafa-4da0-a3ee-fa93757f1b68"</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="102">
   <si>
     <t>Child</t>
   </si>
@@ -207,6 +219,138 @@
   </si>
   <si>
     <t>G000000998</t>
+  </si>
+  <si>
+    <t>KE50C0FF10</t>
+  </si>
+  <si>
+    <t>1756C00005</t>
+  </si>
+  <si>
+    <t>1756CS7063</t>
+  </si>
+  <si>
+    <t>1756CS7346</t>
+  </si>
+  <si>
+    <t>1756OF0007</t>
+  </si>
+  <si>
+    <t>1937L52686</t>
+  </si>
+  <si>
+    <t>2025C01122</t>
+  </si>
+  <si>
+    <t>2063C05891</t>
+  </si>
+  <si>
+    <t>2063C06245</t>
+  </si>
+  <si>
+    <t>2088C00662</t>
+  </si>
+  <si>
+    <t>2088L50001</t>
+  </si>
+  <si>
+    <t>2102CS0020</t>
+  </si>
+  <si>
+    <t>2102CS0713</t>
+  </si>
+  <si>
+    <t>2102OF0002</t>
+  </si>
+  <si>
+    <t>2102TESZ81</t>
+  </si>
+  <si>
+    <t>2103OF0001</t>
+  </si>
+  <si>
+    <t>2123C00049</t>
+  </si>
+  <si>
+    <t>2123CS0002</t>
+  </si>
+  <si>
+    <t>2123L50008</t>
+  </si>
+  <si>
+    <t>2125C00005</t>
+  </si>
+  <si>
+    <t>2128C00002</t>
+  </si>
+  <si>
+    <t>2137TPM813</t>
+  </si>
+  <si>
+    <t>2137TPM819</t>
+  </si>
+  <si>
+    <t>2148L50220</t>
+  </si>
+  <si>
+    <t>DE10639300</t>
+  </si>
+  <si>
+    <t>DE10650100</t>
+  </si>
+  <si>
+    <t>DE10OF0005</t>
+  </si>
+  <si>
+    <t>L000008834</t>
+  </si>
+  <si>
+    <t>L000013555</t>
+  </si>
+  <si>
+    <t>L000013840</t>
+  </si>
+  <si>
+    <t>L000013850</t>
+  </si>
+  <si>
+    <t>L000011362</t>
+  </si>
+  <si>
+    <t>L000011397</t>
+  </si>
+  <si>
+    <t>L000013855</t>
+  </si>
+  <si>
+    <t>L000013554</t>
+  </si>
+  <si>
+    <t>L000013841</t>
+  </si>
+  <si>
+    <t>L000006593</t>
+  </si>
+  <si>
+    <t>L000013861</t>
+  </si>
+  <si>
+    <t>L000013532</t>
+  </si>
+  <si>
+    <t>L000011394</t>
+  </si>
+  <si>
+    <t>L000011363</t>
+  </si>
+  <si>
+    <t>L000010057</t>
+  </si>
+  <si>
+    <t>L000013810</t>
+  </si>
+  <si>
+    <t>L000013831</t>
   </si>
 </sst>
 </file>
@@ -268,9 +412,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -308,7 +452,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -414,7 +558,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -556,7 +700,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -564,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -582,266 +726,218 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="B27" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="B28" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>52</v>
-      </c>
-      <c r="B29" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>53</v>
-      </c>
-      <c r="B30" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>54</v>
-      </c>
-      <c r="B31" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>55</v>
-      </c>
-      <c r="B32" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>56</v>
-      </c>
-      <c r="B33" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>57</v>
-      </c>
-      <c r="B34" t="s">
-        <v>42</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1256,6 +1352,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <customProperties>
+    <customPr name="_pios_id" r:id="rId1"/>
+  </customProperties>
 </worksheet>
 </file>
 
@@ -1437,15 +1536,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
@@ -1454,6 +1544,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1476,14 +1575,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -1492,4 +1583,12 @@
     <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -1,51 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M327220\Documents\GitHub\GCOHFilesTicketsEtc\GCOH Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D135B1B6-527D-4792-8964-17B7683C3ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E0F9099-B98A-4FFE-A85A-4861DBF2B55C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28110" windowHeight="16440" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="-26535" yWindow="1740" windowWidth="15645" windowHeight="10575" activeTab="3" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="7" r:id="rId2"/>
-    <sheet name="Pierre to do" sheetId="8" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="9" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="7" r:id="rId3"/>
+    <sheet name="Pierre to do" sheetId="8" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MDGF!$A$1:$B$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$A$5:$B$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MDGF!$A$1:$D$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet1!$A$5:$B$5</definedName>
     <definedName name="ID" localSheetId="0" hidden="1">"a5f5822f-2145-4cc3-aa32-d164ed237772"</definedName>
-    <definedName name="ID" localSheetId="2" hidden="1">"2b5e4bcf-a0bb-4962-aef7-0fa656cb902f"</definedName>
-    <definedName name="ID" localSheetId="1" hidden="1">"fff7d4e2-cafa-4da0-a3ee-fa93757f1b68"</definedName>
+    <definedName name="ID" localSheetId="3" hidden="1">"2b5e4bcf-a0bb-4962-aef7-0fa656cb902f"</definedName>
+    <definedName name="ID" localSheetId="2" hidden="1">"fff7d4e2-cafa-4da0-a3ee-fa93757f1b68"</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="62">
   <si>
     <t>Child</t>
   </si>
@@ -221,136 +211,16 @@
     <t>G000000998</t>
   </si>
   <si>
-    <t>KE50C0FF10</t>
-  </si>
-  <si>
-    <t>1756C00005</t>
-  </si>
-  <si>
-    <t>1756CS7063</t>
-  </si>
-  <si>
-    <t>1756CS7346</t>
-  </si>
-  <si>
-    <t>1756OF0007</t>
-  </si>
-  <si>
-    <t>1937L52686</t>
-  </si>
-  <si>
-    <t>2025C01122</t>
-  </si>
-  <si>
-    <t>2063C05891</t>
-  </si>
-  <si>
-    <t>2063C06245</t>
-  </si>
-  <si>
-    <t>2088C00662</t>
-  </si>
-  <si>
-    <t>2088L50001</t>
-  </si>
-  <si>
-    <t>2102CS0020</t>
-  </si>
-  <si>
-    <t>2102CS0713</t>
-  </si>
-  <si>
-    <t>2102OF0002</t>
-  </si>
-  <si>
-    <t>2102TESZ81</t>
-  </si>
-  <si>
-    <t>2103OF0001</t>
-  </si>
-  <si>
-    <t>2123C00049</t>
-  </si>
-  <si>
-    <t>2123CS0002</t>
-  </si>
-  <si>
-    <t>2123L50008</t>
-  </si>
-  <si>
-    <t>2125C00005</t>
-  </si>
-  <si>
-    <t>2128C00002</t>
-  </si>
-  <si>
-    <t>2137TPM813</t>
-  </si>
-  <si>
-    <t>2137TPM819</t>
-  </si>
-  <si>
-    <t>2148L50220</t>
-  </si>
-  <si>
-    <t>DE10639300</t>
-  </si>
-  <si>
-    <t>DE10650100</t>
-  </si>
-  <si>
-    <t>DE10OF0005</t>
-  </si>
-  <si>
-    <t>L000008834</t>
-  </si>
-  <si>
-    <t>L000013555</t>
-  </si>
-  <si>
-    <t>L000013840</t>
-  </si>
-  <si>
-    <t>L000013850</t>
-  </si>
-  <si>
-    <t>L000011362</t>
-  </si>
-  <si>
-    <t>L000011397</t>
-  </si>
-  <si>
-    <t>L000013855</t>
-  </si>
-  <si>
-    <t>L000013554</t>
-  </si>
-  <si>
-    <t>L000013841</t>
-  </si>
-  <si>
-    <t>L000006593</t>
-  </si>
-  <si>
-    <t>L000013861</t>
-  </si>
-  <si>
-    <t>L000013532</t>
-  </si>
-  <si>
-    <t>L000011394</t>
-  </si>
-  <si>
-    <t>L000011363</t>
-  </si>
-  <si>
-    <t>L000010057</t>
-  </si>
-  <si>
-    <t>L000013810</t>
-  </si>
-  <si>
-    <t>L000013831</t>
+    <t>G000000472</t>
+  </si>
+  <si>
+    <t>G000000447</t>
+  </si>
+  <si>
+    <t>G000000359</t>
+  </si>
+  <si>
+    <t>G000000873</t>
   </si>
 </sst>
 </file>
@@ -412,9 +282,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -452,7 +322,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -558,7 +428,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -700,7 +570,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -708,7 +578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -716,7 +586,7 @@
     <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -724,224 +594,367 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="D2" t="e">
+        <f>VLOOKUP(A2,Sheet2!A:A,1,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="D3" t="e">
+        <f>VLOOKUP(A3,Sheet2!A:A,1,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="D4" t="e">
+        <f>VLOOKUP(A4,Sheet2!A:A,1,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="D5" t="e">
+        <f>VLOOKUP(A5,Sheet2!A:A,1,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+      <c r="D6" t="e">
+        <f>VLOOKUP(A6,Sheet2!A:A,1,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="D7" t="e">
+        <f>VLOOKUP(A7,Sheet2!A:A,1,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="D8" t="e">
+        <f>VLOOKUP(A8,Sheet2!A:A,1,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="D9" t="e">
+        <f>VLOOKUP(A9,Sheet2!A:A,1,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="D10" t="e">
+        <f>VLOOKUP(A10,Sheet2!A:A,1,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="D11" t="e">
+        <f>VLOOKUP(A11,Sheet2!A:A,1,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="D12" t="e">
+        <f>VLOOKUP(A12,Sheet2!A:A,1,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="D13" t="e">
+        <f>VLOOKUP(A13,Sheet2!A:A,1,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="D14" t="e">
+        <f>VLOOKUP(A14,Sheet2!A:A,1,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="D15" t="e">
+        <f>VLOOKUP(A15,Sheet2!A:A,1,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="D16" t="e">
+        <f>VLOOKUP(A16,Sheet2!A:A,1,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="D17" t="e">
+        <f>VLOOKUP(A17,Sheet2!A:A,1,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="B18" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+      <c r="D18" t="e">
+        <f>VLOOKUP(A18,Sheet2!A:A,1,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="D19" t="e">
+        <f>VLOOKUP(A19,Sheet2!A:A,1,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="B20" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="D20" t="e">
+        <f>VLOOKUP(A20,Sheet2!A:A,1,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="B21" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="D21" t="e">
+        <f>VLOOKUP(A21,Sheet2!A:A,1,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+      <c r="D22" t="e">
+        <f>VLOOKUP(A22,Sheet2!A:A,1,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="B23" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+      <c r="D23" t="e">
+        <f>VLOOKUP(A23,Sheet2!A:A,1,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="B24" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+      <c r="D24" t="e">
+        <f>VLOOKUP(A24,Sheet2!A:A,1,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="B25" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+      <c r="D25" t="e">
+        <f>VLOOKUP(A25,Sheet2!A:A,1,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="B26" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+      <c r="D26" t="e">
+        <f>VLOOKUP(A26,Sheet2!A:A,1,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="B27" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="D27" t="e">
+        <f>VLOOKUP(A27,Sheet2!A:A,1,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="B28" t="s">
-        <v>101</v>
+        <v>52</v>
+      </c>
+      <c r="D28" t="e">
+        <f>VLOOKUP(A28,Sheet2!A:A,1,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" t="e">
+        <f>VLOOKUP(A29,Sheet2!A:A,1,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" t="e">
+        <f>VLOOKUP(A30,Sheet2!A:A,1,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D31" t="e">
+        <f>VLOOKUP(A31,Sheet2!A:A,1,0)</f>
+        <v>#N/A</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B6" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -952,6 +965,63 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6610AEAF-E772-4D88-8C2B-5DD0E0FA07BD}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1">
+        <f>LEN(A1)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C5481AA-55DD-41F0-8076-D4F5ED7BA00E}">
   <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1081,9 +1151,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DADB64C-1560-4418-AEF8-AFB915F63B31}">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1128,31 +1198,31 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
         <v>32</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
         <v>32</v>
@@ -1160,31 +1230,31 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
         <v>36</v>
-      </c>
-      <c r="B12" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
         <v>36</v>
@@ -1192,161 +1262,137 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" t="s">
         <v>44</v>
-      </c>
-      <c r="B20" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" t="s">
         <v>48</v>
-      </c>
-      <c r="B24" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B25" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B27" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" t="s">
         <v>52</v>
-      </c>
-      <c r="B28" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B29" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B30" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>55</v>
-      </c>
-      <c r="B31" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>56</v>
-      </c>
-      <c r="B32" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>57</v>
-      </c>
-      <c r="B33" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1359,6 +1405,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -1535,27 +1601,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
+    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1572,23 +1637,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
-    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M327220\Documents\GitHub\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E0F9099-B98A-4FFE-A85A-4861DBF2B55C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B76BF2C8-31B0-4899-9079-7C929D54D99F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26535" yWindow="1740" windowWidth="15645" windowHeight="10575" activeTab="3" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="20910" windowHeight="8370" activeTab="3" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -24,18 +24,30 @@
     <definedName name="ID" localSheetId="0" hidden="1">"a5f5822f-2145-4cc3-aa32-d164ed237772"</definedName>
     <definedName name="ID" localSheetId="3" hidden="1">"2b5e4bcf-a0bb-4962-aef7-0fa656cb902f"</definedName>
     <definedName name="ID" localSheetId="2" hidden="1">"fff7d4e2-cafa-4da0-a3ee-fa93757f1b68"</definedName>
+    <definedName name="ID" localSheetId="1" hidden="1">"d59c0fca-ea81-453e-b1af-313ab178d2df"</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="66">
   <si>
     <t>Child</t>
   </si>
@@ -221,6 +233,18 @@
   </si>
   <si>
     <t>G000000873</t>
+  </si>
+  <si>
+    <t>CZ50GIT01D</t>
+  </si>
+  <si>
+    <t>CZ50GM1000</t>
+  </si>
+  <si>
+    <t>CZ50GIT01M</t>
+  </si>
+  <si>
+    <t>CZ50OF0007</t>
   </si>
 </sst>
 </file>
@@ -282,9 +306,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -322,7 +346,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -428,7 +452,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -570,7 +594,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1018,6 +1042,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <customProperties>
+    <customPr name="_pios_id" r:id="rId1"/>
+  </customProperties>
 </worksheet>
 </file>
 
@@ -1153,247 +1180,47 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DADB64C-1560-4418-AEF8-AFB915F63B31}">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>45</v>
-      </c>
-      <c r="B18" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>47</v>
-      </c>
-      <c r="B20" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>48</v>
-      </c>
-      <c r="B21" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>49</v>
-      </c>
-      <c r="B22" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>50</v>
-      </c>
-      <c r="B23" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>51</v>
-      </c>
-      <c r="B24" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>52</v>
-      </c>
-      <c r="B25" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>53</v>
-      </c>
-      <c r="B26" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>54</v>
-      </c>
-      <c r="B27" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>55</v>
-      </c>
-      <c r="B28" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>56</v>
-      </c>
-      <c r="B29" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>57</v>
-      </c>
-      <c r="B30" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1405,15 +1232,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
@@ -1424,7 +1242,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -1601,15 +1419,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -1620,7 +1439,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1637,4 +1456,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M327220\Documents\GitHub\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B76BF2C8-31B0-4899-9079-7C929D54D99F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85002BF8-7DC9-4C29-A5B1-18988E2A8C1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="20910" windowHeight="8370" activeTab="3" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="20910" windowHeight="8370" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="37">
   <si>
     <t>Child</t>
   </si>
@@ -121,106 +121,19 @@
     <t>sd</t>
   </si>
   <si>
-    <t>G000000400</t>
-  </si>
-  <si>
-    <t>G000000846</t>
-  </si>
-  <si>
     <t>G000000404</t>
   </si>
   <si>
-    <t>G000000414</t>
-  </si>
-  <si>
     <t>G000000415</t>
   </si>
   <si>
-    <t>G000000417</t>
-  </si>
-  <si>
     <t>G000000443</t>
   </si>
   <si>
     <t>G000000446</t>
   </si>
   <si>
-    <t>G000000463</t>
-  </si>
-  <si>
-    <t>G000000464</t>
-  </si>
-  <si>
-    <t>G000000467</t>
-  </si>
-  <si>
-    <t>G000000468</t>
-  </si>
-  <si>
-    <t>G000000471</t>
-  </si>
-  <si>
-    <t>G000000511</t>
-  </si>
-  <si>
-    <t>G000000512</t>
-  </si>
-  <si>
-    <t>G000000513</t>
-  </si>
-  <si>
-    <t>G000000514</t>
-  </si>
-  <si>
     <t>G000000537</t>
-  </si>
-  <si>
-    <t>G000000869</t>
-  </si>
-  <si>
-    <t>G000000870</t>
-  </si>
-  <si>
-    <t>G000000871</t>
-  </si>
-  <si>
-    <t>G000000872</t>
-  </si>
-  <si>
-    <t>G000000879</t>
-  </si>
-  <si>
-    <t>G000000880</t>
-  </si>
-  <si>
-    <t>G000000881</t>
-  </si>
-  <si>
-    <t>G000000887</t>
-  </si>
-  <si>
-    <t>G000000888</t>
-  </si>
-  <si>
-    <t>G000000915</t>
-  </si>
-  <si>
-    <t>G000000949</t>
-  </si>
-  <si>
-    <t>G000000950</t>
-  </si>
-  <si>
-    <t>G000000993</t>
-  </si>
-  <si>
-    <t>G000000996</t>
-  </si>
-  <si>
-    <t>G000000997</t>
-  </si>
-  <si>
-    <t>G000000998</t>
   </si>
   <si>
     <t>G000000472</t>
@@ -602,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -610,7 +523,7 @@
     <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -618,364 +531,44 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" t="e">
-        <f>VLOOKUP(A2,Sheet2!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="e">
-        <f>VLOOKUP(A3,Sheet2!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="e">
-        <f>VLOOKUP(A4,Sheet2!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="e">
-        <f>VLOOKUP(A5,Sheet2!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="e">
-        <f>VLOOKUP(A6,Sheet2!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" t="e">
-        <f>VLOOKUP(A7,Sheet2!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" t="e">
-        <f>VLOOKUP(A8,Sheet2!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" t="e">
-        <f>VLOOKUP(A9,Sheet2!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" t="e">
-        <f>VLOOKUP(A10,Sheet2!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" t="e">
-        <f>VLOOKUP(A11,Sheet2!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" t="e">
-        <f>VLOOKUP(A12,Sheet2!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" t="e">
-        <f>VLOOKUP(A13,Sheet2!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" t="e">
-        <f>VLOOKUP(A14,Sheet2!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" t="e">
-        <f>VLOOKUP(A15,Sheet2!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" t="e">
-        <f>VLOOKUP(A16,Sheet2!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" t="s">
-        <v>42</v>
-      </c>
-      <c r="D17" t="e">
-        <f>VLOOKUP(A17,Sheet2!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>44</v>
-      </c>
-      <c r="B18" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" t="e">
-        <f>VLOOKUP(A18,Sheet2!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B19" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" t="e">
-        <f>VLOOKUP(A19,Sheet2!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" t="e">
-        <f>VLOOKUP(A20,Sheet2!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>47</v>
-      </c>
-      <c r="B21" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" t="e">
-        <f>VLOOKUP(A21,Sheet2!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>48</v>
-      </c>
-      <c r="B22" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" t="e">
-        <f>VLOOKUP(A22,Sheet2!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>49</v>
-      </c>
-      <c r="B23" t="s">
-        <v>48</v>
-      </c>
-      <c r="D23" t="e">
-        <f>VLOOKUP(A23,Sheet2!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>50</v>
-      </c>
-      <c r="B24" t="s">
-        <v>48</v>
-      </c>
-      <c r="D24" t="e">
-        <f>VLOOKUP(A24,Sheet2!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>51</v>
-      </c>
-      <c r="B25" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" t="e">
-        <f>VLOOKUP(A25,Sheet2!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" t="e">
-        <f>VLOOKUP(A26,Sheet2!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27" t="s">
-        <v>52</v>
-      </c>
-      <c r="D27" t="e">
-        <f>VLOOKUP(A27,Sheet2!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" t="s">
-        <v>52</v>
-      </c>
-      <c r="D28" t="e">
-        <f>VLOOKUP(A28,Sheet2!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>55</v>
-      </c>
-      <c r="B29" t="s">
-        <v>52</v>
-      </c>
-      <c r="D29" t="e">
-        <f>VLOOKUP(A29,Sheet2!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>56</v>
-      </c>
-      <c r="B30" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" t="e">
-        <f>VLOOKUP(A30,Sheet2!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>57</v>
-      </c>
-      <c r="B31" t="s">
-        <v>42</v>
-      </c>
-      <c r="D31" t="e">
-        <f>VLOOKUP(A31,Sheet2!A:A,1,0)</f>
-        <v>#N/A</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -998,10 +591,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="C1">
         <f>LEN(A1)</f>
@@ -1010,34 +603,34 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1180,50 +773,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DADB64C-1560-4418-AEF8-AFB915F63B31}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-  </sheetData>
+  <cols>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <customProperties>
     <customPr name="_pios_id" r:id="rId1"/>
@@ -1232,14 +787,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1420,21 +973,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
-    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1459,9 +1011,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
+    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M327220\Documents\GitHub\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85002BF8-7DC9-4C29-A5B1-18988E2A8C1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D90F36-8E2C-4288-847D-676C78F48388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="20910" windowHeight="8370" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="20910" windowHeight="9345" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="45">
   <si>
     <t>Child</t>
   </si>
@@ -148,16 +148,40 @@
     <t>G000000873</t>
   </si>
   <si>
-    <t>CZ50GIT01D</t>
-  </si>
-  <si>
-    <t>CZ50GM1000</t>
-  </si>
-  <si>
-    <t>CZ50GIT01M</t>
-  </si>
-  <si>
-    <t>CZ50OF0007</t>
+    <t>DE20538353</t>
+  </si>
+  <si>
+    <t>DE10538353</t>
+  </si>
+  <si>
+    <t>DE10538602</t>
+  </si>
+  <si>
+    <t>DE10538603</t>
+  </si>
+  <si>
+    <t>DE10538604</t>
+  </si>
+  <si>
+    <t>DE20538602</t>
+  </si>
+  <si>
+    <t>DE20538603</t>
+  </si>
+  <si>
+    <t>DE20538604</t>
+  </si>
+  <si>
+    <t>G000000994</t>
+  </si>
+  <si>
+    <t>G000001084</t>
+  </si>
+  <si>
+    <t>G000001017</t>
+  </si>
+  <si>
+    <t>G000000943</t>
   </si>
 </sst>
 </file>
@@ -515,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -536,7 +560,7 @@
         <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -544,7 +568,7 @@
         <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -552,23 +576,47 @@
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -787,15 +835,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -972,6 +1011,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -984,14 +1032,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1010,6 +1050,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>

--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M327220\Documents\GitHub\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D90F36-8E2C-4288-847D-676C78F48388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1795342-9D61-4B5C-AC79-CF499C716A88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="20910" windowHeight="9345" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
   <si>
     <t>Child</t>
   </si>
@@ -148,40 +148,13 @@
     <t>G000000873</t>
   </si>
   <si>
-    <t>DE20538353</t>
-  </si>
-  <si>
-    <t>DE10538353</t>
-  </si>
-  <si>
-    <t>DE10538602</t>
-  </si>
-  <si>
-    <t>DE10538603</t>
-  </si>
-  <si>
-    <t>DE10538604</t>
-  </si>
-  <si>
-    <t>DE20538602</t>
-  </si>
-  <si>
-    <t>DE20538603</t>
-  </si>
-  <si>
-    <t>DE20538604</t>
-  </si>
-  <si>
-    <t>G000000994</t>
-  </si>
-  <si>
-    <t>G000001084</t>
-  </si>
-  <si>
-    <t>G000001017</t>
-  </si>
-  <si>
-    <t>G000000943</t>
+    <t>DZ50GM1100</t>
+  </si>
+  <si>
+    <t>ZA50GM2100</t>
+  </si>
+  <si>
+    <t>2053OF0000</t>
   </si>
 </sst>
 </file>
@@ -539,7 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -560,7 +533,7 @@
         <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -568,7 +541,7 @@
         <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -576,47 +549,7 @@
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -835,6 +768,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -1011,15 +953,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1032,6 +965,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1050,14 +991,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>

--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M327220\Documents\GitHub\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1795342-9D61-4B5C-AC79-CF499C716A88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A73686F-2DDE-452C-B4F3-422945DFE8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="4260" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="61">
   <si>
     <t>Child</t>
   </si>
@@ -148,13 +148,88 @@
     <t>G000000873</t>
   </si>
   <si>
-    <t>DZ50GM1100</t>
-  </si>
-  <si>
-    <t>ZA50GM2100</t>
-  </si>
-  <si>
-    <t>2053OF0000</t>
+    <t>DE10N11700</t>
+  </si>
+  <si>
+    <t>DE10N11714</t>
+  </si>
+  <si>
+    <t>DE10N11716</t>
+  </si>
+  <si>
+    <t>DE10N11720</t>
+  </si>
+  <si>
+    <t>DE10N11722</t>
+  </si>
+  <si>
+    <t>DE10N11740</t>
+  </si>
+  <si>
+    <t>DE10N11750</t>
+  </si>
+  <si>
+    <t>DE10N11780</t>
+  </si>
+  <si>
+    <t>DE10N11800</t>
+  </si>
+  <si>
+    <t>DE10N11812</t>
+  </si>
+  <si>
+    <t>DE10N11813</t>
+  </si>
+  <si>
+    <t>DE10N11814</t>
+  </si>
+  <si>
+    <t>DE10N11816</t>
+  </si>
+  <si>
+    <t>DE10N11818</t>
+  </si>
+  <si>
+    <t>DE10N11820</t>
+  </si>
+  <si>
+    <t>DE10N11826</t>
+  </si>
+  <si>
+    <t>DE10N11830</t>
+  </si>
+  <si>
+    <t>DE10N11840</t>
+  </si>
+  <si>
+    <t>DE10N11850</t>
+  </si>
+  <si>
+    <t>DE10N11855</t>
+  </si>
+  <si>
+    <t>DE10N11860</t>
+  </si>
+  <si>
+    <t>DE10N11863</t>
+  </si>
+  <si>
+    <t>DE10N11864</t>
+  </si>
+  <si>
+    <t>DE10N11870</t>
+  </si>
+  <si>
+    <t>DE10N11880</t>
+  </si>
+  <si>
+    <t>DE10N11881</t>
+  </si>
+  <si>
+    <t>L000013834</t>
+  </si>
+  <si>
+    <t>L000013835</t>
   </si>
 </sst>
 </file>
@@ -512,7 +587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -533,7 +608,7 @@
         <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -541,7 +616,7 @@
         <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -549,7 +624,191 @@
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -777,6 +1036,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -953,17 +1223,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
   <ds:schemaRefs>
@@ -973,6 +1232,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
+    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -989,15 +1259,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
-    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M327220\Documents\GitHub\GCOHFilesTicketsEtc\GCOH Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A73686F-2DDE-452C-B4F3-422945DFE8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84834945-8150-476B-B7B5-CEB256BBFF0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4260" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -19,35 +19,24 @@
     <sheet name="Pierre to do" sheetId="8" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MDGF!$A$1:$D$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MDGF!$A$1:$D$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet1!$A$5:$B$5</definedName>
     <definedName name="ID" localSheetId="0" hidden="1">"a5f5822f-2145-4cc3-aa32-d164ed237772"</definedName>
     <definedName name="ID" localSheetId="3" hidden="1">"2b5e4bcf-a0bb-4962-aef7-0fa656cb902f"</definedName>
     <definedName name="ID" localSheetId="2" hidden="1">"fff7d4e2-cafa-4da0-a3ee-fa93757f1b68"</definedName>
     <definedName name="ID" localSheetId="1" hidden="1">"d59c0fca-ea81-453e-b1af-313ab178d2df"</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
   <si>
     <t>Child</t>
   </si>
@@ -148,88 +137,10 @@
     <t>G000000873</t>
   </si>
   <si>
-    <t>DE10N11700</t>
-  </si>
-  <si>
-    <t>DE10N11714</t>
-  </si>
-  <si>
-    <t>DE10N11716</t>
-  </si>
-  <si>
-    <t>DE10N11720</t>
-  </si>
-  <si>
-    <t>DE10N11722</t>
-  </si>
-  <si>
-    <t>DE10N11740</t>
-  </si>
-  <si>
-    <t>DE10N11750</t>
-  </si>
-  <si>
-    <t>DE10N11780</t>
-  </si>
-  <si>
-    <t>DE10N11800</t>
-  </si>
-  <si>
-    <t>DE10N11812</t>
-  </si>
-  <si>
-    <t>DE10N11813</t>
-  </si>
-  <si>
-    <t>DE10N11814</t>
-  </si>
-  <si>
-    <t>DE10N11816</t>
-  </si>
-  <si>
-    <t>DE10N11818</t>
-  </si>
-  <si>
-    <t>DE10N11820</t>
-  </si>
-  <si>
-    <t>DE10N11826</t>
-  </si>
-  <si>
-    <t>DE10N11830</t>
-  </si>
-  <si>
-    <t>DE10N11840</t>
-  </si>
-  <si>
-    <t>DE10N11850</t>
-  </si>
-  <si>
-    <t>DE10N11855</t>
-  </si>
-  <si>
-    <t>DE10N11860</t>
-  </si>
-  <si>
-    <t>DE10N11863</t>
-  </si>
-  <si>
-    <t>DE10N11864</t>
-  </si>
-  <si>
-    <t>DE10N11870</t>
-  </si>
-  <si>
-    <t>DE10N11880</t>
-  </si>
-  <si>
-    <t>DE10N11881</t>
-  </si>
-  <si>
-    <t>L000013834</t>
-  </si>
-  <si>
-    <t>L000013835</t>
+    <t>DE10B20210</t>
+  </si>
+  <si>
+    <t>L000013794</t>
   </si>
 </sst>
 </file>
@@ -291,9 +202,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -331,7 +242,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -437,7 +348,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -579,7 +490,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -587,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -608,207 +519,7 @@
         <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
         <v>34</v>
-      </c>
-      <c r="B3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>50</v>
-      </c>
-      <c r="B19" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>51</v>
-      </c>
-      <c r="B20" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>52</v>
-      </c>
-      <c r="B21" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>53</v>
-      </c>
-      <c r="B22" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>54</v>
-      </c>
-      <c r="B23" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>56</v>
-      </c>
-      <c r="B25" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>57</v>
-      </c>
-      <c r="B26" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>58</v>
-      </c>
-      <c r="B27" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1027,15 +738,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
@@ -1044,6 +746,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1224,20 +935,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
     <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M327220\Documents\GitHub\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84834945-8150-476B-B7B5-CEB256BBFF0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3A86E36-83C7-4206-A104-8CFC15F15F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -26,17 +26,28 @@
     <definedName name="ID" localSheetId="2" hidden="1">"fff7d4e2-cafa-4da0-a3ee-fa93757f1b68"</definedName>
     <definedName name="ID" localSheetId="1" hidden="1">"d59c0fca-ea81-453e-b1af-313ab178d2df"</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="41">
   <si>
     <t>Child</t>
   </si>
@@ -137,10 +148,28 @@
     <t>G000000873</t>
   </si>
   <si>
-    <t>DE10B20210</t>
-  </si>
-  <si>
-    <t>L000013794</t>
+    <t>2068TAUA00</t>
+  </si>
+  <si>
+    <t>2068TAUA99</t>
+  </si>
+  <si>
+    <t>2068TBUZ21</t>
+  </si>
+  <si>
+    <t>2068TFUZ61</t>
+  </si>
+  <si>
+    <t>2068TKUZ70</t>
+  </si>
+  <si>
+    <t>2068TQUZ90</t>
+  </si>
+  <si>
+    <t>2068TAUA01</t>
+  </si>
+  <si>
+    <t>L000013447</t>
   </si>
 </sst>
 </file>
@@ -202,9 +231,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -242,7 +271,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -348,7 +377,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -490,7 +519,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -498,7 +527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -519,7 +548,55 @@
         <v>33</v>
       </c>
       <c r="B2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>34</v>
+      </c>
+      <c r="B3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -749,15 +826,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -934,6 +1002,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>
@@ -946,14 +1023,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -970,4 +1039,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M327220\Documents\GitHub\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3A86E36-83C7-4206-A104-8CFC15F15F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF427BB-5306-40C7-B8CF-035A14046729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="3630" yWindow="2325" windowWidth="21600" windowHeight="11295" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="41">
   <si>
     <t>Child</t>
   </si>
@@ -148,28 +148,28 @@
     <t>G000000873</t>
   </si>
   <si>
-    <t>2068TAUA00</t>
-  </si>
-  <si>
-    <t>2068TAUA99</t>
-  </si>
-  <si>
-    <t>2068TBUZ21</t>
-  </si>
-  <si>
-    <t>2068TFUZ61</t>
-  </si>
-  <si>
-    <t>2068TKUZ70</t>
-  </si>
-  <si>
-    <t>2068TQUZ90</t>
-  </si>
-  <si>
-    <t>2068TAUA01</t>
-  </si>
-  <si>
-    <t>L000013447</t>
+    <t>DE10677800</t>
+  </si>
+  <si>
+    <t>DE65GIT032</t>
+  </si>
+  <si>
+    <t>ES50GIT40L</t>
+  </si>
+  <si>
+    <t>IT50GIT025</t>
+  </si>
+  <si>
+    <t>P000000763</t>
+  </si>
+  <si>
+    <t>G000000256</t>
+  </si>
+  <si>
+    <t>P000000765</t>
+  </si>
+  <si>
+    <t>G000000339</t>
   </si>
 </sst>
 </file>
@@ -527,7 +527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -548,7 +548,7 @@
         <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -556,7 +556,7 @@
         <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -564,7 +564,7 @@
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -572,30 +572,6 @@
         <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" t="s">
         <v>40</v>
       </c>
     </row>
@@ -815,14 +791,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1003,21 +977,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
-    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1042,9 +1015,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
+    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M327220\Documents\GitHub\GCOHFilesTicketsEtc\GCOH Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mdigital-my.sharepoint.com/personal/m327220_one_merckgroup_com/Documents/Documents/GitHub/GCOHFilesTicketsEtc/GCOH Resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF427BB-5306-40C7-B8CF-035A14046729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{3DF427BB-5306-40C7-B8CF-035A14046729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E42952FC-0A66-4BBF-8753-B06717C9974C}"/>
   <bookViews>
-    <workbookView xWindow="3630" yWindow="2325" windowWidth="21600" windowHeight="11295" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="380">
   <si>
     <t>Child</t>
   </si>
@@ -148,28 +148,1045 @@
     <t>G000000873</t>
   </si>
   <si>
-    <t>DE10677800</t>
-  </si>
-  <si>
-    <t>DE65GIT032</t>
-  </si>
-  <si>
-    <t>ES50GIT40L</t>
-  </si>
-  <si>
-    <t>IT50GIT025</t>
-  </si>
-  <si>
-    <t>P000000763</t>
-  </si>
-  <si>
-    <t>G000000256</t>
-  </si>
-  <si>
-    <t>P000000765</t>
-  </si>
-  <si>
-    <t>G000000339</t>
+    <t>DE20122000</t>
+  </si>
+  <si>
+    <t>DE20123000</t>
+  </si>
+  <si>
+    <t>DE10515800</t>
+  </si>
+  <si>
+    <t>DE10538021</t>
+  </si>
+  <si>
+    <t>DE10566000</t>
+  </si>
+  <si>
+    <t>DE10537833</t>
+  </si>
+  <si>
+    <t>DE10538012</t>
+  </si>
+  <si>
+    <t>DE10538014</t>
+  </si>
+  <si>
+    <t>DE10538015</t>
+  </si>
+  <si>
+    <t>DE10538017</t>
+  </si>
+  <si>
+    <t>DE10538018</t>
+  </si>
+  <si>
+    <t>DE10538132</t>
+  </si>
+  <si>
+    <t>DE10538101</t>
+  </si>
+  <si>
+    <t>DE10538102</t>
+  </si>
+  <si>
+    <t>DE10538104</t>
+  </si>
+  <si>
+    <t>DE10538109</t>
+  </si>
+  <si>
+    <t>DE10538116</t>
+  </si>
+  <si>
+    <t>DE10538123</t>
+  </si>
+  <si>
+    <t>DE10538128</t>
+  </si>
+  <si>
+    <t>DE10538146</t>
+  </si>
+  <si>
+    <t>DE10538150</t>
+  </si>
+  <si>
+    <t>DE10538152</t>
+  </si>
+  <si>
+    <t>DE10538157</t>
+  </si>
+  <si>
+    <t>DE10538158</t>
+  </si>
+  <si>
+    <t>DE10538159</t>
+  </si>
+  <si>
+    <t>DE10538179</t>
+  </si>
+  <si>
+    <t>DE10538180</t>
+  </si>
+  <si>
+    <t>DE10538181</t>
+  </si>
+  <si>
+    <t>DE10538182</t>
+  </si>
+  <si>
+    <t>DE10538183</t>
+  </si>
+  <si>
+    <t>DE10538187</t>
+  </si>
+  <si>
+    <t>DE10538188</t>
+  </si>
+  <si>
+    <t>DE10538189</t>
+  </si>
+  <si>
+    <t>DE10538196</t>
+  </si>
+  <si>
+    <t>DE10538236</t>
+  </si>
+  <si>
+    <t>DE10538470</t>
+  </si>
+  <si>
+    <t>DE10538472</t>
+  </si>
+  <si>
+    <t>DE10538473</t>
+  </si>
+  <si>
+    <t>DE10538762</t>
+  </si>
+  <si>
+    <t>DE10538961</t>
+  </si>
+  <si>
+    <t>DE10538962</t>
+  </si>
+  <si>
+    <t>DE10538963</t>
+  </si>
+  <si>
+    <t>DE10538964</t>
+  </si>
+  <si>
+    <t>DE10538965</t>
+  </si>
+  <si>
+    <t>DE10538966</t>
+  </si>
+  <si>
+    <t>DE10538967</t>
+  </si>
+  <si>
+    <t>DE10538968</t>
+  </si>
+  <si>
+    <t>DE10538969</t>
+  </si>
+  <si>
+    <t>DE10538970</t>
+  </si>
+  <si>
+    <t>DE10538971</t>
+  </si>
+  <si>
+    <t>DE10538972</t>
+  </si>
+  <si>
+    <t>DE10538973</t>
+  </si>
+  <si>
+    <t>DE10538974</t>
+  </si>
+  <si>
+    <t>DE10538975</t>
+  </si>
+  <si>
+    <t>DE10538977</t>
+  </si>
+  <si>
+    <t>DE10538979</t>
+  </si>
+  <si>
+    <t>DE10538980</t>
+  </si>
+  <si>
+    <t>DE10538982</t>
+  </si>
+  <si>
+    <t>DE10538984</t>
+  </si>
+  <si>
+    <t>DE10538985</t>
+  </si>
+  <si>
+    <t>DE10538994</t>
+  </si>
+  <si>
+    <t>DE10539930</t>
+  </si>
+  <si>
+    <t>DE10539931</t>
+  </si>
+  <si>
+    <t>DE10539932</t>
+  </si>
+  <si>
+    <t>DE10539934</t>
+  </si>
+  <si>
+    <t>DE10539935</t>
+  </si>
+  <si>
+    <t>DE10539936</t>
+  </si>
+  <si>
+    <t>DE10539937</t>
+  </si>
+  <si>
+    <t>DE10539938</t>
+  </si>
+  <si>
+    <t>DE10539939</t>
+  </si>
+  <si>
+    <t>DE10539940</t>
+  </si>
+  <si>
+    <t>DE10539941</t>
+  </si>
+  <si>
+    <t>DE10539942</t>
+  </si>
+  <si>
+    <t>DE10539943</t>
+  </si>
+  <si>
+    <t>DE10539944</t>
+  </si>
+  <si>
+    <t>DE10539995</t>
+  </si>
+  <si>
+    <t>DE10538103</t>
+  </si>
+  <si>
+    <t>DE10538108</t>
+  </si>
+  <si>
+    <t>DE10538110</t>
+  </si>
+  <si>
+    <t>DE10538111</t>
+  </si>
+  <si>
+    <t>DE10538112</t>
+  </si>
+  <si>
+    <t>DE10538113</t>
+  </si>
+  <si>
+    <t>DE10538114</t>
+  </si>
+  <si>
+    <t>DE10538115</t>
+  </si>
+  <si>
+    <t>DE10538117</t>
+  </si>
+  <si>
+    <t>DE10538119</t>
+  </si>
+  <si>
+    <t>DE10538120</t>
+  </si>
+  <si>
+    <t>DE10538121</t>
+  </si>
+  <si>
+    <t>DE10538122</t>
+  </si>
+  <si>
+    <t>DE10538124</t>
+  </si>
+  <si>
+    <t>DE10538129</t>
+  </si>
+  <si>
+    <t>DE10538130</t>
+  </si>
+  <si>
+    <t>DE10538131</t>
+  </si>
+  <si>
+    <t>DE10538133</t>
+  </si>
+  <si>
+    <t>DE10538134</t>
+  </si>
+  <si>
+    <t>DE10538135</t>
+  </si>
+  <si>
+    <t>DE10538138</t>
+  </si>
+  <si>
+    <t>DE10538139</t>
+  </si>
+  <si>
+    <t>DE10538142</t>
+  </si>
+  <si>
+    <t>DE10538144</t>
+  </si>
+  <si>
+    <t>DE10538161</t>
+  </si>
+  <si>
+    <t>DE10538174</t>
+  </si>
+  <si>
+    <t>DE10538178</t>
+  </si>
+  <si>
+    <t>DE10538192</t>
+  </si>
+  <si>
+    <t>DE10538397</t>
+  </si>
+  <si>
+    <t>DE10538556</t>
+  </si>
+  <si>
+    <t>DE10538654</t>
+  </si>
+  <si>
+    <t>DE10579990</t>
+  </si>
+  <si>
+    <t>DE10538107</t>
+  </si>
+  <si>
+    <t>DE10538118</t>
+  </si>
+  <si>
+    <t>DE10538136</t>
+  </si>
+  <si>
+    <t>DE10538137</t>
+  </si>
+  <si>
+    <t>DE10538141</t>
+  </si>
+  <si>
+    <t>DE10538143</t>
+  </si>
+  <si>
+    <t>DE10538147</t>
+  </si>
+  <si>
+    <t>DE10538148</t>
+  </si>
+  <si>
+    <t>DE10538151</t>
+  </si>
+  <si>
+    <t>DE10538153</t>
+  </si>
+  <si>
+    <t>DE10538160</t>
+  </si>
+  <si>
+    <t>DE10538162</t>
+  </si>
+  <si>
+    <t>DE10538163</t>
+  </si>
+  <si>
+    <t>DE10538164</t>
+  </si>
+  <si>
+    <t>DE10538166</t>
+  </si>
+  <si>
+    <t>DE10538167</t>
+  </si>
+  <si>
+    <t>DE10538168</t>
+  </si>
+  <si>
+    <t>DE10538171</t>
+  </si>
+  <si>
+    <t>DE10538175</t>
+  </si>
+  <si>
+    <t>DE10538176</t>
+  </si>
+  <si>
+    <t>DE10538177</t>
+  </si>
+  <si>
+    <t>DE10538184</t>
+  </si>
+  <si>
+    <t>DE10538185</t>
+  </si>
+  <si>
+    <t>DE10538186</t>
+  </si>
+  <si>
+    <t>DE10538193</t>
+  </si>
+  <si>
+    <t>DE10538194</t>
+  </si>
+  <si>
+    <t>DE10538195</t>
+  </si>
+  <si>
+    <t>DE10538197</t>
+  </si>
+  <si>
+    <t>DE10538712</t>
+  </si>
+  <si>
+    <t>DE10538713</t>
+  </si>
+  <si>
+    <t>DE10538714</t>
+  </si>
+  <si>
+    <t>DE10538715</t>
+  </si>
+  <si>
+    <t>DE10538716</t>
+  </si>
+  <si>
+    <t>DE10538717</t>
+  </si>
+  <si>
+    <t>DE10538887</t>
+  </si>
+  <si>
+    <t>DE10538920</t>
+  </si>
+  <si>
+    <t>DE10538921</t>
+  </si>
+  <si>
+    <t>DE10538978</t>
+  </si>
+  <si>
+    <t>DE10539001</t>
+  </si>
+  <si>
+    <t>DE10539002</t>
+  </si>
+  <si>
+    <t>DE10539004</t>
+  </si>
+  <si>
+    <t>DE10567500</t>
+  </si>
+  <si>
+    <t>DE10569401</t>
+  </si>
+  <si>
+    <t>DE10538145</t>
+  </si>
+  <si>
+    <t>DE10538190</t>
+  </si>
+  <si>
+    <t>DE10539003</t>
+  </si>
+  <si>
+    <t>DE10567400</t>
+  </si>
+  <si>
+    <t>DE20510800</t>
+  </si>
+  <si>
+    <t>DE20516800</t>
+  </si>
+  <si>
+    <t>DE20518800</t>
+  </si>
+  <si>
+    <t>DE20518900</t>
+  </si>
+  <si>
+    <t>DE20538199</t>
+  </si>
+  <si>
+    <t>DE20542000</t>
+  </si>
+  <si>
+    <t>DE20537833</t>
+  </si>
+  <si>
+    <t>DE20538012</t>
+  </si>
+  <si>
+    <t>DE20538014</t>
+  </si>
+  <si>
+    <t>DE20538015</t>
+  </si>
+  <si>
+    <t>DE20538017</t>
+  </si>
+  <si>
+    <t>DE20538018</t>
+  </si>
+  <si>
+    <t>DE20538132</t>
+  </si>
+  <si>
+    <t>DE20538101</t>
+  </si>
+  <si>
+    <t>DE20538102</t>
+  </si>
+  <si>
+    <t>DE20538104</t>
+  </si>
+  <si>
+    <t>DE20538109</t>
+  </si>
+  <si>
+    <t>DE20538116</t>
+  </si>
+  <si>
+    <t>DE20538123</t>
+  </si>
+  <si>
+    <t>DE20538128</t>
+  </si>
+  <si>
+    <t>DE20538146</t>
+  </si>
+  <si>
+    <t>DE20538150</t>
+  </si>
+  <si>
+    <t>DE20538152</t>
+  </si>
+  <si>
+    <t>DE20538157</t>
+  </si>
+  <si>
+    <t>DE20538158</t>
+  </si>
+  <si>
+    <t>DE20538159</t>
+  </si>
+  <si>
+    <t>DE20538179</t>
+  </si>
+  <si>
+    <t>DE20538180</t>
+  </si>
+  <si>
+    <t>DE20538181</t>
+  </si>
+  <si>
+    <t>DE20538182</t>
+  </si>
+  <si>
+    <t>DE20538183</t>
+  </si>
+  <si>
+    <t>DE20538187</t>
+  </si>
+  <si>
+    <t>DE20538188</t>
+  </si>
+  <si>
+    <t>DE20538189</t>
+  </si>
+  <si>
+    <t>DE20538196</t>
+  </si>
+  <si>
+    <t>DE20538236</t>
+  </si>
+  <si>
+    <t>DE20538470</t>
+  </si>
+  <si>
+    <t>DE20538472</t>
+  </si>
+  <si>
+    <t>DE20538473</t>
+  </si>
+  <si>
+    <t>DE20538762</t>
+  </si>
+  <si>
+    <t>DE20538961</t>
+  </si>
+  <si>
+    <t>DE20538962</t>
+  </si>
+  <si>
+    <t>DE20538963</t>
+  </si>
+  <si>
+    <t>DE20538964</t>
+  </si>
+  <si>
+    <t>DE20538965</t>
+  </si>
+  <si>
+    <t>DE20538966</t>
+  </si>
+  <si>
+    <t>DE20538967</t>
+  </si>
+  <si>
+    <t>DE20538968</t>
+  </si>
+  <si>
+    <t>DE20538969</t>
+  </si>
+  <si>
+    <t>DE20538970</t>
+  </si>
+  <si>
+    <t>DE20538971</t>
+  </si>
+  <si>
+    <t>DE20538972</t>
+  </si>
+  <si>
+    <t>DE20538973</t>
+  </si>
+  <si>
+    <t>DE20538974</t>
+  </si>
+  <si>
+    <t>DE20538975</t>
+  </si>
+  <si>
+    <t>DE20538977</t>
+  </si>
+  <si>
+    <t>DE20538979</t>
+  </si>
+  <si>
+    <t>DE20538980</t>
+  </si>
+  <si>
+    <t>DE20538982</t>
+  </si>
+  <si>
+    <t>DE20538984</t>
+  </si>
+  <si>
+    <t>DE20538985</t>
+  </si>
+  <si>
+    <t>DE20538994</t>
+  </si>
+  <si>
+    <t>DE20539930</t>
+  </si>
+  <si>
+    <t>DE20539931</t>
+  </si>
+  <si>
+    <t>DE20539932</t>
+  </si>
+  <si>
+    <t>DE20539934</t>
+  </si>
+  <si>
+    <t>DE20539935</t>
+  </si>
+  <si>
+    <t>DE20539936</t>
+  </si>
+  <si>
+    <t>DE20539937</t>
+  </si>
+  <si>
+    <t>DE20539938</t>
+  </si>
+  <si>
+    <t>DE20539939</t>
+  </si>
+  <si>
+    <t>DE20539940</t>
+  </si>
+  <si>
+    <t>DE20539941</t>
+  </si>
+  <si>
+    <t>DE20539942</t>
+  </si>
+  <si>
+    <t>DE20539943</t>
+  </si>
+  <si>
+    <t>DE20539944</t>
+  </si>
+  <si>
+    <t>DE20539995</t>
+  </si>
+  <si>
+    <t>DE20538103</t>
+  </si>
+  <si>
+    <t>DE20538108</t>
+  </si>
+  <si>
+    <t>DE20538110</t>
+  </si>
+  <si>
+    <t>DE20538111</t>
+  </si>
+  <si>
+    <t>DE20538112</t>
+  </si>
+  <si>
+    <t>DE20538113</t>
+  </si>
+  <si>
+    <t>DE20538114</t>
+  </si>
+  <si>
+    <t>DE20538115</t>
+  </si>
+  <si>
+    <t>DE20538117</t>
+  </si>
+  <si>
+    <t>DE20538119</t>
+  </si>
+  <si>
+    <t>DE20538120</t>
+  </si>
+  <si>
+    <t>DE20538121</t>
+  </si>
+  <si>
+    <t>DE20538122</t>
+  </si>
+  <si>
+    <t>DE20538124</t>
+  </si>
+  <si>
+    <t>DE20538129</t>
+  </si>
+  <si>
+    <t>DE20538130</t>
+  </si>
+  <si>
+    <t>DE20538131</t>
+  </si>
+  <si>
+    <t>DE20538133</t>
+  </si>
+  <si>
+    <t>DE20538134</t>
+  </si>
+  <si>
+    <t>DE20538135</t>
+  </si>
+  <si>
+    <t>DE20538138</t>
+  </si>
+  <si>
+    <t>DE20538139</t>
+  </si>
+  <si>
+    <t>DE20538142</t>
+  </si>
+  <si>
+    <t>DE20538144</t>
+  </si>
+  <si>
+    <t>DE20538161</t>
+  </si>
+  <si>
+    <t>DE20538174</t>
+  </si>
+  <si>
+    <t>DE20538178</t>
+  </si>
+  <si>
+    <t>DE20538192</t>
+  </si>
+  <si>
+    <t>DE20538397</t>
+  </si>
+  <si>
+    <t>DE20538556</t>
+  </si>
+  <si>
+    <t>DE20538654</t>
+  </si>
+  <si>
+    <t>DE20579990</t>
+  </si>
+  <si>
+    <t>DE20538107</t>
+  </si>
+  <si>
+    <t>DE20538118</t>
+  </si>
+  <si>
+    <t>DE20538136</t>
+  </si>
+  <si>
+    <t>DE20538137</t>
+  </si>
+  <si>
+    <t>DE20538141</t>
+  </si>
+  <si>
+    <t>DE20538143</t>
+  </si>
+  <si>
+    <t>DE20538147</t>
+  </si>
+  <si>
+    <t>DE20538148</t>
+  </si>
+  <si>
+    <t>DE20538151</t>
+  </si>
+  <si>
+    <t>DE20538153</t>
+  </si>
+  <si>
+    <t>DE20538160</t>
+  </si>
+  <si>
+    <t>DE20538162</t>
+  </si>
+  <si>
+    <t>DE20538163</t>
+  </si>
+  <si>
+    <t>DE20538164</t>
+  </si>
+  <si>
+    <t>DE20538166</t>
+  </si>
+  <si>
+    <t>DE20538167</t>
+  </si>
+  <si>
+    <t>DE20538168</t>
+  </si>
+  <si>
+    <t>DE20538171</t>
+  </si>
+  <si>
+    <t>DE20538175</t>
+  </si>
+  <si>
+    <t>DE20538176</t>
+  </si>
+  <si>
+    <t>DE20538177</t>
+  </si>
+  <si>
+    <t>DE20538184</t>
+  </si>
+  <si>
+    <t>DE20538185</t>
+  </si>
+  <si>
+    <t>DE20538186</t>
+  </si>
+  <si>
+    <t>DE20538193</t>
+  </si>
+  <si>
+    <t>DE20538194</t>
+  </si>
+  <si>
+    <t>DE20538195</t>
+  </si>
+  <si>
+    <t>DE20538197</t>
+  </si>
+  <si>
+    <t>DE20538712</t>
+  </si>
+  <si>
+    <t>DE20538713</t>
+  </si>
+  <si>
+    <t>DE20538714</t>
+  </si>
+  <si>
+    <t>DE20538715</t>
+  </si>
+  <si>
+    <t>DE20538716</t>
+  </si>
+  <si>
+    <t>DE20538717</t>
+  </si>
+  <si>
+    <t>DE20538887</t>
+  </si>
+  <si>
+    <t>DE20538920</t>
+  </si>
+  <si>
+    <t>DE20538921</t>
+  </si>
+  <si>
+    <t>DE20538978</t>
+  </si>
+  <si>
+    <t>DE20539001</t>
+  </si>
+  <si>
+    <t>DE20539002</t>
+  </si>
+  <si>
+    <t>DE20539004</t>
+  </si>
+  <si>
+    <t>DE20567500</t>
+  </si>
+  <si>
+    <t>DE20569401</t>
+  </si>
+  <si>
+    <t>DE20538145</t>
+  </si>
+  <si>
+    <t>DE20538190</t>
+  </si>
+  <si>
+    <t>DE20539003</t>
+  </si>
+  <si>
+    <t>DE20567400</t>
+  </si>
+  <si>
+    <t>DE50OF0154</t>
+  </si>
+  <si>
+    <t>DE10624416</t>
+  </si>
+  <si>
+    <t>CH65GCA008</t>
+  </si>
+  <si>
+    <t>CH65GCA010</t>
+  </si>
+  <si>
+    <t>CH65GCA001</t>
+  </si>
+  <si>
+    <t>DE50OF6808</t>
+  </si>
+  <si>
+    <t>DK50L93100</t>
+  </si>
+  <si>
+    <t>KR02GHR119</t>
+  </si>
+  <si>
+    <t>MA50GHR018</t>
+  </si>
+  <si>
+    <t>TN50GHR018</t>
+  </si>
+  <si>
+    <t>TN50GHR019</t>
+  </si>
+  <si>
+    <t>TN60GHR018</t>
+  </si>
+  <si>
+    <t>G000000400</t>
+  </si>
+  <si>
+    <t>G000000998</t>
+  </si>
+  <si>
+    <t>G000000997</t>
+  </si>
+  <si>
+    <t>G000000996</t>
+  </si>
+  <si>
+    <t>G000000880</t>
+  </si>
+  <si>
+    <t>G000000915</t>
+  </si>
+  <si>
+    <t>G000000872</t>
+  </si>
+  <si>
+    <t>G000000993</t>
+  </si>
+  <si>
+    <t>G000000950</t>
+  </si>
+  <si>
+    <t>G000000888</t>
+  </si>
+  <si>
+    <t>G000000879</t>
+  </si>
+  <si>
+    <t>G000000514</t>
+  </si>
+  <si>
+    <t>G000000513</t>
+  </si>
+  <si>
+    <t>G000000468</t>
+  </si>
+  <si>
+    <t>G000000417</t>
+  </si>
+  <si>
+    <t>G000000512</t>
+  </si>
+  <si>
+    <t>G000000511</t>
+  </si>
+  <si>
+    <t>G000000467</t>
+  </si>
+  <si>
+    <t>H000004394</t>
+  </si>
+  <si>
+    <t>G000001227</t>
+  </si>
+  <si>
+    <t>G000000119</t>
+  </si>
+  <si>
+    <t>P000000188</t>
+  </si>
+  <si>
+    <t>P000000333</t>
+  </si>
+  <si>
+    <t>L000013447</t>
   </si>
 </sst>
 </file>
@@ -527,7 +1544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B330"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -548,7 +1565,7 @@
         <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -556,7 +1573,7 @@
         <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -564,7 +1581,7 @@
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -572,7 +1589,2607 @@
         <v>36</v>
       </c>
       <c r="B5" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>40</v>
+      </c>
+      <c r="B9" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>59</v>
+      </c>
+      <c r="B28" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>66</v>
+      </c>
+      <c r="B35" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>67</v>
+      </c>
+      <c r="B36" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>68</v>
+      </c>
+      <c r="B37" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>69</v>
+      </c>
+      <c r="B38" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>70</v>
+      </c>
+      <c r="B39" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>71</v>
+      </c>
+      <c r="B40" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>72</v>
+      </c>
+      <c r="B41" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>73</v>
+      </c>
+      <c r="B42" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>74</v>
+      </c>
+      <c r="B43" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>75</v>
+      </c>
+      <c r="B44" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>76</v>
+      </c>
+      <c r="B45" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>77</v>
+      </c>
+      <c r="B46" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>78</v>
+      </c>
+      <c r="B47" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>79</v>
+      </c>
+      <c r="B48" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B49" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>81</v>
+      </c>
+      <c r="B50" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>82</v>
+      </c>
+      <c r="B51" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>83</v>
+      </c>
+      <c r="B52" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>84</v>
+      </c>
+      <c r="B53" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>85</v>
+      </c>
+      <c r="B54" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>86</v>
+      </c>
+      <c r="B55" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>87</v>
+      </c>
+      <c r="B56" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>88</v>
+      </c>
+      <c r="B57" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>89</v>
+      </c>
+      <c r="B58" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>90</v>
+      </c>
+      <c r="B59" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>91</v>
+      </c>
+      <c r="B60" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>92</v>
+      </c>
+      <c r="B61" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>93</v>
+      </c>
+      <c r="B62" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>94</v>
+      </c>
+      <c r="B63" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>95</v>
+      </c>
+      <c r="B64" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>96</v>
+      </c>
+      <c r="B65" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>97</v>
+      </c>
+      <c r="B66" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>98</v>
+      </c>
+      <c r="B67" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>99</v>
+      </c>
+      <c r="B68" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>100</v>
+      </c>
+      <c r="B69" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>101</v>
+      </c>
+      <c r="B70" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>102</v>
+      </c>
+      <c r="B71" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>103</v>
+      </c>
+      <c r="B72" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>104</v>
+      </c>
+      <c r="B73" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>105</v>
+      </c>
+      <c r="B74" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>106</v>
+      </c>
+      <c r="B75" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>107</v>
+      </c>
+      <c r="B76" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>108</v>
+      </c>
+      <c r="B77" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>109</v>
+      </c>
+      <c r="B78" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>110</v>
+      </c>
+      <c r="B79" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>111</v>
+      </c>
+      <c r="B80" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>112</v>
+      </c>
+      <c r="B81" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>113</v>
+      </c>
+      <c r="B82" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>114</v>
+      </c>
+      <c r="B83" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>115</v>
+      </c>
+      <c r="B84" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>116</v>
+      </c>
+      <c r="B85" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>117</v>
+      </c>
+      <c r="B86" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>118</v>
+      </c>
+      <c r="B87" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>119</v>
+      </c>
+      <c r="B88" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>120</v>
+      </c>
+      <c r="B89" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>121</v>
+      </c>
+      <c r="B90" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>122</v>
+      </c>
+      <c r="B91" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>123</v>
+      </c>
+      <c r="B92" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>124</v>
+      </c>
+      <c r="B93" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>125</v>
+      </c>
+      <c r="B94" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>126</v>
+      </c>
+      <c r="B95" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>127</v>
+      </c>
+      <c r="B96" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>128</v>
+      </c>
+      <c r="B97" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>129</v>
+      </c>
+      <c r="B98" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>130</v>
+      </c>
+      <c r="B99" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>131</v>
+      </c>
+      <c r="B100" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>132</v>
+      </c>
+      <c r="B101" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>133</v>
+      </c>
+      <c r="B102" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>134</v>
+      </c>
+      <c r="B103" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>135</v>
+      </c>
+      <c r="B104" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>136</v>
+      </c>
+      <c r="B105" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>137</v>
+      </c>
+      <c r="B106" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>138</v>
+      </c>
+      <c r="B107" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>139</v>
+      </c>
+      <c r="B108" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>140</v>
+      </c>
+      <c r="B109" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>141</v>
+      </c>
+      <c r="B110" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>142</v>
+      </c>
+      <c r="B111" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>143</v>
+      </c>
+      <c r="B112" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>144</v>
+      </c>
+      <c r="B113" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>145</v>
+      </c>
+      <c r="B114" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>146</v>
+      </c>
+      <c r="B115" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>147</v>
+      </c>
+      <c r="B116" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>148</v>
+      </c>
+      <c r="B117" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>149</v>
+      </c>
+      <c r="B118" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>150</v>
+      </c>
+      <c r="B119" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>151</v>
+      </c>
+      <c r="B120" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>152</v>
+      </c>
+      <c r="B121" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>153</v>
+      </c>
+      <c r="B122" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>154</v>
+      </c>
+      <c r="B123" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>155</v>
+      </c>
+      <c r="B124" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>156</v>
+      </c>
+      <c r="B125" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>157</v>
+      </c>
+      <c r="B126" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>158</v>
+      </c>
+      <c r="B127" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>159</v>
+      </c>
+      <c r="B128" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>160</v>
+      </c>
+      <c r="B129" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>161</v>
+      </c>
+      <c r="B130" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>162</v>
+      </c>
+      <c r="B131" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>163</v>
+      </c>
+      <c r="B132" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>164</v>
+      </c>
+      <c r="B133" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>165</v>
+      </c>
+      <c r="B134" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>166</v>
+      </c>
+      <c r="B135" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>167</v>
+      </c>
+      <c r="B136" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>168</v>
+      </c>
+      <c r="B137" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>169</v>
+      </c>
+      <c r="B138" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>170</v>
+      </c>
+      <c r="B139" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>171</v>
+      </c>
+      <c r="B140" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>172</v>
+      </c>
+      <c r="B141" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>173</v>
+      </c>
+      <c r="B142" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>174</v>
+      </c>
+      <c r="B143" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>175</v>
+      </c>
+      <c r="B144" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>176</v>
+      </c>
+      <c r="B145" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>177</v>
+      </c>
+      <c r="B146" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>178</v>
+      </c>
+      <c r="B147" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>179</v>
+      </c>
+      <c r="B148" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>180</v>
+      </c>
+      <c r="B149" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>181</v>
+      </c>
+      <c r="B150" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>182</v>
+      </c>
+      <c r="B151" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>183</v>
+      </c>
+      <c r="B152" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>184</v>
+      </c>
+      <c r="B153" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>185</v>
+      </c>
+      <c r="B154" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>186</v>
+      </c>
+      <c r="B155" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>187</v>
+      </c>
+      <c r="B156" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>188</v>
+      </c>
+      <c r="B157" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>189</v>
+      </c>
+      <c r="B158" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>190</v>
+      </c>
+      <c r="B159" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>191</v>
+      </c>
+      <c r="B160" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>192</v>
+      </c>
+      <c r="B161" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>193</v>
+      </c>
+      <c r="B162" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>194</v>
+      </c>
+      <c r="B163" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>195</v>
+      </c>
+      <c r="B164" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>196</v>
+      </c>
+      <c r="B165" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>197</v>
+      </c>
+      <c r="B166" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>198</v>
+      </c>
+      <c r="B167" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>199</v>
+      </c>
+      <c r="B168" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>200</v>
+      </c>
+      <c r="B169" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>201</v>
+      </c>
+      <c r="B170" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>202</v>
+      </c>
+      <c r="B171" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>203</v>
+      </c>
+      <c r="B172" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>204</v>
+      </c>
+      <c r="B173" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>205</v>
+      </c>
+      <c r="B174" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>206</v>
+      </c>
+      <c r="B175" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>207</v>
+      </c>
+      <c r="B176" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>208</v>
+      </c>
+      <c r="B177" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>209</v>
+      </c>
+      <c r="B178" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>210</v>
+      </c>
+      <c r="B179" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>211</v>
+      </c>
+      <c r="B180" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>212</v>
+      </c>
+      <c r="B181" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>213</v>
+      </c>
+      <c r="B182" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>214</v>
+      </c>
+      <c r="B183" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>215</v>
+      </c>
+      <c r="B184" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>216</v>
+      </c>
+      <c r="B185" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>217</v>
+      </c>
+      <c r="B186" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>218</v>
+      </c>
+      <c r="B187" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>219</v>
+      </c>
+      <c r="B188" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>220</v>
+      </c>
+      <c r="B189" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>221</v>
+      </c>
+      <c r="B190" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>222</v>
+      </c>
+      <c r="B191" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>223</v>
+      </c>
+      <c r="B192" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>224</v>
+      </c>
+      <c r="B193" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>225</v>
+      </c>
+      <c r="B194" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>226</v>
+      </c>
+      <c r="B195" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>227</v>
+      </c>
+      <c r="B196" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>228</v>
+      </c>
+      <c r="B197" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>229</v>
+      </c>
+      <c r="B198" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>230</v>
+      </c>
+      <c r="B199" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>231</v>
+      </c>
+      <c r="B200" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>232</v>
+      </c>
+      <c r="B201" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>233</v>
+      </c>
+      <c r="B202" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>234</v>
+      </c>
+      <c r="B203" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>235</v>
+      </c>
+      <c r="B204" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>236</v>
+      </c>
+      <c r="B205" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>237</v>
+      </c>
+      <c r="B206" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>238</v>
+      </c>
+      <c r="B207" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>239</v>
+      </c>
+      <c r="B208" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>240</v>
+      </c>
+      <c r="B209" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>241</v>
+      </c>
+      <c r="B210" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>242</v>
+      </c>
+      <c r="B211" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>243</v>
+      </c>
+      <c r="B212" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>244</v>
+      </c>
+      <c r="B213" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>245</v>
+      </c>
+      <c r="B214" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>246</v>
+      </c>
+      <c r="B215" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>247</v>
+      </c>
+      <c r="B216" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>248</v>
+      </c>
+      <c r="B217" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>249</v>
+      </c>
+      <c r="B218" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>250</v>
+      </c>
+      <c r="B219" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>251</v>
+      </c>
+      <c r="B220" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>252</v>
+      </c>
+      <c r="B221" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>253</v>
+      </c>
+      <c r="B222" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>254</v>
+      </c>
+      <c r="B223" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>255</v>
+      </c>
+      <c r="B224" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>256</v>
+      </c>
+      <c r="B225" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>257</v>
+      </c>
+      <c r="B226" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>258</v>
+      </c>
+      <c r="B227" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>259</v>
+      </c>
+      <c r="B228" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>260</v>
+      </c>
+      <c r="B229" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>261</v>
+      </c>
+      <c r="B230" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>262</v>
+      </c>
+      <c r="B231" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>263</v>
+      </c>
+      <c r="B232" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>264</v>
+      </c>
+      <c r="B233" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>265</v>
+      </c>
+      <c r="B234" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>266</v>
+      </c>
+      <c r="B235" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>267</v>
+      </c>
+      <c r="B236" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>268</v>
+      </c>
+      <c r="B237" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>269</v>
+      </c>
+      <c r="B238" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>270</v>
+      </c>
+      <c r="B239" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>271</v>
+      </c>
+      <c r="B240" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>272</v>
+      </c>
+      <c r="B241" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>273</v>
+      </c>
+      <c r="B242" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>274</v>
+      </c>
+      <c r="B243" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>275</v>
+      </c>
+      <c r="B244" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>276</v>
+      </c>
+      <c r="B245" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>277</v>
+      </c>
+      <c r="B246" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>278</v>
+      </c>
+      <c r="B247" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>279</v>
+      </c>
+      <c r="B248" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>280</v>
+      </c>
+      <c r="B249" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>281</v>
+      </c>
+      <c r="B250" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>282</v>
+      </c>
+      <c r="B251" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>283</v>
+      </c>
+      <c r="B252" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>284</v>
+      </c>
+      <c r="B253" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>285</v>
+      </c>
+      <c r="B254" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>286</v>
+      </c>
+      <c r="B255" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>287</v>
+      </c>
+      <c r="B256" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>288</v>
+      </c>
+      <c r="B257" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>289</v>
+      </c>
+      <c r="B258" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>290</v>
+      </c>
+      <c r="B259" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>291</v>
+      </c>
+      <c r="B260" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>292</v>
+      </c>
+      <c r="B261" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>293</v>
+      </c>
+      <c r="B262" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>294</v>
+      </c>
+      <c r="B263" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>295</v>
+      </c>
+      <c r="B264" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>296</v>
+      </c>
+      <c r="B265" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>297</v>
+      </c>
+      <c r="B266" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>298</v>
+      </c>
+      <c r="B267" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>299</v>
+      </c>
+      <c r="B268" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>300</v>
+      </c>
+      <c r="B269" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>301</v>
+      </c>
+      <c r="B270" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>302</v>
+      </c>
+      <c r="B271" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>303</v>
+      </c>
+      <c r="B272" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>304</v>
+      </c>
+      <c r="B273" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>305</v>
+      </c>
+      <c r="B274" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>306</v>
+      </c>
+      <c r="B275" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>307</v>
+      </c>
+      <c r="B276" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>308</v>
+      </c>
+      <c r="B277" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>309</v>
+      </c>
+      <c r="B278" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>310</v>
+      </c>
+      <c r="B279" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>311</v>
+      </c>
+      <c r="B280" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>312</v>
+      </c>
+      <c r="B281" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>313</v>
+      </c>
+      <c r="B282" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>314</v>
+      </c>
+      <c r="B283" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>315</v>
+      </c>
+      <c r="B284" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>316</v>
+      </c>
+      <c r="B285" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>317</v>
+      </c>
+      <c r="B286" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>318</v>
+      </c>
+      <c r="B287" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>319</v>
+      </c>
+      <c r="B288" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>320</v>
+      </c>
+      <c r="B289" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>321</v>
+      </c>
+      <c r="B290" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>322</v>
+      </c>
+      <c r="B291" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>323</v>
+      </c>
+      <c r="B292" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>324</v>
+      </c>
+      <c r="B293" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>325</v>
+      </c>
+      <c r="B294" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>326</v>
+      </c>
+      <c r="B295" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>327</v>
+      </c>
+      <c r="B296" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>328</v>
+      </c>
+      <c r="B297" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>329</v>
+      </c>
+      <c r="B298" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>330</v>
+      </c>
+      <c r="B299" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>331</v>
+      </c>
+      <c r="B300" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>332</v>
+      </c>
+      <c r="B301" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>333</v>
+      </c>
+      <c r="B302" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>334</v>
+      </c>
+      <c r="B303" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>335</v>
+      </c>
+      <c r="B304" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>336</v>
+      </c>
+      <c r="B305" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>337</v>
+      </c>
+      <c r="B306" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>338</v>
+      </c>
+      <c r="B307" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>339</v>
+      </c>
+      <c r="B308" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>340</v>
+      </c>
+      <c r="B309" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>341</v>
+      </c>
+      <c r="B310" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>342</v>
+      </c>
+      <c r="B311" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>343</v>
+      </c>
+      <c r="B312" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>344</v>
+      </c>
+      <c r="B313" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>345</v>
+      </c>
+      <c r="B314" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>346</v>
+      </c>
+      <c r="B315" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>347</v>
+      </c>
+      <c r="B316" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>348</v>
+      </c>
+      <c r="B317" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>349</v>
+      </c>
+      <c r="B318" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>9</v>
+      </c>
+      <c r="B319" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>350</v>
+      </c>
+      <c r="B320" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>8</v>
+      </c>
+      <c r="B321" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>351</v>
+      </c>
+      <c r="B322" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>352</v>
+      </c>
+      <c r="B323" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>5</v>
+      </c>
+      <c r="B324" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>7</v>
+      </c>
+      <c r="B325" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>353</v>
+      </c>
+      <c r="B326" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>354</v>
+      </c>
+      <c r="B327" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>355</v>
+      </c>
+      <c r="B328" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>377</v>
+      </c>
+      <c r="B329" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>378</v>
+      </c>
+      <c r="B330" t="s">
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -800,6 +4417,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -976,17 +4604,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
   <ds:schemaRefs>
@@ -996,6 +4613,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
+    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1012,15 +4640,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
-    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M327220\OneDrive - MerckGroup\Documents\GitHub\GCOHFilesTicketsEtc\GCOH Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mdigital-my.sharepoint.com/personal/m327220_one_merckgroup_com/Documents/Documents/GitHub/GCOHFilesTicketsEtc/GCOH Resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB4027B1-B87F-49AC-97F5-F33E1EA49957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{AB4027B1-B87F-49AC-97F5-F33E1EA49957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A095E99-C2EF-4AAC-A40B-50A805FAE186}"/>
   <bookViews>
-    <workbookView xWindow="2595" yWindow="2595" windowWidth="21600" windowHeight="11295" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="170">
   <si>
     <t>Child</t>
   </si>
@@ -151,322 +151,412 @@
     <t>G000000872</t>
   </si>
   <si>
-    <t>G000000993</t>
-  </si>
-  <si>
-    <t>DE10538161</t>
-  </si>
-  <si>
-    <t>DE10538174</t>
-  </si>
-  <si>
-    <t>DE10538178</t>
-  </si>
-  <si>
-    <t>DE10538192</t>
-  </si>
-  <si>
-    <t>DE10538397</t>
-  </si>
-  <si>
-    <t>DE10538556</t>
-  </si>
-  <si>
-    <t>DE10538654</t>
-  </si>
-  <si>
-    <t>DE10579990</t>
-  </si>
-  <si>
-    <t>DE10538107</t>
-  </si>
-  <si>
-    <t>DE10538118</t>
-  </si>
-  <si>
-    <t>DE10538136</t>
-  </si>
-  <si>
-    <t>DE10538137</t>
-  </si>
-  <si>
-    <t>DE10538141</t>
-  </si>
-  <si>
-    <t>DE10538143</t>
-  </si>
-  <si>
-    <t>DE10538147</t>
-  </si>
-  <si>
-    <t>DE10538148</t>
-  </si>
-  <si>
-    <t>DE10538151</t>
-  </si>
-  <si>
-    <t>DE10538153</t>
-  </si>
-  <si>
-    <t>DE10538160</t>
-  </si>
-  <si>
-    <t>DE10538162</t>
-  </si>
-  <si>
-    <t>DE10538163</t>
-  </si>
-  <si>
-    <t>DE10538164</t>
-  </si>
-  <si>
-    <t>DE10538166</t>
-  </si>
-  <si>
-    <t>DE10538167</t>
-  </si>
-  <si>
-    <t>DE10538168</t>
-  </si>
-  <si>
-    <t>DE10538171</t>
-  </si>
-  <si>
-    <t>DE10538175</t>
-  </si>
-  <si>
-    <t>DE10538176</t>
-  </si>
-  <si>
-    <t>DE10538177</t>
-  </si>
-  <si>
-    <t>DE10538184</t>
-  </si>
-  <si>
-    <t>DE10538185</t>
-  </si>
-  <si>
-    <t>DE10538186</t>
-  </si>
-  <si>
-    <t>DE10538193</t>
-  </si>
-  <si>
-    <t>DE10538194</t>
-  </si>
-  <si>
-    <t>DE10538195</t>
-  </si>
-  <si>
-    <t>DE10538197</t>
-  </si>
-  <si>
-    <t>DE10538712</t>
-  </si>
-  <si>
-    <t>DE10538713</t>
-  </si>
-  <si>
-    <t>DE10538714</t>
-  </si>
-  <si>
-    <t>DE10538715</t>
-  </si>
-  <si>
-    <t>DE10538716</t>
-  </si>
-  <si>
-    <t>DE10538717</t>
-  </si>
-  <si>
-    <t>DE10538887</t>
-  </si>
-  <si>
-    <t>DE10538920</t>
-  </si>
-  <si>
-    <t>DE10538921</t>
-  </si>
-  <si>
-    <t>DE10538978</t>
-  </si>
-  <si>
-    <t>DE10539001</t>
-  </si>
-  <si>
-    <t>DE10539002</t>
-  </si>
-  <si>
-    <t>DE10539004</t>
-  </si>
-  <si>
-    <t>DE10567500</t>
-  </si>
-  <si>
-    <t>DE10569401</t>
-  </si>
-  <si>
-    <t>DE10538145</t>
-  </si>
-  <si>
-    <t>DE10538190</t>
-  </si>
-  <si>
-    <t>DE10539003</t>
-  </si>
-  <si>
-    <t>DE10567400</t>
-  </si>
-  <si>
-    <t>DE20510800</t>
-  </si>
-  <si>
-    <t>DE20516800</t>
-  </si>
-  <si>
-    <t>DE20518800</t>
-  </si>
-  <si>
-    <t>DE20518900</t>
-  </si>
-  <si>
-    <t>DE20538199</t>
-  </si>
-  <si>
-    <t>DE20542000</t>
-  </si>
-  <si>
-    <t>DE20537833</t>
-  </si>
-  <si>
-    <t>DE20538012</t>
-  </si>
-  <si>
-    <t>DE20538014</t>
-  </si>
-  <si>
-    <t>DE20538015</t>
-  </si>
-  <si>
-    <t>DE20538017</t>
-  </si>
-  <si>
-    <t>DE20538018</t>
-  </si>
-  <si>
-    <t>DE20538132</t>
-  </si>
-  <si>
-    <t>DE20538101</t>
-  </si>
-  <si>
-    <t>DE20538102</t>
-  </si>
-  <si>
-    <t>DE20538104</t>
-  </si>
-  <si>
-    <t>DE20538109</t>
-  </si>
-  <si>
-    <t>DE20538116</t>
-  </si>
-  <si>
-    <t>DE20538123</t>
-  </si>
-  <si>
-    <t>DE20538128</t>
-  </si>
-  <si>
-    <t>DE20538146</t>
-  </si>
-  <si>
-    <t>DE20538150</t>
-  </si>
-  <si>
-    <t>DE20538152</t>
-  </si>
-  <si>
-    <t>DE20538157</t>
-  </si>
-  <si>
-    <t>DE20538158</t>
-  </si>
-  <si>
-    <t>DE20538159</t>
-  </si>
-  <si>
-    <t>DE20538179</t>
-  </si>
-  <si>
-    <t>DE20538180</t>
-  </si>
-  <si>
-    <t>DE20538181</t>
-  </si>
-  <si>
-    <t>DE20538182</t>
-  </si>
-  <si>
-    <t>DE20538183</t>
-  </si>
-  <si>
-    <t>DE20538187</t>
-  </si>
-  <si>
-    <t>DE20538188</t>
-  </si>
-  <si>
-    <t>DE20538189</t>
-  </si>
-  <si>
-    <t>DE20538196</t>
-  </si>
-  <si>
-    <t>DE20538236</t>
-  </si>
-  <si>
-    <t>DE20538470</t>
-  </si>
-  <si>
-    <t>DE20538472</t>
-  </si>
-  <si>
-    <t>DE20538473</t>
-  </si>
-  <si>
-    <t>DE20538762</t>
-  </si>
-  <si>
-    <t>DE20538961</t>
-  </si>
-  <si>
-    <t>DE20538962</t>
-  </si>
-  <si>
-    <t>DE20538963</t>
-  </si>
-  <si>
-    <t>DE20538964</t>
-  </si>
-  <si>
-    <t>DE20538965</t>
-  </si>
-  <si>
-    <t>G000000888</t>
-  </si>
-  <si>
     <t>G000000879</t>
   </si>
   <si>
-    <t>G000000514</t>
-  </si>
-  <si>
     <t>G000000513</t>
   </si>
   <si>
     <t>G000000468</t>
+  </si>
+  <si>
+    <t>DE20538966</t>
+  </si>
+  <si>
+    <t>DE20538967</t>
+  </si>
+  <si>
+    <t>DE20538968</t>
+  </si>
+  <si>
+    <t>DE20538969</t>
+  </si>
+  <si>
+    <t>DE20538970</t>
+  </si>
+  <si>
+    <t>DE20538971</t>
+  </si>
+  <si>
+    <t>DE20538972</t>
+  </si>
+  <si>
+    <t>DE20538973</t>
+  </si>
+  <si>
+    <t>DE20538974</t>
+  </si>
+  <si>
+    <t>DE20538975</t>
+  </si>
+  <si>
+    <t>DE20538977</t>
+  </si>
+  <si>
+    <t>DE20538979</t>
+  </si>
+  <si>
+    <t>DE20538980</t>
+  </si>
+  <si>
+    <t>DE20538982</t>
+  </si>
+  <si>
+    <t>DE20538984</t>
+  </si>
+  <si>
+    <t>DE20538985</t>
+  </si>
+  <si>
+    <t>DE20538994</t>
+  </si>
+  <si>
+    <t>DE20539930</t>
+  </si>
+  <si>
+    <t>DE20539931</t>
+  </si>
+  <si>
+    <t>DE20539932</t>
+  </si>
+  <si>
+    <t>DE20539934</t>
+  </si>
+  <si>
+    <t>DE20539935</t>
+  </si>
+  <si>
+    <t>DE20539936</t>
+  </si>
+  <si>
+    <t>DE20539937</t>
+  </si>
+  <si>
+    <t>DE20539938</t>
+  </si>
+  <si>
+    <t>DE20539939</t>
+  </si>
+  <si>
+    <t>DE20539940</t>
+  </si>
+  <si>
+    <t>DE20539941</t>
+  </si>
+  <si>
+    <t>DE20539942</t>
+  </si>
+  <si>
+    <t>DE20539943</t>
+  </si>
+  <si>
+    <t>DE20539944</t>
+  </si>
+  <si>
+    <t>DE20539995</t>
+  </si>
+  <si>
+    <t>DE20538103</t>
+  </si>
+  <si>
+    <t>DE20538108</t>
+  </si>
+  <si>
+    <t>DE20538110</t>
+  </si>
+  <si>
+    <t>DE20538111</t>
+  </si>
+  <si>
+    <t>DE20538112</t>
+  </si>
+  <si>
+    <t>DE20538113</t>
+  </si>
+  <si>
+    <t>DE20538114</t>
+  </si>
+  <si>
+    <t>DE20538115</t>
+  </si>
+  <si>
+    <t>DE20538117</t>
+  </si>
+  <si>
+    <t>DE20538119</t>
+  </si>
+  <si>
+    <t>DE20538120</t>
+  </si>
+  <si>
+    <t>DE20538121</t>
+  </si>
+  <si>
+    <t>DE20538122</t>
+  </si>
+  <si>
+    <t>DE20538124</t>
+  </si>
+  <si>
+    <t>DE20538129</t>
+  </si>
+  <si>
+    <t>DE20538130</t>
+  </si>
+  <si>
+    <t>DE20538131</t>
+  </si>
+  <si>
+    <t>DE20538133</t>
+  </si>
+  <si>
+    <t>DE20538134</t>
+  </si>
+  <si>
+    <t>DE20538135</t>
+  </si>
+  <si>
+    <t>DE20538138</t>
+  </si>
+  <si>
+    <t>DE20538139</t>
+  </si>
+  <si>
+    <t>DE20538142</t>
+  </si>
+  <si>
+    <t>DE20538144</t>
+  </si>
+  <si>
+    <t>DE20538161</t>
+  </si>
+  <si>
+    <t>DE20538174</t>
+  </si>
+  <si>
+    <t>DE20538178</t>
+  </si>
+  <si>
+    <t>DE20538192</t>
+  </si>
+  <si>
+    <t>DE20538397</t>
+  </si>
+  <si>
+    <t>DE20538556</t>
+  </si>
+  <si>
+    <t>DE20538654</t>
+  </si>
+  <si>
+    <t>DE20579990</t>
+  </si>
+  <si>
+    <t>DE20538107</t>
+  </si>
+  <si>
+    <t>DE20538118</t>
+  </si>
+  <si>
+    <t>DE20538136</t>
+  </si>
+  <si>
+    <t>DE20538137</t>
+  </si>
+  <si>
+    <t>DE20538141</t>
+  </si>
+  <si>
+    <t>DE20538143</t>
+  </si>
+  <si>
+    <t>DE20538147</t>
+  </si>
+  <si>
+    <t>DE20538148</t>
+  </si>
+  <si>
+    <t>DE20538151</t>
+  </si>
+  <si>
+    <t>DE20538153</t>
+  </si>
+  <si>
+    <t>DE20538160</t>
+  </si>
+  <si>
+    <t>DE20538162</t>
+  </si>
+  <si>
+    <t>DE20538163</t>
+  </si>
+  <si>
+    <t>DE20538164</t>
+  </si>
+  <si>
+    <t>DE20538166</t>
+  </si>
+  <si>
+    <t>DE20538167</t>
+  </si>
+  <si>
+    <t>DE20538168</t>
+  </si>
+  <si>
+    <t>DE20538171</t>
+  </si>
+  <si>
+    <t>DE20538175</t>
+  </si>
+  <si>
+    <t>DE20538176</t>
+  </si>
+  <si>
+    <t>DE20538177</t>
+  </si>
+  <si>
+    <t>DE20538184</t>
+  </si>
+  <si>
+    <t>DE20538185</t>
+  </si>
+  <si>
+    <t>DE20538186</t>
+  </si>
+  <si>
+    <t>DE20538193</t>
+  </si>
+  <si>
+    <t>DE20538194</t>
+  </si>
+  <si>
+    <t>DE20538195</t>
+  </si>
+  <si>
+    <t>DE20538197</t>
+  </si>
+  <si>
+    <t>DE20538712</t>
+  </si>
+  <si>
+    <t>DE20538713</t>
+  </si>
+  <si>
+    <t>DE20538714</t>
+  </si>
+  <si>
+    <t>DE20538715</t>
+  </si>
+  <si>
+    <t>DE20538716</t>
+  </si>
+  <si>
+    <t>DE20538717</t>
+  </si>
+  <si>
+    <t>DE20538887</t>
+  </si>
+  <si>
+    <t>DE20538920</t>
+  </si>
+  <si>
+    <t>DE20538921</t>
+  </si>
+  <si>
+    <t>DE20538978</t>
+  </si>
+  <si>
+    <t>DE20539001</t>
+  </si>
+  <si>
+    <t>DE20539002</t>
+  </si>
+  <si>
+    <t>DE20539004</t>
+  </si>
+  <si>
+    <t>DE20567500</t>
+  </si>
+  <si>
+    <t>DE20569401</t>
+  </si>
+  <si>
+    <t>DE20538145</t>
+  </si>
+  <si>
+    <t>DE20538190</t>
+  </si>
+  <si>
+    <t>DE20539003</t>
+  </si>
+  <si>
+    <t>DE20567400</t>
+  </si>
+  <si>
+    <t>DE50OF0154</t>
+  </si>
+  <si>
+    <t>DE10624416</t>
+  </si>
+  <si>
+    <t>CH65GCA008</t>
+  </si>
+  <si>
+    <t>CH65GCA010</t>
+  </si>
+  <si>
+    <t>CH65GCA001</t>
+  </si>
+  <si>
+    <t>DE50OF6808</t>
+  </si>
+  <si>
+    <t>DK50L93100</t>
+  </si>
+  <si>
+    <t>KR02GHR119</t>
+  </si>
+  <si>
+    <t>MA50GHR018</t>
+  </si>
+  <si>
+    <t>TN50GHR018</t>
+  </si>
+  <si>
+    <t>TN50GHR019</t>
+  </si>
+  <si>
+    <t>TN60GHR018</t>
+  </si>
+  <si>
+    <t>G000000417</t>
+  </si>
+  <si>
+    <t>G000000512</t>
+  </si>
+  <si>
+    <t>G000000511</t>
+  </si>
+  <si>
+    <t>G000000467</t>
+  </si>
+  <si>
+    <t>H000004394</t>
+  </si>
+  <si>
+    <t>G000001227</t>
+  </si>
+  <si>
+    <t>G000000119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P000000188 </t>
+  </si>
+  <si>
+    <t>P000000333</t>
+  </si>
+  <si>
+    <t>L000013447</t>
   </si>
 </sst>
 </file>
@@ -824,7 +914,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:B130"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -842,802 +932,1034 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s">
-        <v>135</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B17" t="s">
-        <v>136</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B22" t="s">
-        <v>136</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B28" t="s">
-        <v>135</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B29" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B32" t="s">
-        <v>135</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B33" t="s">
-        <v>135</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B34" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B35" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B36" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B37" t="s">
-        <v>34</v>
+        <v>162</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B38" t="s">
-        <v>34</v>
+        <v>160</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B39" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B40" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B41" t="s">
-        <v>135</v>
+        <v>162</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B42" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B43" t="s">
-        <v>34</v>
+        <v>160</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B44" t="s">
-        <v>34</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B45" t="s">
-        <v>34</v>
+        <v>160</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B46" t="s">
-        <v>34</v>
+        <v>160</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B47" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B48" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B49" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B50" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B51" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B52" t="s">
-        <v>34</v>
+        <v>160</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B53" t="s">
-        <v>33</v>
+        <v>160</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B54" t="s">
-        <v>33</v>
+        <v>160</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B55" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B56" t="s">
-        <v>33</v>
+        <v>160</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B57" t="s">
-        <v>28</v>
+        <v>160</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B58" t="s">
-        <v>28</v>
+        <v>160</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B59" t="s">
-        <v>28</v>
+        <v>161</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B60" t="s">
-        <v>28</v>
+        <v>161</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B61" t="s">
-        <v>28</v>
+        <v>160</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B62" t="s">
-        <v>28</v>
+        <v>161</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B63" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B64" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B65" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B66" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B67" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B68" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B69" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B70" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B71" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B72" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B73" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B74" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B75" t="s">
-        <v>27</v>
+        <v>161</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B76" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B77" t="s">
-        <v>27</v>
+        <v>161</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B78" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B79" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B80" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B81" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B82" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B83" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B84" t="s">
-        <v>139</v>
+        <v>36</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B85" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B86" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B87" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B88" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B89" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B90" t="s">
-        <v>138</v>
+        <v>26</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B91" t="s">
-        <v>138</v>
+        <v>26</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B92" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B93" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B94" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B95" t="s">
-        <v>139</v>
+        <v>36</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B96" t="s">
-        <v>138</v>
+        <v>36</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B97" t="s">
-        <v>138</v>
+        <v>36</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B98" t="s">
-        <v>138</v>
+        <v>36</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B99" t="s">
-        <v>27</v>
+        <v>161</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B100" t="s">
-        <v>27</v>
+        <v>161</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B101" t="s">
-        <v>27</v>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>137</v>
+      </c>
+      <c r="B102" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>138</v>
+      </c>
+      <c r="B103" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>139</v>
+      </c>
+      <c r="B104" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>140</v>
+      </c>
+      <c r="B105" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>141</v>
+      </c>
+      <c r="B106" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>142</v>
+      </c>
+      <c r="B107" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>143</v>
+      </c>
+      <c r="B108" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>144</v>
+      </c>
+      <c r="B109" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>145</v>
+      </c>
+      <c r="B110" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>146</v>
+      </c>
+      <c r="B111" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>147</v>
+      </c>
+      <c r="B112" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>148</v>
+      </c>
+      <c r="B113" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>149</v>
+      </c>
+      <c r="B114" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>150</v>
+      </c>
+      <c r="B115" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>151</v>
+      </c>
+      <c r="B116" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>152</v>
+      </c>
+      <c r="B117" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>153</v>
+      </c>
+      <c r="B118" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>9</v>
+      </c>
+      <c r="B119" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>154</v>
+      </c>
+      <c r="B120" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>8</v>
+      </c>
+      <c r="B121" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>155</v>
+      </c>
+      <c r="B122" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>156</v>
+      </c>
+      <c r="B123" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>5</v>
+      </c>
+      <c r="B124" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>7</v>
+      </c>
+      <c r="B125" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>157</v>
+      </c>
+      <c r="B126" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>158</v>
+      </c>
+      <c r="B127" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>159</v>
+      </c>
+      <c r="B128" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>167</v>
+      </c>
+      <c r="B129" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>168</v>
+      </c>
+      <c r="B130" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -1856,6 +2178,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
@@ -1866,7 +2197,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -2043,16 +2374,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -2063,7 +2393,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2080,12 +2410,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EBA91CD-9BC4-4EC5-863A-4B63174676CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0138EB6B-9D73-48E6-87A3-97ECF838AF63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9270" yWindow="2910" windowWidth="19215" windowHeight="13875" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="-20130" yWindow="930" windowWidth="19215" windowHeight="13875" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="36">
   <si>
     <t>Child</t>
   </si>
@@ -137,10 +137,13 @@
     <t>G000000873</t>
   </si>
   <si>
-    <t>2102TASR00</t>
-  </si>
-  <si>
-    <t>L000013816</t>
+    <t>G000000944</t>
+  </si>
+  <si>
+    <t>G000000789</t>
+  </si>
+  <si>
+    <t>G000001381</t>
   </si>
 </sst>
 </file>
@@ -498,7 +501,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
-  <dimension ref="A1:B2"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -519,7 +523,15 @@
         <v>33</v>
       </c>
       <c r="B2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>34</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -534,6 +546,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6610AEAF-E772-4D88-8C2B-5DD0E0FA07BD}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -594,6 +607,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C5481AA-55DD-41F0-8076-D4F5ED7BA00E}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -724,6 +738,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DADB64C-1560-4418-AEF8-AFB915F63B31}">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>

--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0138EB6B-9D73-48E6-87A3-97ECF838AF63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2C89E9F-3F3A-4C0C-B2CD-67F53225504F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20130" yWindow="930" windowWidth="19215" windowHeight="13875" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="83">
   <si>
     <t>Child</t>
   </si>
@@ -137,13 +137,154 @@
     <t>G000000873</t>
   </si>
   <si>
-    <t>G000000944</t>
-  </si>
-  <si>
-    <t>G000000789</t>
-  </si>
-  <si>
-    <t>G000001381</t>
+    <t>L000013532</t>
+  </si>
+  <si>
+    <t>L000012674</t>
+  </si>
+  <si>
+    <t>L000012586</t>
+  </si>
+  <si>
+    <t>L000006565</t>
+  </si>
+  <si>
+    <t>L000006563</t>
+  </si>
+  <si>
+    <t>L000013564</t>
+  </si>
+  <si>
+    <t>L000011665</t>
+  </si>
+  <si>
+    <t>L000011328</t>
+  </si>
+  <si>
+    <t>L000011139</t>
+  </si>
+  <si>
+    <t>L000007598</t>
+  </si>
+  <si>
+    <t>L000006209</t>
+  </si>
+  <si>
+    <t>L000012335</t>
+  </si>
+  <si>
+    <t>L000013195</t>
+  </si>
+  <si>
+    <t>L000005336</t>
+  </si>
+  <si>
+    <t>L000013129</t>
+  </si>
+  <si>
+    <t>L000013145</t>
+  </si>
+  <si>
+    <t>L000011455</t>
+  </si>
+  <si>
+    <t>L000011454</t>
+  </si>
+  <si>
+    <t>L000011453</t>
+  </si>
+  <si>
+    <t>L000006463</t>
+  </si>
+  <si>
+    <t>L000006455</t>
+  </si>
+  <si>
+    <t>L000006451</t>
+  </si>
+  <si>
+    <t>L000006450</t>
+  </si>
+  <si>
+    <t>L000013740</t>
+  </si>
+  <si>
+    <t>L000013754</t>
+  </si>
+  <si>
+    <t>L000013756</t>
+  </si>
+  <si>
+    <t>L000012281</t>
+  </si>
+  <si>
+    <t>L000012968</t>
+  </si>
+  <si>
+    <t>L000012280</t>
+  </si>
+  <si>
+    <t>L000012430</t>
+  </si>
+  <si>
+    <t>L000012967</t>
+  </si>
+  <si>
+    <t>L000011337</t>
+  </si>
+  <si>
+    <t>L000013108</t>
+  </si>
+  <si>
+    <t>L000011154</t>
+  </si>
+  <si>
+    <t>L000011153</t>
+  </si>
+  <si>
+    <t>L000013620</t>
+  </si>
+  <si>
+    <t>L000013686</t>
+  </si>
+  <si>
+    <t>L000013374</t>
+  </si>
+  <si>
+    <t>L000013882</t>
+  </si>
+  <si>
+    <t>L000006568</t>
+  </si>
+  <si>
+    <t>L000013847</t>
+  </si>
+  <si>
+    <t>L000013880</t>
+  </si>
+  <si>
+    <t>L000013734</t>
+  </si>
+  <si>
+    <t>L000013388</t>
+  </si>
+  <si>
+    <t>L000013891</t>
+  </si>
+  <si>
+    <t>L000013892</t>
+  </si>
+  <si>
+    <t>L000013893</t>
+  </si>
+  <si>
+    <t>L000013736</t>
+  </si>
+  <si>
+    <t>L000013679</t>
+  </si>
+  <si>
+    <t>L000013687</t>
   </si>
 </sst>
 </file>
@@ -502,7 +643,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -523,7 +664,7 @@
         <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -531,7 +672,295 @@
         <v>34</v>
       </c>
       <c r="B3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>35</v>
+      </c>
+      <c r="B4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>59</v>
+      </c>
+      <c r="B28" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>66</v>
+      </c>
+      <c r="B35" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>67</v>
+      </c>
+      <c r="B36" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>68</v>
+      </c>
+      <c r="B37" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>69</v>
+      </c>
+      <c r="B38" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>70</v>
+      </c>
+      <c r="B39" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -753,6 +1182,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
@@ -763,7 +1201,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -940,16 +1378,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -960,7 +1397,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -977,12 +1414,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,23 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2C89E9F-3F3A-4C0C-B2CD-67F53225504F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C7D36A-7CB6-4623-AC06-452AFFC06ED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="-24585" yWindow="1290" windowWidth="19215" windowHeight="13875" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="9" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="7" r:id="rId3"/>
-    <sheet name="Pierre to do" sheetId="8" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="10" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="9" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="7" r:id="rId4"/>
+    <sheet name="Pierre to do" sheetId="8" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MDGF!$A$1:$D$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet1!$A$5:$B$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Sheet1!$A$5:$B$5</definedName>
     <definedName name="ID" localSheetId="0" hidden="1">"a5f5822f-2145-4cc3-aa32-d164ed237772"</definedName>
-    <definedName name="ID" localSheetId="3" hidden="1">"2b5e4bcf-a0bb-4962-aef7-0fa656cb902f"</definedName>
-    <definedName name="ID" localSheetId="2" hidden="1">"fff7d4e2-cafa-4da0-a3ee-fa93757f1b68"</definedName>
-    <definedName name="ID" localSheetId="1" hidden="1">"d59c0fca-ea81-453e-b1af-313ab178d2df"</definedName>
+    <definedName name="ID" localSheetId="4" hidden="1">"2b5e4bcf-a0bb-4962-aef7-0fa656cb902f"</definedName>
+    <definedName name="ID" localSheetId="3" hidden="1">"fff7d4e2-cafa-4da0-a3ee-fa93757f1b68"</definedName>
+    <definedName name="ID" localSheetId="2" hidden="1">"d59c0fca-ea81-453e-b1af-313ab178d2df"</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="66">
   <si>
     <t>Child</t>
   </si>
@@ -137,154 +138,103 @@
     <t>G000000873</t>
   </si>
   <si>
-    <t>L000013532</t>
-  </si>
-  <si>
-    <t>L000012674</t>
-  </si>
-  <si>
-    <t>L000012586</t>
-  </si>
-  <si>
-    <t>L000006565</t>
-  </si>
-  <si>
-    <t>L000006563</t>
-  </si>
-  <si>
-    <t>L000013564</t>
-  </si>
-  <si>
-    <t>L000011665</t>
-  </si>
-  <si>
-    <t>L000011328</t>
-  </si>
-  <si>
-    <t>L000011139</t>
-  </si>
-  <si>
-    <t>L000007598</t>
-  </si>
-  <si>
-    <t>L000006209</t>
-  </si>
-  <si>
-    <t>L000012335</t>
-  </si>
-  <si>
-    <t>L000013195</t>
-  </si>
-  <si>
-    <t>L000005336</t>
-  </si>
-  <si>
-    <t>L000013129</t>
-  </si>
-  <si>
-    <t>L000013145</t>
-  </si>
-  <si>
-    <t>L000011455</t>
-  </si>
-  <si>
-    <t>L000011454</t>
-  </si>
-  <si>
-    <t>L000011453</t>
-  </si>
-  <si>
-    <t>L000006463</t>
-  </si>
-  <si>
-    <t>L000006455</t>
-  </si>
-  <si>
-    <t>L000006451</t>
-  </si>
-  <si>
-    <t>L000006450</t>
-  </si>
-  <si>
-    <t>L000013740</t>
-  </si>
-  <si>
-    <t>L000013754</t>
-  </si>
-  <si>
-    <t>L000013756</t>
-  </si>
-  <si>
-    <t>L000012281</t>
-  </si>
-  <si>
-    <t>L000012968</t>
-  </si>
-  <si>
-    <t>L000012280</t>
-  </si>
-  <si>
-    <t>L000012430</t>
-  </si>
-  <si>
-    <t>L000012967</t>
-  </si>
-  <si>
-    <t>L000011337</t>
-  </si>
-  <si>
-    <t>L000013108</t>
-  </si>
-  <si>
-    <t>L000011154</t>
-  </si>
-  <si>
-    <t>L000011153</t>
-  </si>
-  <si>
-    <t>L000013620</t>
-  </si>
-  <si>
-    <t>L000013686</t>
-  </si>
-  <si>
-    <t>L000013374</t>
-  </si>
-  <si>
-    <t>L000013882</t>
-  </si>
-  <si>
-    <t>L000006568</t>
-  </si>
-  <si>
-    <t>L000013847</t>
-  </si>
-  <si>
-    <t>L000013880</t>
-  </si>
-  <si>
-    <t>L000013734</t>
-  </si>
-  <si>
-    <t>L000013388</t>
-  </si>
-  <si>
-    <t>L000013891</t>
-  </si>
-  <si>
-    <t>L000013892</t>
-  </si>
-  <si>
-    <t>L000013893</t>
-  </si>
-  <si>
-    <t>L000013736</t>
-  </si>
-  <si>
-    <t>L000013679</t>
-  </si>
-  <si>
-    <t>L000013687</t>
+    <t>DE10685700</t>
+  </si>
+  <si>
+    <t>KR03GIT01B</t>
+  </si>
+  <si>
+    <t>2123GIT027</t>
+  </si>
+  <si>
+    <t>2123GIT212</t>
+  </si>
+  <si>
+    <t>2123GIT448</t>
+  </si>
+  <si>
+    <t>2123GIT520</t>
+  </si>
+  <si>
+    <t>2123GST008</t>
+  </si>
+  <si>
+    <t>2123GIT098</t>
+  </si>
+  <si>
+    <t>2123GIT096</t>
+  </si>
+  <si>
+    <t>2123C00079</t>
+  </si>
+  <si>
+    <t>2123GIT135</t>
+  </si>
+  <si>
+    <t>2123GIT085</t>
+  </si>
+  <si>
+    <t>2123GIT097</t>
+  </si>
+  <si>
+    <t>2123GIT025</t>
+  </si>
+  <si>
+    <t>2123GIT311</t>
+  </si>
+  <si>
+    <t>2123GIT312</t>
+  </si>
+  <si>
+    <t>2123GIT313</t>
+  </si>
+  <si>
+    <t>DE10669638</t>
+  </si>
+  <si>
+    <t>DE10YIT014</t>
+  </si>
+  <si>
+    <t>DE10GMS070</t>
+  </si>
+  <si>
+    <t>2123GMS050</t>
+  </si>
+  <si>
+    <t>2123GMS080</t>
+  </si>
+  <si>
+    <t>L000013397</t>
+  </si>
+  <si>
+    <t>G000000253</t>
+  </si>
+  <si>
+    <t>G000001399</t>
+  </si>
+  <si>
+    <t>G000000277</t>
+  </si>
+  <si>
+    <t>G000001398</t>
+  </si>
+  <si>
+    <t>G000001396</t>
+  </si>
+  <si>
+    <t>P000000765</t>
+  </si>
+  <si>
+    <t>G000001401</t>
+  </si>
+  <si>
+    <t>G000001391</t>
+  </si>
+  <si>
+    <t>G000001416</t>
+  </si>
+  <si>
+    <t>G000001392</t>
   </si>
 </sst>
 </file>
@@ -643,7 +593,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -661,306 +611,162 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>53</v>
-      </c>
-      <c r="B22" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>54</v>
-      </c>
-      <c r="B23" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>56</v>
-      </c>
-      <c r="B25" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>57</v>
-      </c>
-      <c r="B26" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>58</v>
-      </c>
-      <c r="B27" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>59</v>
-      </c>
-      <c r="B28" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>60</v>
-      </c>
-      <c r="B29" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>61</v>
-      </c>
-      <c r="B30" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>63</v>
-      </c>
-      <c r="B32" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
         <v>64</v>
-      </c>
-      <c r="B33" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>65</v>
-      </c>
-      <c r="B34" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>66</v>
-      </c>
-      <c r="B35" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>67</v>
-      </c>
-      <c r="B36" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>68</v>
-      </c>
-      <c r="B37" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>69</v>
-      </c>
-      <c r="B38" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>70</v>
-      </c>
-      <c r="B39" t="s">
-        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -974,6 +780,32 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7257C8B-1D24-4D66-A83C-B8897642E3C4}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6610AEAF-E772-4D88-8C2B-5DD0E0FA07BD}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C5"/>
@@ -1034,7 +866,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C5481AA-55DD-41F0-8076-D4F5ED7BA00E}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:B16"/>
@@ -1165,7 +997,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DADB64C-1560-4418-AEF8-AFB915F63B31}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1"/>
@@ -1182,26 +1014,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -1378,26 +1190,27 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
-    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1414,4 +1227,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
+    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C7D36A-7CB6-4623-AC06-452AFFC06ED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E97566-F554-4CC4-9990-2D8578DF0487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24585" yWindow="1290" windowWidth="19215" windowHeight="13875" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="50">
   <si>
     <t>Child</t>
   </si>
@@ -144,97 +144,49 @@
     <t>KR03GIT01B</t>
   </si>
   <si>
-    <t>2123GIT027</t>
-  </si>
-  <si>
-    <t>2123GIT212</t>
-  </si>
-  <si>
-    <t>2123GIT448</t>
-  </si>
-  <si>
-    <t>2123GIT520</t>
-  </si>
-  <si>
-    <t>2123GST008</t>
-  </si>
-  <si>
-    <t>2123GIT098</t>
-  </si>
-  <si>
-    <t>2123GIT096</t>
-  </si>
-  <si>
-    <t>2123C00079</t>
-  </si>
-  <si>
-    <t>2123GIT135</t>
-  </si>
-  <si>
-    <t>2123GIT085</t>
-  </si>
-  <si>
-    <t>2123GIT097</t>
-  </si>
-  <si>
-    <t>2123GIT025</t>
-  </si>
-  <si>
-    <t>2123GIT311</t>
-  </si>
-  <si>
-    <t>2123GIT312</t>
-  </si>
-  <si>
-    <t>2123GIT313</t>
-  </si>
-  <si>
-    <t>DE10669638</t>
-  </si>
-  <si>
-    <t>DE10YIT014</t>
-  </si>
-  <si>
-    <t>DE10GMS070</t>
-  </si>
-  <si>
-    <t>2123GMS050</t>
-  </si>
-  <si>
-    <t>2123GMS080</t>
-  </si>
-  <si>
-    <t>L000013397</t>
-  </si>
-  <si>
-    <t>G000000253</t>
-  </si>
-  <si>
-    <t>G000001399</t>
-  </si>
-  <si>
     <t>G000000277</t>
   </si>
   <si>
-    <t>G000001398</t>
-  </si>
-  <si>
-    <t>G000001396</t>
-  </si>
-  <si>
     <t>P000000765</t>
   </si>
   <si>
-    <t>G000001401</t>
-  </si>
-  <si>
-    <t>G000001391</t>
-  </si>
-  <si>
-    <t>G000001416</t>
-  </si>
-  <si>
-    <t>G000001392</t>
+    <t>DE10Z03112</t>
+  </si>
+  <si>
+    <t>2068TAUA01</t>
+  </si>
+  <si>
+    <t>2068TAUA00</t>
+  </si>
+  <si>
+    <t>2068TAUA99</t>
+  </si>
+  <si>
+    <t>2068TBUZ21</t>
+  </si>
+  <si>
+    <t>2068TFUZ61</t>
+  </si>
+  <si>
+    <t>2068TKUZ70</t>
+  </si>
+  <si>
+    <t>2068TQUZ90</t>
+  </si>
+  <si>
+    <t>2148TFCZ62</t>
+  </si>
+  <si>
+    <t>2148TFSZ62</t>
+  </si>
+  <si>
+    <t>P000001206</t>
+  </si>
+  <si>
+    <t>L000013876</t>
+  </si>
+  <si>
+    <t>L000013875</t>
   </si>
 </sst>
 </file>
@@ -593,7 +545,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -611,162 +563,82 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
         <v>48</v>
-      </c>
-      <c r="B15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>49</v>
-      </c>
-      <c r="B16" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>53</v>
-      </c>
-      <c r="B20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>54</v>
-      </c>
-      <c r="B21" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -789,7 +661,7 @@
         <v>33</v>
       </c>
       <c r="B1" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -797,7 +669,7 @@
         <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1014,6 +886,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -1190,17 +1073,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1211,6 +1083,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
+    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1229,17 +1112,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
-    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
   <ds:schemaRefs>

--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E97566-F554-4CC4-9990-2D8578DF0487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90F94408-E5B7-4F9F-AD14-635C86B3BB1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="17760" yWindow="5085" windowWidth="19215" windowHeight="13875" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="42">
   <si>
     <t>Child</t>
   </si>
@@ -150,9 +150,6 @@
     <t>P000000765</t>
   </si>
   <si>
-    <t>DE10Z03112</t>
-  </si>
-  <si>
     <t>2068TAUA01</t>
   </si>
   <si>
@@ -163,27 +160,6 @@
   </si>
   <si>
     <t>2068TBUZ21</t>
-  </si>
-  <si>
-    <t>2068TFUZ61</t>
-  </si>
-  <si>
-    <t>2068TKUZ70</t>
-  </si>
-  <si>
-    <t>2068TQUZ90</t>
-  </si>
-  <si>
-    <t>2148TFCZ62</t>
-  </si>
-  <si>
-    <t>2148TFSZ62</t>
-  </si>
-  <si>
-    <t>P000001206</t>
-  </si>
-  <si>
-    <t>L000013876</t>
   </si>
   <si>
     <t>L000013875</t>
@@ -545,7 +521,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -566,7 +542,7 @@
         <v>37</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -574,7 +550,7 @@
         <v>38</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -582,7 +558,7 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -590,55 +566,7 @@
         <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
         <v>41</v>
-      </c>
-      <c r="B6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -886,14 +814,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1074,21 +1000,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
-    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1113,9 +1038,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
+    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90F94408-E5B7-4F9F-AD14-635C86B3BB1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C608B678-6A08-4C14-83C4-21ED8302B000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17760" yWindow="5085" windowWidth="19215" windowHeight="13875" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="2100" yWindow="5610" windowWidth="19215" windowHeight="13875" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="47">
   <si>
     <t>Child</t>
   </si>
@@ -150,19 +150,34 @@
     <t>P000000765</t>
   </si>
   <si>
-    <t>2068TAUA01</t>
-  </si>
-  <si>
-    <t>2068TAUA00</t>
-  </si>
-  <si>
-    <t>2068TAUA99</t>
-  </si>
-  <si>
-    <t>2068TBUZ21</t>
-  </si>
-  <si>
-    <t>L000013875</t>
+    <t>CN70R03104</t>
+  </si>
+  <si>
+    <t>DE50TMDA06</t>
+  </si>
+  <si>
+    <t>CH65R00046</t>
+  </si>
+  <si>
+    <t>CH65R00045</t>
+  </si>
+  <si>
+    <t>CH65R00044</t>
+  </si>
+  <si>
+    <t>IT50R02001</t>
+  </si>
+  <si>
+    <t>IT50R02002</t>
+  </si>
+  <si>
+    <t>H000000643</t>
+  </si>
+  <si>
+    <t>H000004380</t>
+  </si>
+  <si>
+    <t>H000000617</t>
   </si>
 </sst>
 </file>
@@ -184,15 +199,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -200,12 +221,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -521,7 +555,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -538,35 +572,59 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" t="s">
-        <v>41</v>
+      <c r="B6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -814,15 +872,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -999,6 +1048,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1011,14 +1069,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1037,6 +1087,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>

--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C608B678-6A08-4C14-83C4-21ED8302B000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61602BEE-A7B7-4E6A-B20B-DBF72ABD76DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2100" yWindow="5610" windowWidth="19215" windowHeight="13875" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="42">
   <si>
     <t>Child</t>
   </si>
@@ -150,34 +150,19 @@
     <t>P000000765</t>
   </si>
   <si>
-    <t>CN70R03104</t>
-  </si>
-  <si>
-    <t>DE50TMDA06</t>
-  </si>
-  <si>
-    <t>CH65R00046</t>
-  </si>
-  <si>
-    <t>CH65R00045</t>
-  </si>
-  <si>
-    <t>CH65R00044</t>
-  </si>
-  <si>
-    <t>IT50R02001</t>
-  </si>
-  <si>
-    <t>IT50R02002</t>
-  </si>
-  <si>
-    <t>H000000643</t>
-  </si>
-  <si>
-    <t>H000004380</t>
-  </si>
-  <si>
-    <t>H000000617</t>
+    <t>KR03GPO001</t>
+  </si>
+  <si>
+    <t>TW91GPO013</t>
+  </si>
+  <si>
+    <t>US10GPO022</t>
+  </si>
+  <si>
+    <t>US10GPO024</t>
+  </si>
+  <si>
+    <t>G000001130</t>
   </si>
 </sst>
 </file>
@@ -199,21 +184,15 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -221,25 +200,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -555,7 +521,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -572,59 +538,27 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>37</v>
+      <c r="A2" t="s">
+        <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>38</v>
+      <c r="A3" t="s">
+        <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>39</v>
+      <c r="A4" t="s">
+        <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="B6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -639,7 +573,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7257C8B-1D24-4D66-A83C-B8897642E3C4}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -656,6 +590,14 @@
       </c>
       <c r="B2" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -872,6 +814,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -1048,15 +999,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1069,6 +1011,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1087,14 +1037,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>

--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61602BEE-A7B7-4E6A-B20B-DBF72ABD76DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{306DF3A3-070D-4369-8AC0-01499364AEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="18315" yWindow="5730" windowWidth="19215" windowHeight="13170" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -32,12 +32,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="51">
   <si>
     <t>Child</t>
   </si>
@@ -153,16 +156,43 @@
     <t>KR03GPO001</t>
   </si>
   <si>
-    <t>TW91GPO013</t>
-  </si>
-  <si>
-    <t>US10GPO022</t>
-  </si>
-  <si>
-    <t>US10GPO024</t>
-  </si>
-  <si>
     <t>G000001130</t>
+  </si>
+  <si>
+    <t>P000001331</t>
+  </si>
+  <si>
+    <t>P000001332</t>
+  </si>
+  <si>
+    <t>BE10DB3600</t>
+  </si>
+  <si>
+    <t>FR10DB3600</t>
+  </si>
+  <si>
+    <t>GB10DB3600</t>
+  </si>
+  <si>
+    <t>IE10DB3600</t>
+  </si>
+  <si>
+    <t>IL10DB3600</t>
+  </si>
+  <si>
+    <t>IT07DB3600</t>
+  </si>
+  <si>
+    <t>NL10DB3600</t>
+  </si>
+  <si>
+    <t>DE01OF0303</t>
+  </si>
+  <si>
+    <t>DE04OFHQ02</t>
+  </si>
+  <si>
+    <t>DE04TP5000</t>
   </si>
 </sst>
 </file>
@@ -521,7 +551,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -539,26 +569,82 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" t="s">
         <v>39</v>
-      </c>
-      <c r="B3" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s">
         <v>40</v>
       </c>
-      <c r="B4" t="s">
-        <v>41</v>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -597,7 +683,7 @@
         <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{306DF3A3-070D-4369-8AC0-01499364AEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E982EE17-075B-415D-BD92-A1C3D2CA6985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18315" yWindow="5730" windowWidth="19215" windowHeight="13170" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="15825" yWindow="9435" windowWidth="19215" windowHeight="13170" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="54">
   <si>
     <t>Child</t>
   </si>
@@ -193,6 +193,15 @@
   </si>
   <si>
     <t>DE04TP5000</t>
+  </si>
+  <si>
+    <t>DE73R00021</t>
+  </si>
+  <si>
+    <t>DE73R00013</t>
+  </si>
+  <si>
+    <t>G000001283</t>
   </si>
 </sst>
 </file>
@@ -551,7 +560,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -569,23 +578,23 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B4" t="s">
         <v>39</v>
@@ -593,7 +602,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s">
         <v>39</v>
@@ -601,7 +610,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B6" t="s">
         <v>39</v>
@@ -609,7 +618,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s">
         <v>39</v>
@@ -617,7 +626,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
         <v>39</v>
@@ -625,25 +634,41 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>50</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B13" t="s">
         <v>40</v>
       </c>
     </row>
@@ -900,12 +925,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1086,20 +1113,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
+    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1124,12 +1152,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
-    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E982EE17-075B-415D-BD92-A1C3D2CA6985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2288C1E3-ED5B-4639-B08E-84D5416DA4A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15825" yWindow="9435" windowWidth="19215" windowHeight="13170" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="24780" yWindow="5475" windowWidth="13680" windowHeight="13170" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="46">
   <si>
     <t>Child</t>
   </si>
@@ -159,49 +159,25 @@
     <t>G000001130</t>
   </si>
   <si>
-    <t>P000001331</t>
-  </si>
-  <si>
-    <t>P000001332</t>
-  </si>
-  <si>
-    <t>BE10DB3600</t>
-  </si>
-  <si>
-    <t>FR10DB3600</t>
-  </si>
-  <si>
-    <t>GB10DB3600</t>
-  </si>
-  <si>
-    <t>IE10DB3600</t>
-  </si>
-  <si>
-    <t>IL10DB3600</t>
-  </si>
-  <si>
-    <t>IT07DB3600</t>
-  </si>
-  <si>
-    <t>NL10DB3600</t>
-  </si>
-  <si>
-    <t>DE01OF0303</t>
-  </si>
-  <si>
-    <t>DE04OFHQ02</t>
-  </si>
-  <si>
-    <t>DE04TP5000</t>
-  </si>
-  <si>
-    <t>DE73R00021</t>
-  </si>
-  <si>
-    <t>DE73R00013</t>
-  </si>
-  <si>
-    <t>G000001283</t>
+    <t>DE10523400</t>
+  </si>
+  <si>
+    <t>DE10524300</t>
+  </si>
+  <si>
+    <t>DE10625700</t>
+  </si>
+  <si>
+    <t>DE10510000</t>
+  </si>
+  <si>
+    <t>DE10551100</t>
+  </si>
+  <si>
+    <t>G000000387</t>
+  </si>
+  <si>
+    <t>G000000918</t>
   </si>
 </sst>
 </file>
@@ -560,7 +536,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -578,18 +554,18 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -597,7 +573,7 @@
         <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -605,7 +581,7 @@
         <v>42</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -613,63 +589,7 @@
         <v>43</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
         <v>45</v>
-      </c>
-      <c r="B8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -925,14 +845,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1113,21 +1031,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
-    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1152,9 +1069,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
+    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,24 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2288C1E3-ED5B-4639-B08E-84D5416DA4A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{578980F1-858F-4AB6-9A7C-E0AAFFEC2A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24780" yWindow="5475" windowWidth="13680" windowHeight="13170" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="13680" windowHeight="13170" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet3" sheetId="10" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="9" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="7" r:id="rId4"/>
-    <sheet name="Pierre to do" sheetId="8" r:id="rId5"/>
+    <sheet name="Sheet4" sheetId="11" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="10" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="9" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="7" r:id="rId5"/>
+    <sheet name="Pierre to do" sheetId="8" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MDGF!$A$1:$D$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Sheet1!$A$5:$B$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MDGF!$A$1:$B$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sheet1!$A$5:$B$5</definedName>
     <definedName name="ID" localSheetId="0" hidden="1">"a5f5822f-2145-4cc3-aa32-d164ed237772"</definedName>
-    <definedName name="ID" localSheetId="4" hidden="1">"2b5e4bcf-a0bb-4962-aef7-0fa656cb902f"</definedName>
-    <definedName name="ID" localSheetId="3" hidden="1">"fff7d4e2-cafa-4da0-a3ee-fa93757f1b68"</definedName>
-    <definedName name="ID" localSheetId="2" hidden="1">"d59c0fca-ea81-453e-b1af-313ab178d2df"</definedName>
+    <definedName name="ID" localSheetId="5" hidden="1">"2b5e4bcf-a0bb-4962-aef7-0fa656cb902f"</definedName>
+    <definedName name="ID" localSheetId="4" hidden="1">"fff7d4e2-cafa-4da0-a3ee-fa93757f1b68"</definedName>
+    <definedName name="ID" localSheetId="3" hidden="1">"d59c0fca-ea81-453e-b1af-313ab178d2df"</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="112">
   <si>
     <t>Child</t>
   </si>
@@ -159,25 +160,223 @@
     <t>G000001130</t>
   </si>
   <si>
-    <t>DE10523400</t>
-  </si>
-  <si>
-    <t>DE10524300</t>
-  </si>
-  <si>
-    <t>DE10625700</t>
-  </si>
-  <si>
-    <t>DE10510000</t>
-  </si>
-  <si>
-    <t>DE10551100</t>
-  </si>
-  <si>
-    <t>G000000387</t>
-  </si>
-  <si>
-    <t>G000000918</t>
+    <t>JP01C00020</t>
+  </si>
+  <si>
+    <t>GNMI000090</t>
+  </si>
+  <si>
+    <t>JP01C00301</t>
+  </si>
+  <si>
+    <t>JP01C00401</t>
+  </si>
+  <si>
+    <t>JP01C0M825</t>
+  </si>
+  <si>
+    <t>GNMI000051</t>
+  </si>
+  <si>
+    <t>JP01GBT301</t>
+  </si>
+  <si>
+    <t>GNMI000084</t>
+  </si>
+  <si>
+    <t>JP01GBT303</t>
+  </si>
+  <si>
+    <t>JP01GBT304</t>
+  </si>
+  <si>
+    <t>JP01GBT305</t>
+  </si>
+  <si>
+    <t>JP01GCM301</t>
+  </si>
+  <si>
+    <t>GNMI000091</t>
+  </si>
+  <si>
+    <t>JP01GCO301</t>
+  </si>
+  <si>
+    <t>GNMI000081</t>
+  </si>
+  <si>
+    <t>JP01GFO300</t>
+  </si>
+  <si>
+    <t>JP01GFO301</t>
+  </si>
+  <si>
+    <t>JP01GHR301</t>
+  </si>
+  <si>
+    <t>GNMI000082</t>
+  </si>
+  <si>
+    <t>JP01GHR303</t>
+  </si>
+  <si>
+    <t>JP01GIT01B</t>
+  </si>
+  <si>
+    <t>JP01GLE301</t>
+  </si>
+  <si>
+    <t>GNMI000080</t>
+  </si>
+  <si>
+    <t>JP01GLE302</t>
+  </si>
+  <si>
+    <t>JP01GM1002</t>
+  </si>
+  <si>
+    <t>JP01GM4001</t>
+  </si>
+  <si>
+    <t>JP01GM4002</t>
+  </si>
+  <si>
+    <t>JP01GM8001</t>
+  </si>
+  <si>
+    <t>JP01GM8002</t>
+  </si>
+  <si>
+    <t>JP01GMB040</t>
+  </si>
+  <si>
+    <t>JP01GMW080</t>
+  </si>
+  <si>
+    <t>JP01GPO301</t>
+  </si>
+  <si>
+    <t>GNMI000083</t>
+  </si>
+  <si>
+    <t>JP01GPO302</t>
+  </si>
+  <si>
+    <t>JP01GPO303</t>
+  </si>
+  <si>
+    <t>JP01GSQ013</t>
+  </si>
+  <si>
+    <t>JP01L1M001</t>
+  </si>
+  <si>
+    <t>JP01L3K302</t>
+  </si>
+  <si>
+    <t>JP01L3K304</t>
+  </si>
+  <si>
+    <t>JP01L3M301</t>
+  </si>
+  <si>
+    <t>JP01L3M303</t>
+  </si>
+  <si>
+    <t>JP01L4M301</t>
+  </si>
+  <si>
+    <t>JP01L4M302</t>
+  </si>
+  <si>
+    <t>JP01L5M301</t>
+  </si>
+  <si>
+    <t>JP01L5M302</t>
+  </si>
+  <si>
+    <t>JP01L7M301</t>
+  </si>
+  <si>
+    <t>JP01L7M302</t>
+  </si>
+  <si>
+    <t>JP01O05000</t>
+  </si>
+  <si>
+    <t>JP01O05001</t>
+  </si>
+  <si>
+    <t>JP01O05002</t>
+  </si>
+  <si>
+    <t>JP01O05003</t>
+  </si>
+  <si>
+    <t>JP01O05004</t>
+  </si>
+  <si>
+    <t>JP01Z01000</t>
+  </si>
+  <si>
+    <t>JP01Z01IF9</t>
+  </si>
+  <si>
+    <t>JP01Z02141</t>
+  </si>
+  <si>
+    <t>JP01Z02171</t>
+  </si>
+  <si>
+    <t>JP01Z02173</t>
+  </si>
+  <si>
+    <t>JP01Z02174</t>
+  </si>
+  <si>
+    <t>JP01Z02175</t>
+  </si>
+  <si>
+    <t>JP01Z02183</t>
+  </si>
+  <si>
+    <t>JP01Z03103</t>
+  </si>
+  <si>
+    <t>JP01Z03104</t>
+  </si>
+  <si>
+    <t>JP01Z03105</t>
+  </si>
+  <si>
+    <t>JP01Z03700</t>
+  </si>
+  <si>
+    <t>JP01Z03725</t>
+  </si>
+  <si>
+    <t>DE10YIT011</t>
+  </si>
+  <si>
+    <t>DE10YIT012</t>
+  </si>
+  <si>
+    <t>DE10YIT009</t>
+  </si>
+  <si>
+    <t>CH65YIT001</t>
+  </si>
+  <si>
+    <t>DE10YIT008</t>
+  </si>
+  <si>
+    <t>DE10GM8401</t>
+  </si>
+  <si>
+    <t>G000000627</t>
+  </si>
+  <si>
+    <t>L000013461</t>
   </si>
 </sst>
 </file>
@@ -536,7 +735,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -554,45 +753,58 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>104</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>106</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>107</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B7" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B1" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B115">
+      <sortCondition ref="B1"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -603,6 +815,477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B00A0FC-D79D-4B10-944D-C6C9BF412C7A}">
+  <dimension ref="A1:B59"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>86</v>
+      </c>
+      <c r="B19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>88</v>
+      </c>
+      <c r="B21" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>89</v>
+      </c>
+      <c r="B22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>64</v>
+      </c>
+      <c r="B28" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>67</v>
+      </c>
+      <c r="B30" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>69</v>
+      </c>
+      <c r="B32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>91</v>
+      </c>
+      <c r="B33" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>93</v>
+      </c>
+      <c r="B35" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>94</v>
+      </c>
+      <c r="B36" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>95</v>
+      </c>
+      <c r="B37" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>96</v>
+      </c>
+      <c r="B38" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>97</v>
+      </c>
+      <c r="B39" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>98</v>
+      </c>
+      <c r="B40" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>100</v>
+      </c>
+      <c r="B41" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>101</v>
+      </c>
+      <c r="B42" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>102</v>
+      </c>
+      <c r="B43" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>103</v>
+      </c>
+      <c r="B44" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>50</v>
+      </c>
+      <c r="B45" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>55</v>
+      </c>
+      <c r="B47" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>66</v>
+      </c>
+      <c r="B48" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>73</v>
+      </c>
+      <c r="B49" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>75</v>
+      </c>
+      <c r="B50" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>76</v>
+      </c>
+      <c r="B51" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>77</v>
+      </c>
+      <c r="B52" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>78</v>
+      </c>
+      <c r="B53" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>79</v>
+      </c>
+      <c r="B54" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>80</v>
+      </c>
+      <c r="B55" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>82</v>
+      </c>
+      <c r="B56" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>83</v>
+      </c>
+      <c r="B57" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>84</v>
+      </c>
+      <c r="B58" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>85</v>
+      </c>
+      <c r="B59" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7257C8B-1D24-4D66-A83C-B8897642E3C4}">
   <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -636,7 +1319,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6610AEAF-E772-4D88-8C2B-5DD0E0FA07BD}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C5"/>
@@ -697,7 +1380,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C5481AA-55DD-41F0-8076-D4F5ED7BA00E}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:B16"/>
@@ -828,7 +1511,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DADB64C-1560-4418-AEF8-AFB915F63B31}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1"/>

--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{578980F1-858F-4AB6-9A7C-E0AAFFEC2A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C54B4AC8-0F06-469C-8C6E-217E1FA421EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="13680" windowHeight="13170" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="112">
   <si>
     <t>Child</t>
   </si>
@@ -355,28 +355,28 @@
     <t>JP01Z03725</t>
   </si>
   <si>
-    <t>DE10YIT011</t>
-  </si>
-  <si>
-    <t>DE10YIT012</t>
-  </si>
-  <si>
-    <t>DE10YIT009</t>
-  </si>
-  <si>
-    <t>CH65YIT001</t>
-  </si>
-  <si>
-    <t>DE10YIT008</t>
-  </si>
-  <si>
-    <t>DE10GM8401</t>
-  </si>
-  <si>
-    <t>G000000627</t>
-  </si>
-  <si>
-    <t>L000013461</t>
+    <t>IT06071200</t>
+  </si>
+  <si>
+    <t>IT06071300</t>
+  </si>
+  <si>
+    <t>IT07010200</t>
+  </si>
+  <si>
+    <t>IT06021100</t>
+  </si>
+  <si>
+    <t>IT06020300</t>
+  </si>
+  <si>
+    <t>G000001276</t>
+  </si>
+  <si>
+    <t>G000001396</t>
+  </si>
+  <si>
+    <t>G000001235</t>
   </si>
 </sst>
 </file>
@@ -735,7 +735,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -756,7 +756,7 @@
         <v>104</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -764,7 +764,7 @@
         <v>105</v>
       </c>
       <c r="B3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -780,7 +780,7 @@
         <v>107</v>
       </c>
       <c r="B5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -788,14 +788,6 @@
         <v>108</v>
       </c>
       <c r="B6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>109</v>
-      </c>
-      <c r="B7" t="s">
         <v>111</v>
       </c>
     </row>
@@ -1537,6 +1529,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -1713,17 +1716,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
   <ds:schemaRefs>
@@ -1733,6 +1725,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
+    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1749,15 +1752,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
-    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C54B4AC8-0F06-469C-8C6E-217E1FA421EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38237651-271E-4443-B554-449EFF921795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="24960" yWindow="1380" windowWidth="13680" windowHeight="13170" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="222">
   <si>
     <t>Child</t>
   </si>
@@ -355,28 +355,358 @@
     <t>JP01Z03725</t>
   </si>
   <si>
-    <t>IT06071200</t>
-  </si>
-  <si>
-    <t>IT06071300</t>
-  </si>
-  <si>
-    <t>IT07010200</t>
-  </si>
-  <si>
-    <t>IT06021100</t>
-  </si>
-  <si>
-    <t>IT06020300</t>
-  </si>
-  <si>
-    <t>G000001276</t>
-  </si>
-  <si>
-    <t>G000001396</t>
-  </si>
-  <si>
-    <t>G000001235</t>
+    <t>DE10677800</t>
+  </si>
+  <si>
+    <t>P000000763</t>
+  </si>
+  <si>
+    <t>US10GIT034</t>
+  </si>
+  <si>
+    <t>P000000768</t>
+  </si>
+  <si>
+    <t>P01C0M121</t>
+  </si>
+  <si>
+    <t>P000000667</t>
+  </si>
+  <si>
+    <t>P01TQOZ04</t>
+  </si>
+  <si>
+    <t>P000000601</t>
+  </si>
+  <si>
+    <t>P01C0O921</t>
+  </si>
+  <si>
+    <t>P000000616</t>
+  </si>
+  <si>
+    <t>P01R0O721</t>
+  </si>
+  <si>
+    <t>P01C0M621</t>
+  </si>
+  <si>
+    <t>P000000610</t>
+  </si>
+  <si>
+    <t>P01C0M600</t>
+  </si>
+  <si>
+    <t>P000000609</t>
+  </si>
+  <si>
+    <t>P01GCM301</t>
+  </si>
+  <si>
+    <t>P000000756</t>
+  </si>
+  <si>
+    <t>P01GCO301</t>
+  </si>
+  <si>
+    <t>P000000751</t>
+  </si>
+  <si>
+    <t>P01L5M302</t>
+  </si>
+  <si>
+    <t>P000000421</t>
+  </si>
+  <si>
+    <t>P01L4M302</t>
+  </si>
+  <si>
+    <t>P000000420</t>
+  </si>
+  <si>
+    <t>P01L7M303</t>
+  </si>
+  <si>
+    <t>P000000424</t>
+  </si>
+  <si>
+    <t>P01TPOZ01</t>
+  </si>
+  <si>
+    <t>P01TQOZ03</t>
+  </si>
+  <si>
+    <t>P01C0M825</t>
+  </si>
+  <si>
+    <t>P000000742</t>
+  </si>
+  <si>
+    <t>P01TFOZ01</t>
+  </si>
+  <si>
+    <t>P000000175</t>
+  </si>
+  <si>
+    <t>P01TFOZ02</t>
+  </si>
+  <si>
+    <t>P01TFOZ03</t>
+  </si>
+  <si>
+    <t>P01Z03725</t>
+  </si>
+  <si>
+    <t>P000001206</t>
+  </si>
+  <si>
+    <t>P01Z03104</t>
+  </si>
+  <si>
+    <t>P000001201</t>
+  </si>
+  <si>
+    <t>P01Z03105</t>
+  </si>
+  <si>
+    <t>P000001270</t>
+  </si>
+  <si>
+    <t>P01C00020</t>
+  </si>
+  <si>
+    <t>P000000612</t>
+  </si>
+  <si>
+    <t>P01C00301</t>
+  </si>
+  <si>
+    <t>P000001050</t>
+  </si>
+  <si>
+    <t>P01C00401</t>
+  </si>
+  <si>
+    <t>P01Z01000</t>
+  </si>
+  <si>
+    <t>P000001045</t>
+  </si>
+  <si>
+    <t>P01Z02141</t>
+  </si>
+  <si>
+    <t>P000000556</t>
+  </si>
+  <si>
+    <t>P01Z02171</t>
+  </si>
+  <si>
+    <t>P000001048</t>
+  </si>
+  <si>
+    <t>P01Z02173</t>
+  </si>
+  <si>
+    <t>P01Z02174</t>
+  </si>
+  <si>
+    <t>P01Z02175</t>
+  </si>
+  <si>
+    <t>P01GPO301</t>
+  </si>
+  <si>
+    <t>P000000755</t>
+  </si>
+  <si>
+    <t>P000000170</t>
+  </si>
+  <si>
+    <t>P01GHR303</t>
+  </si>
+  <si>
+    <t>P000000757</t>
+  </si>
+  <si>
+    <t>P01Z03103</t>
+  </si>
+  <si>
+    <t>P000001271</t>
+  </si>
+  <si>
+    <t>P01TAOZ03</t>
+  </si>
+  <si>
+    <t>P01TDOZ01</t>
+  </si>
+  <si>
+    <t>P000000173</t>
+  </si>
+  <si>
+    <t>P01TDOZ02</t>
+  </si>
+  <si>
+    <t>P01TDOZ03</t>
+  </si>
+  <si>
+    <t>P01TDOZ04</t>
+  </si>
+  <si>
+    <t>P01TDOZ05</t>
+  </si>
+  <si>
+    <t>P01TDOZ06</t>
+  </si>
+  <si>
+    <t>P01TEOZ01</t>
+  </si>
+  <si>
+    <t>P000000174</t>
+  </si>
+  <si>
+    <t>P01TAOB00</t>
+  </si>
+  <si>
+    <t>P01TAOB01</t>
+  </si>
+  <si>
+    <t>P01TAOB02</t>
+  </si>
+  <si>
+    <t>P01TAOB99</t>
+  </si>
+  <si>
+    <t>P01TAOC02</t>
+  </si>
+  <si>
+    <t>P01TAOE00</t>
+  </si>
+  <si>
+    <t>P01TAOE01</t>
+  </si>
+  <si>
+    <t>P01TAOE99</t>
+  </si>
+  <si>
+    <t>P01TAOA00</t>
+  </si>
+  <si>
+    <t>P01TAOA01</t>
+  </si>
+  <si>
+    <t>P01TAOA99</t>
+  </si>
+  <si>
+    <t>P01TAOD02</t>
+  </si>
+  <si>
+    <t>P01TAOZ06</t>
+  </si>
+  <si>
+    <t>P01TAOZ01</t>
+  </si>
+  <si>
+    <t>P01TLOZ01</t>
+  </si>
+  <si>
+    <t>P000000177</t>
+  </si>
+  <si>
+    <t>P01TNMZ04</t>
+  </si>
+  <si>
+    <t>P000000794</t>
+  </si>
+  <si>
+    <t>P01TAOZ04</t>
+  </si>
+  <si>
+    <t>P01TKOZ00</t>
+  </si>
+  <si>
+    <t>P000000176</t>
+  </si>
+  <si>
+    <t>P01TBOZ01</t>
+  </si>
+  <si>
+    <t>P000000171</t>
+  </si>
+  <si>
+    <t>P01TQOZ01</t>
+  </si>
+  <si>
+    <t>P01TBOZ05</t>
+  </si>
+  <si>
+    <t>P000000317</t>
+  </si>
+  <si>
+    <t>P01TCOZ01</t>
+  </si>
+  <si>
+    <t>P000000172</t>
+  </si>
+  <si>
+    <t>P01C0M821</t>
+  </si>
+  <si>
+    <t>P000000447</t>
+  </si>
+  <si>
+    <t>P01C0M921</t>
+  </si>
+  <si>
+    <t>P000000666</t>
+  </si>
+  <si>
+    <t>P01C0M822</t>
+  </si>
+  <si>
+    <t>P000000448</t>
+  </si>
+  <si>
+    <t>P01C0O999</t>
+  </si>
+  <si>
+    <t>P000000565</t>
+  </si>
+  <si>
+    <t>P01L1M001</t>
+  </si>
+  <si>
+    <t>P000000958</t>
+  </si>
+  <si>
+    <t>P01L3K304</t>
+  </si>
+  <si>
+    <t>P01L3M303</t>
+  </si>
+  <si>
+    <t>P01L4M301</t>
+  </si>
+  <si>
+    <t>P01L5M301</t>
+  </si>
+  <si>
+    <t>P01L7M301</t>
+  </si>
+  <si>
+    <t>P01L7M302</t>
+  </si>
+  <si>
+    <t>P01OF0203</t>
+  </si>
+  <si>
+    <t>P000001160</t>
+  </si>
+  <si>
+    <t>P01R0S743</t>
+  </si>
+  <si>
+    <t>P000001015</t>
   </si>
 </sst>
 </file>
@@ -735,7 +1065,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B79"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -753,50 +1083,629 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>104</v>
+        <v>164</v>
       </c>
       <c r="B2" t="s">
-        <v>109</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>105</v>
+        <v>174</v>
       </c>
       <c r="B3" t="s">
-        <v>109</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>106</v>
+        <v>175</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>107</v>
+        <v>176</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>178</v>
+      </c>
+      <c r="B7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>179</v>
+      </c>
+      <c r="B8" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>180</v>
+      </c>
+      <c r="B9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>181</v>
+      </c>
+      <c r="B10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>182</v>
+      </c>
+      <c r="B11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>183</v>
+      </c>
+      <c r="B12" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>184</v>
+      </c>
+      <c r="B13" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>185</v>
+      </c>
+      <c r="B14" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>186</v>
+      </c>
+      <c r="B15" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B16" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>192</v>
+      </c>
+      <c r="B17" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>195</v>
+      </c>
+      <c r="B18" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>200</v>
+      </c>
+      <c r="B19" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>165</v>
+      </c>
+      <c r="B20" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>167</v>
+      </c>
+      <c r="B21" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>168</v>
+      </c>
+      <c r="B22" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>169</v>
+      </c>
+      <c r="B23" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>170</v>
+      </c>
+      <c r="B24" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>171</v>
+      </c>
+      <c r="B25" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>172</v>
+      </c>
+      <c r="B26" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>133</v>
+      </c>
+      <c r="B27" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>135</v>
+      </c>
+      <c r="B28" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>136</v>
+      </c>
+      <c r="B29" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>193</v>
+      </c>
+      <c r="B30" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>188</v>
+      </c>
+      <c r="B31" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>198</v>
+      </c>
+      <c r="B32" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>125</v>
+      </c>
+      <c r="B33" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>123</v>
+      </c>
+      <c r="B34" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>215</v>
+      </c>
+      <c r="B35" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>127</v>
+      </c>
+      <c r="B36" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>212</v>
+      </c>
+      <c r="B37" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>213</v>
+      </c>
+      <c r="B38" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>214</v>
+      </c>
+      <c r="B39" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>216</v>
+      </c>
+      <c r="B40" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>217</v>
+      </c>
+      <c r="B41" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>202</v>
+      </c>
+      <c r="B42" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>206</v>
+      </c>
+      <c r="B43" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>150</v>
+      </c>
+      <c r="B44" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>208</v>
+      </c>
+      <c r="B45" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>110</v>
+      </c>
+      <c r="B46" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>129</v>
+      </c>
+      <c r="B47" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>130</v>
+      </c>
+      <c r="B48" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>197</v>
+      </c>
+      <c r="B49" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>117</v>
+      </c>
+      <c r="B50" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>115</v>
+      </c>
+      <c r="B51" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>143</v>
+      </c>
+      <c r="B52" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>112</v>
+      </c>
+      <c r="B53" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>114</v>
+      </c>
+      <c r="B54" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>204</v>
+      </c>
+      <c r="B55" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
         <v>108</v>
       </c>
-      <c r="B6" t="s">
-        <v>111</v>
+      <c r="B56" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>131</v>
+      </c>
+      <c r="B57" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>121</v>
+      </c>
+      <c r="B58" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>157</v>
+      </c>
+      <c r="B59" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>119</v>
+      </c>
+      <c r="B60" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>160</v>
+      </c>
+      <c r="B61" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>104</v>
+      </c>
+      <c r="B62" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>33</v>
+      </c>
+      <c r="B63" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>106</v>
+      </c>
+      <c r="B64" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>190</v>
+      </c>
+      <c r="B65" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>210</v>
+      </c>
+      <c r="B66" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>220</v>
+      </c>
+      <c r="B67" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>148</v>
+      </c>
+      <c r="B68" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>152</v>
+      </c>
+      <c r="B69" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>154</v>
+      </c>
+      <c r="B70" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>155</v>
+      </c>
+      <c r="B71" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>156</v>
+      </c>
+      <c r="B72" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>145</v>
+      </c>
+      <c r="B73" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>147</v>
+      </c>
+      <c r="B74" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>218</v>
+      </c>
+      <c r="B75" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>139</v>
+      </c>
+      <c r="B76" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>137</v>
+      </c>
+      <c r="B77" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>141</v>
+      </c>
+      <c r="B78" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>162</v>
+      </c>
+      <c r="B79" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B115">
-      <sortCondition ref="B1"/>
-    </sortState>
-  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1520,26 +2429,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -1716,10 +2605,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1736,20 +2656,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
-    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,25 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38237651-271E-4443-B554-449EFF921795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01CB0942-DEDA-417E-8EA7-A4777F5878DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24960" yWindow="1380" windowWidth="13680" windowHeight="13170" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="11775" yWindow="3885" windowWidth="13680" windowHeight="13170" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet4" sheetId="11" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="10" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="9" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="7" r:id="rId5"/>
-    <sheet name="Pierre to do" sheetId="8" r:id="rId6"/>
+    <sheet name="Sheet5" sheetId="12" r:id="rId2"/>
+    <sheet name="Sheet4" sheetId="11" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="10" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="9" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="7" r:id="rId6"/>
+    <sheet name="Pierre to do" sheetId="8" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MDGF!$A$1:$B$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sheet1!$A$5:$B$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Sheet1!$A$5:$B$5</definedName>
     <definedName name="ID" localSheetId="0" hidden="1">"a5f5822f-2145-4cc3-aa32-d164ed237772"</definedName>
-    <definedName name="ID" localSheetId="5" hidden="1">"2b5e4bcf-a0bb-4962-aef7-0fa656cb902f"</definedName>
-    <definedName name="ID" localSheetId="4" hidden="1">"fff7d4e2-cafa-4da0-a3ee-fa93757f1b68"</definedName>
-    <definedName name="ID" localSheetId="3" hidden="1">"d59c0fca-ea81-453e-b1af-313ab178d2df"</definedName>
+    <definedName name="ID" localSheetId="6" hidden="1">"2b5e4bcf-a0bb-4962-aef7-0fa656cb902f"</definedName>
+    <definedName name="ID" localSheetId="5" hidden="1">"fff7d4e2-cafa-4da0-a3ee-fa93757f1b68"</definedName>
+    <definedName name="ID" localSheetId="4" hidden="1">"d59c0fca-ea81-453e-b1af-313ab178d2df"</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="116">
   <si>
     <t>Child</t>
   </si>
@@ -355,358 +356,40 @@
     <t>JP01Z03725</t>
   </si>
   <si>
-    <t>DE10677800</t>
-  </si>
-  <si>
-    <t>P000000763</t>
-  </si>
-  <si>
-    <t>US10GIT034</t>
-  </si>
-  <si>
-    <t>P000000768</t>
-  </si>
-  <si>
-    <t>P01C0M121</t>
-  </si>
-  <si>
-    <t>P000000667</t>
-  </si>
-  <si>
-    <t>P01TQOZ04</t>
-  </si>
-  <si>
-    <t>P000000601</t>
-  </si>
-  <si>
-    <t>P01C0O921</t>
-  </si>
-  <si>
-    <t>P000000616</t>
-  </si>
-  <si>
-    <t>P01R0O721</t>
-  </si>
-  <si>
-    <t>P01C0M621</t>
-  </si>
-  <si>
-    <t>P000000610</t>
-  </si>
-  <si>
-    <t>P01C0M600</t>
-  </si>
-  <si>
-    <t>P000000609</t>
-  </si>
-  <si>
-    <t>P01GCM301</t>
-  </si>
-  <si>
-    <t>P000000756</t>
-  </si>
-  <si>
-    <t>P01GCO301</t>
-  </si>
-  <si>
-    <t>P000000751</t>
-  </si>
-  <si>
-    <t>P01L5M302</t>
-  </si>
-  <si>
-    <t>P000000421</t>
-  </si>
-  <si>
-    <t>P01L4M302</t>
-  </si>
-  <si>
-    <t>P000000420</t>
-  </si>
-  <si>
-    <t>P01L7M303</t>
-  </si>
-  <si>
-    <t>P000000424</t>
-  </si>
-  <si>
-    <t>P01TPOZ01</t>
-  </si>
-  <si>
-    <t>P01TQOZ03</t>
-  </si>
-  <si>
-    <t>P01C0M825</t>
-  </si>
-  <si>
-    <t>P000000742</t>
-  </si>
-  <si>
-    <t>P01TFOZ01</t>
-  </si>
-  <si>
-    <t>P000000175</t>
-  </si>
-  <si>
-    <t>P01TFOZ02</t>
-  </si>
-  <si>
-    <t>P01TFOZ03</t>
-  </si>
-  <si>
-    <t>P01Z03725</t>
-  </si>
-  <si>
-    <t>P000001206</t>
-  </si>
-  <si>
-    <t>P01Z03104</t>
-  </si>
-  <si>
-    <t>P000001201</t>
-  </si>
-  <si>
-    <t>P01Z03105</t>
-  </si>
-  <si>
-    <t>P000001270</t>
-  </si>
-  <si>
-    <t>P01C00020</t>
-  </si>
-  <si>
-    <t>P000000612</t>
-  </si>
-  <si>
-    <t>P01C00301</t>
-  </si>
-  <si>
-    <t>P000001050</t>
-  </si>
-  <si>
-    <t>P01C00401</t>
-  </si>
-  <si>
-    <t>P01Z01000</t>
-  </si>
-  <si>
-    <t>P000001045</t>
-  </si>
-  <si>
-    <t>P01Z02141</t>
-  </si>
-  <si>
-    <t>P000000556</t>
-  </si>
-  <si>
-    <t>P01Z02171</t>
-  </si>
-  <si>
-    <t>P000001048</t>
-  </si>
-  <si>
-    <t>P01Z02173</t>
-  </si>
-  <si>
-    <t>P01Z02174</t>
-  </si>
-  <si>
-    <t>P01Z02175</t>
-  </si>
-  <si>
-    <t>P01GPO301</t>
-  </si>
-  <si>
-    <t>P000000755</t>
-  </si>
-  <si>
-    <t>P000000170</t>
-  </si>
-  <si>
-    <t>P01GHR303</t>
-  </si>
-  <si>
-    <t>P000000757</t>
-  </si>
-  <si>
-    <t>P01Z03103</t>
-  </si>
-  <si>
-    <t>P000001271</t>
-  </si>
-  <si>
-    <t>P01TAOZ03</t>
-  </si>
-  <si>
-    <t>P01TDOZ01</t>
-  </si>
-  <si>
-    <t>P000000173</t>
-  </si>
-  <si>
-    <t>P01TDOZ02</t>
-  </si>
-  <si>
-    <t>P01TDOZ03</t>
-  </si>
-  <si>
-    <t>P01TDOZ04</t>
-  </si>
-  <si>
-    <t>P01TDOZ05</t>
-  </si>
-  <si>
-    <t>P01TDOZ06</t>
-  </si>
-  <si>
-    <t>P01TEOZ01</t>
-  </si>
-  <si>
-    <t>P000000174</t>
-  </si>
-  <si>
-    <t>P01TAOB00</t>
-  </si>
-  <si>
-    <t>P01TAOB01</t>
-  </si>
-  <si>
-    <t>P01TAOB02</t>
-  </si>
-  <si>
-    <t>P01TAOB99</t>
-  </si>
-  <si>
-    <t>P01TAOC02</t>
-  </si>
-  <si>
-    <t>P01TAOE00</t>
-  </si>
-  <si>
-    <t>P01TAOE01</t>
-  </si>
-  <si>
-    <t>P01TAOE99</t>
-  </si>
-  <si>
-    <t>P01TAOA00</t>
-  </si>
-  <si>
-    <t>P01TAOA01</t>
-  </si>
-  <si>
-    <t>P01TAOA99</t>
-  </si>
-  <si>
-    <t>P01TAOD02</t>
-  </si>
-  <si>
-    <t>P01TAOZ06</t>
-  </si>
-  <si>
-    <t>P01TAOZ01</t>
-  </si>
-  <si>
-    <t>P01TLOZ01</t>
-  </si>
-  <si>
-    <t>P000000177</t>
-  </si>
-  <si>
-    <t>P01TNMZ04</t>
-  </si>
-  <si>
-    <t>P000000794</t>
-  </si>
-  <si>
-    <t>P01TAOZ04</t>
-  </si>
-  <si>
-    <t>P01TKOZ00</t>
-  </si>
-  <si>
-    <t>P000000176</t>
-  </si>
-  <si>
-    <t>P01TBOZ01</t>
-  </si>
-  <si>
-    <t>P000000171</t>
-  </si>
-  <si>
-    <t>P01TQOZ01</t>
-  </si>
-  <si>
-    <t>P01TBOZ05</t>
-  </si>
-  <si>
-    <t>P000000317</t>
-  </si>
-  <si>
-    <t>P01TCOZ01</t>
-  </si>
-  <si>
-    <t>P000000172</t>
-  </si>
-  <si>
-    <t>P01C0M821</t>
-  </si>
-  <si>
-    <t>P000000447</t>
-  </si>
-  <si>
-    <t>P01C0M921</t>
-  </si>
-  <si>
-    <t>P000000666</t>
-  </si>
-  <si>
-    <t>P01C0M822</t>
-  </si>
-  <si>
-    <t>P000000448</t>
-  </si>
-  <si>
-    <t>P01C0O999</t>
-  </si>
-  <si>
-    <t>P000000565</t>
-  </si>
-  <si>
-    <t>P01L1M001</t>
-  </si>
-  <si>
-    <t>P000000958</t>
-  </si>
-  <si>
-    <t>P01L3K304</t>
-  </si>
-  <si>
-    <t>P01L3M303</t>
-  </si>
-  <si>
-    <t>P01L4M301</t>
-  </si>
-  <si>
-    <t>P01L5M301</t>
-  </si>
-  <si>
-    <t>P01L7M301</t>
-  </si>
-  <si>
-    <t>P01L7M302</t>
-  </si>
-  <si>
-    <t>P01OF0203</t>
-  </si>
-  <si>
-    <t>P000001160</t>
-  </si>
-  <si>
-    <t>P01R0S743</t>
-  </si>
-  <si>
-    <t>P000001015</t>
+    <t>CNS1OF0144</t>
+  </si>
+  <si>
+    <t>DES1OFCX20</t>
+  </si>
+  <si>
+    <t>DES1OFCX21</t>
+  </si>
+  <si>
+    <t>DES1Z01000</t>
+  </si>
+  <si>
+    <t>KRS1Z01000</t>
+  </si>
+  <si>
+    <t>MYS1OF0110</t>
+  </si>
+  <si>
+    <t>MYS1Z01000</t>
+  </si>
+  <si>
+    <t>THS1OF0110</t>
+  </si>
+  <si>
+    <t>USS1Z01000</t>
+  </si>
+  <si>
+    <t>CNS1Z01000</t>
+  </si>
+  <si>
+    <t>THS1Z01000</t>
+  </si>
+  <si>
+    <t>P000000769</t>
   </si>
 </sst>
 </file>
@@ -1065,7 +748,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B79"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -1083,626 +766,74 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>164</v>
+        <v>104</v>
       </c>
       <c r="B2" t="s">
-        <v>159</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>174</v>
+        <v>107</v>
       </c>
       <c r="B3" t="s">
-        <v>159</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>175</v>
+        <v>108</v>
       </c>
       <c r="B4" t="s">
-        <v>159</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>176</v>
+        <v>109</v>
       </c>
       <c r="B5" t="s">
-        <v>159</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>177</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s">
-        <v>159</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>178</v>
+        <v>111</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>179</v>
+        <v>112</v>
       </c>
       <c r="B8" t="s">
-        <v>159</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>180</v>
+        <v>113</v>
       </c>
       <c r="B9" t="s">
-        <v>159</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>181</v>
+        <v>114</v>
       </c>
       <c r="B10" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>182</v>
-      </c>
-      <c r="B11" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>183</v>
-      </c>
-      <c r="B12" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>184</v>
-      </c>
-      <c r="B13" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>185</v>
-      </c>
-      <c r="B14" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>186</v>
-      </c>
-      <c r="B15" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>187</v>
-      </c>
-      <c r="B16" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>192</v>
-      </c>
-      <c r="B17" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>195</v>
-      </c>
-      <c r="B18" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>200</v>
-      </c>
-      <c r="B19" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>165</v>
-      </c>
-      <c r="B20" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>167</v>
-      </c>
-      <c r="B21" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>168</v>
-      </c>
-      <c r="B22" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>169</v>
-      </c>
-      <c r="B23" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>170</v>
-      </c>
-      <c r="B24" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>171</v>
-      </c>
-      <c r="B25" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>172</v>
-      </c>
-      <c r="B26" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>133</v>
-      </c>
-      <c r="B27" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>135</v>
-      </c>
-      <c r="B28" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>136</v>
-      </c>
-      <c r="B29" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>193</v>
-      </c>
-      <c r="B30" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>188</v>
-      </c>
-      <c r="B31" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>198</v>
-      </c>
-      <c r="B32" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>125</v>
-      </c>
-      <c r="B33" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>123</v>
-      </c>
-      <c r="B34" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>215</v>
-      </c>
-      <c r="B35" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>127</v>
-      </c>
-      <c r="B36" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>212</v>
-      </c>
-      <c r="B37" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>213</v>
-      </c>
-      <c r="B38" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>214</v>
-      </c>
-      <c r="B39" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>216</v>
-      </c>
-      <c r="B40" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>217</v>
-      </c>
-      <c r="B41" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>202</v>
-      </c>
-      <c r="B42" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>206</v>
-      </c>
-      <c r="B43" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>150</v>
-      </c>
-      <c r="B44" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>208</v>
-      </c>
-      <c r="B45" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>110</v>
-      </c>
-      <c r="B46" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>129</v>
-      </c>
-      <c r="B47" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>130</v>
-      </c>
-      <c r="B48" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>197</v>
-      </c>
-      <c r="B49" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>117</v>
-      </c>
-      <c r="B50" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>115</v>
-      </c>
-      <c r="B51" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>143</v>
-      </c>
-      <c r="B52" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>112</v>
-      </c>
-      <c r="B53" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>114</v>
-      </c>
-      <c r="B54" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>204</v>
-      </c>
-      <c r="B55" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>108</v>
-      </c>
-      <c r="B56" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>131</v>
-      </c>
-      <c r="B57" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>121</v>
-      </c>
-      <c r="B58" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>157</v>
-      </c>
-      <c r="B59" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>119</v>
-      </c>
-      <c r="B60" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>160</v>
-      </c>
-      <c r="B61" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>104</v>
-      </c>
-      <c r="B62" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>33</v>
-      </c>
-      <c r="B63" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>106</v>
-      </c>
-      <c r="B64" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>190</v>
-      </c>
-      <c r="B65" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>210</v>
-      </c>
-      <c r="B66" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>220</v>
-      </c>
-      <c r="B67" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>148</v>
-      </c>
-      <c r="B68" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>152</v>
-      </c>
-      <c r="B69" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>154</v>
-      </c>
-      <c r="B70" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>155</v>
-      </c>
-      <c r="B71" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>156</v>
-      </c>
-      <c r="B72" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>145</v>
-      </c>
-      <c r="B73" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>147</v>
-      </c>
-      <c r="B74" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>218</v>
-      </c>
-      <c r="B75" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>139</v>
-      </c>
-      <c r="B76" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>137</v>
-      </c>
-      <c r="B77" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>141</v>
-      </c>
-      <c r="B78" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>162</v>
-      </c>
-      <c r="B79" t="s">
-        <v>163</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1716,6 +847,32 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEFFB296-0EDE-4DB3-9556-9CC7179143E5}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B00A0FC-D79D-4B10-944D-C6C9BF412C7A}">
   <dimension ref="A1:B59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2186,7 +1343,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7257C8B-1D24-4D66-A83C-B8897642E3C4}">
   <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2220,7 +1377,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6610AEAF-E772-4D88-8C2B-5DD0E0FA07BD}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C5"/>
@@ -2281,7 +1438,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C5481AA-55DD-41F0-8076-D4F5ED7BA00E}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:B16"/>
@@ -2412,7 +1569,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DADB64C-1560-4418-AEF8-AFB915F63B31}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1"/>
@@ -2429,6 +1586,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -2605,27 +1782,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
+    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2642,23 +1818,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
-    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M346157\Documents\GCOH-Tickets-for-Processing\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01CB0942-DEDA-417E-8EA7-A4777F5878DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4AFD18E-7F1B-48E2-9847-EBA03C5000B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11775" yWindow="3885" windowWidth="13680" windowHeight="13170" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -28,8 +28,11 @@
     <definedName name="ID" localSheetId="6" hidden="1">"2b5e4bcf-a0bb-4962-aef7-0fa656cb902f"</definedName>
     <definedName name="ID" localSheetId="5" hidden="1">"fff7d4e2-cafa-4da0-a3ee-fa93757f1b68"</definedName>
     <definedName name="ID" localSheetId="4" hidden="1">"d59c0fca-ea81-453e-b1af-313ab178d2df"</definedName>
+    <definedName name="ID" localSheetId="3" hidden="1">"78c1409c-f389-4bdf-b04b-8c605d40ec4a"</definedName>
+    <definedName name="ID" localSheetId="2" hidden="1">"4893a801-c8f4-43e0-8b40-4123b65c3b6f"</definedName>
+    <definedName name="ID" localSheetId="1" hidden="1">"bab6acb3-5d16-4394-984a-d708b37c40df"</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" calcCompleted="0" calcOnSave="0" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="123">
   <si>
     <t>Child</t>
   </si>
@@ -365,31 +368,52 @@
     <t>DES1OFCX21</t>
   </si>
   <si>
-    <t>DES1Z01000</t>
-  </si>
-  <si>
-    <t>KRS1Z01000</t>
-  </si>
-  <si>
     <t>MYS1OF0110</t>
   </si>
   <si>
-    <t>MYS1Z01000</t>
-  </si>
-  <si>
     <t>THS1OF0110</t>
   </si>
   <si>
-    <t>USS1Z01000</t>
-  </si>
-  <si>
-    <t>CNS1Z01000</t>
-  </si>
-  <si>
-    <t>THS1Z01000</t>
-  </si>
-  <si>
-    <t>P000000769</t>
+    <t>BE50GLE300</t>
+  </si>
+  <si>
+    <t>JP02GLE302</t>
+  </si>
+  <si>
+    <t>KR02GLE005</t>
+  </si>
+  <si>
+    <t>TW02GLE006</t>
+  </si>
+  <si>
+    <t>TW03GLE006</t>
+  </si>
+  <si>
+    <t>2057GLE006</t>
+  </si>
+  <si>
+    <t>KR03GLE005</t>
+  </si>
+  <si>
+    <t>TW10GLE106</t>
+  </si>
+  <si>
+    <t>TW91GLE106</t>
+  </si>
+  <si>
+    <t>DE10620801</t>
+  </si>
+  <si>
+    <t>G000001104</t>
+  </si>
+  <si>
+    <t>G000001103</t>
+  </si>
+  <si>
+    <t>G000000432</t>
+  </si>
+  <si>
+    <t>GNMI000720</t>
   </si>
 </sst>
 </file>
@@ -451,9 +475,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -491,7 +515,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -597,7 +621,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -739,7 +763,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -748,15 +772,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -764,76 +788,124 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>114</v>
+      </c>
+      <c r="B8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B10" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>104</v>
       </c>
-      <c r="B2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>107</v>
       </c>
-      <c r="B3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B14" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>108</v>
       </c>
-      <c r="B4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>110</v>
-      </c>
-      <c r="B6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>111</v>
-      </c>
-      <c r="B7" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>112</v>
-      </c>
-      <c r="B8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>113</v>
-      </c>
-      <c r="B9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>114</v>
-      </c>
-      <c r="B10" t="s">
-        <v>40</v>
+      <c r="B15" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>107</v>
+      </c>
+      <c r="B16" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -849,9 +921,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEFFB296-0EDE-4DB3-9556-9CC7179143E5}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>105</v>
       </c>
@@ -859,7 +931,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>106</v>
       </c>
@@ -875,13 +947,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B00A0FC-D79D-4B10-944D-C6C9BF412C7A}">
   <dimension ref="A1:B59"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>43</v>
       </c>
@@ -889,7 +961,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>60</v>
       </c>
@@ -897,7 +969,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>62</v>
       </c>
@@ -905,7 +977,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>52</v>
       </c>
@@ -913,7 +985,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>56</v>
       </c>
@@ -921,7 +993,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>58</v>
       </c>
@@ -929,7 +1001,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>81</v>
       </c>
@@ -937,7 +1009,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>99</v>
       </c>
@@ -945,7 +1017,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>70</v>
       </c>
@@ -953,7 +1025,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>72</v>
       </c>
@@ -961,7 +1033,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>45</v>
       </c>
@@ -969,7 +1041,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>47</v>
       </c>
@@ -977,7 +1049,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>48</v>
       </c>
@@ -985,7 +1057,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>49</v>
       </c>
@@ -993,7 +1065,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>59</v>
       </c>
@@ -1001,7 +1073,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>74</v>
       </c>
@@ -1009,7 +1081,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>86</v>
       </c>
@@ -1017,7 +1089,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>87</v>
       </c>
@@ -1025,7 +1097,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>88</v>
       </c>
@@ -1033,7 +1105,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>89</v>
       </c>
@@ -1041,7 +1113,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>90</v>
       </c>
@@ -1049,7 +1121,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -1057,7 +1129,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>41</v>
       </c>
@@ -1065,7 +1137,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>42</v>
       </c>
@@ -1073,7 +1145,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -1081,7 +1153,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>64</v>
       </c>
@@ -1089,7 +1161,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>65</v>
       </c>
@@ -1097,7 +1169,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>67</v>
       </c>
@@ -1105,7 +1177,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>68</v>
       </c>
@@ -1113,7 +1185,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>69</v>
       </c>
@@ -1121,7 +1193,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>91</v>
       </c>
@@ -1129,7 +1201,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>92</v>
       </c>
@@ -1137,7 +1209,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>93</v>
       </c>
@@ -1145,7 +1217,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>94</v>
       </c>
@@ -1153,7 +1225,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>95</v>
       </c>
@@ -1161,7 +1233,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>96</v>
       </c>
@@ -1169,7 +1241,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>97</v>
       </c>
@@ -1177,7 +1249,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>98</v>
       </c>
@@ -1185,7 +1257,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>100</v>
       </c>
@@ -1193,7 +1265,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>101</v>
       </c>
@@ -1201,7 +1273,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>102</v>
       </c>
@@ -1209,7 +1281,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>103</v>
       </c>
@@ -1217,7 +1289,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -1225,7 +1297,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>54</v>
       </c>
@@ -1233,7 +1305,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>55</v>
       </c>
@@ -1241,7 +1313,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>66</v>
       </c>
@@ -1249,7 +1321,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>73</v>
       </c>
@@ -1257,7 +1329,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>75</v>
       </c>
@@ -1265,7 +1337,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>76</v>
       </c>
@@ -1273,7 +1345,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>77</v>
       </c>
@@ -1281,7 +1353,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>78</v>
       </c>
@@ -1289,7 +1361,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>79</v>
       </c>
@@ -1297,7 +1369,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>80</v>
       </c>
@@ -1305,7 +1377,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>82</v>
       </c>
@@ -1313,7 +1385,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>83</v>
       </c>
@@ -1321,7 +1393,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>84</v>
       </c>
@@ -1329,7 +1401,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>85</v>
       </c>
@@ -1346,9 +1418,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7257C8B-1D24-4D66-A83C-B8897642E3C4}">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>33</v>
       </c>
@@ -1356,7 +1428,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -1364,7 +1436,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>37</v>
       </c>
@@ -1381,12 +1453,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6610AEAF-E772-4D88-8C2B-5DD0E0FA07BD}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>29</v>
       </c>
@@ -1398,7 +1470,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -1406,7 +1478,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -1414,7 +1486,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -1422,7 +1494,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -1442,12 +1514,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C5481AA-55DD-41F0-8076-D4F5ED7BA00E}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -1455,7 +1527,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1463,12 +1535,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1476,7 +1548,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1484,7 +1556,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1492,7 +1564,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1500,7 +1572,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1508,7 +1580,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1516,7 +1588,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1524,7 +1596,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1532,7 +1604,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -1540,7 +1612,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -1548,7 +1620,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -1573,9 +1645,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DADB64C-1560-4418-AEF8-AFB915F63B31}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1597,15 +1669,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -1782,6 +1845,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>
@@ -1794,14 +1866,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1818,4 +1882,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -1,38 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M346157\Documents\GCOH-Tickets-for-Processing\GCOH Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4AFD18E-7F1B-48E2-9847-EBA03C5000B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68DC9A48-5432-4257-B9CF-FA8FD505A66A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="26265" yWindow="825" windowWidth="10545" windowHeight="13170" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet5" sheetId="12" r:id="rId2"/>
-    <sheet name="Sheet4" sheetId="11" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="10" r:id="rId4"/>
-    <sheet name="Sheet2" sheetId="9" r:id="rId5"/>
-    <sheet name="Sheet1" sheetId="7" r:id="rId6"/>
-    <sheet name="Pierre to do" sheetId="8" r:id="rId7"/>
+    <sheet name="Sheet6" sheetId="13" r:id="rId2"/>
+    <sheet name="Sheet5" sheetId="12" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="11" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="10" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="9" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="7" r:id="rId7"/>
+    <sheet name="Pierre to do" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MDGF!$A$1:$B$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Sheet1!$A$5:$B$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Sheet1!$A$5:$B$5</definedName>
     <definedName name="ID" localSheetId="0" hidden="1">"a5f5822f-2145-4cc3-aa32-d164ed237772"</definedName>
-    <definedName name="ID" localSheetId="6" hidden="1">"2b5e4bcf-a0bb-4962-aef7-0fa656cb902f"</definedName>
-    <definedName name="ID" localSheetId="5" hidden="1">"fff7d4e2-cafa-4da0-a3ee-fa93757f1b68"</definedName>
-    <definedName name="ID" localSheetId="4" hidden="1">"d59c0fca-ea81-453e-b1af-313ab178d2df"</definedName>
-    <definedName name="ID" localSheetId="3" hidden="1">"78c1409c-f389-4bdf-b04b-8c605d40ec4a"</definedName>
-    <definedName name="ID" localSheetId="2" hidden="1">"4893a801-c8f4-43e0-8b40-4123b65c3b6f"</definedName>
-    <definedName name="ID" localSheetId="1" hidden="1">"bab6acb3-5d16-4394-984a-d708b37c40df"</definedName>
+    <definedName name="ID" localSheetId="7" hidden="1">"2b5e4bcf-a0bb-4962-aef7-0fa656cb902f"</definedName>
+    <definedName name="ID" localSheetId="6" hidden="1">"fff7d4e2-cafa-4da0-a3ee-fa93757f1b68"</definedName>
+    <definedName name="ID" localSheetId="5" hidden="1">"d59c0fca-ea81-453e-b1af-313ab178d2df"</definedName>
+    <definedName name="ID" localSheetId="4" hidden="1">"78c1409c-f389-4bdf-b04b-8c605d40ec4a"</definedName>
+    <definedName name="ID" localSheetId="3" hidden="1">"4893a801-c8f4-43e0-8b40-4123b65c3b6f"</definedName>
+    <definedName name="ID" localSheetId="2" hidden="1">"bab6acb3-5d16-4394-984a-d708b37c40df"</definedName>
   </definedNames>
-  <calcPr calcId="181029" calcCompleted="0" calcOnSave="0" concurrentCalc="0"/>
+  <calcPr calcId="181029" calcOnSave="0" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="118">
   <si>
     <t>Child</t>
   </si>
@@ -372,21 +373,6 @@
   </si>
   <si>
     <t>THS1OF0110</t>
-  </si>
-  <si>
-    <t>BE50GLE300</t>
-  </si>
-  <si>
-    <t>JP02GLE302</t>
-  </si>
-  <si>
-    <t>KR02GLE005</t>
-  </si>
-  <si>
-    <t>TW02GLE006</t>
-  </si>
-  <si>
-    <t>TW03GLE006</t>
   </si>
   <si>
     <t>2057GLE006</t>
@@ -475,9 +461,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -515,7 +501,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -621,7 +607,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -763,7 +749,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -772,15 +758,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -788,124 +774,68 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>109</v>
       </c>
       <c r="B2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="B3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B5" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="B9" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B10" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
         <v>117</v>
-      </c>
-      <c r="B11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>118</v>
-      </c>
-      <c r="B12" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>104</v>
-      </c>
-      <c r="B13" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>107</v>
-      </c>
-      <c r="B14" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>108</v>
-      </c>
-      <c r="B15" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>107</v>
-      </c>
-      <c r="B16" t="s">
-        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -919,24 +849,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEFFB296-0EDE-4DB3-9556-9CC7179143E5}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59ACF2BE-4EA3-4BA6-9064-75F76A13BE50}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B2" t="s">
-        <v>57</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -945,15 +867,41 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEFFB296-0EDE-4DB3-9556-9CC7179143E5}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B00A0FC-D79D-4B10-944D-C6C9BF412C7A}">
   <dimension ref="A1:B59"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>43</v>
       </c>
@@ -961,7 +909,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>60</v>
       </c>
@@ -969,7 +917,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>62</v>
       </c>
@@ -977,7 +925,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>52</v>
       </c>
@@ -985,7 +933,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>56</v>
       </c>
@@ -993,7 +941,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>58</v>
       </c>
@@ -1001,7 +949,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>81</v>
       </c>
@@ -1009,7 +957,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>99</v>
       </c>
@@ -1017,7 +965,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>70</v>
       </c>
@@ -1025,7 +973,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>72</v>
       </c>
@@ -1033,7 +981,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>45</v>
       </c>
@@ -1041,7 +989,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>47</v>
       </c>
@@ -1049,7 +997,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>48</v>
       </c>
@@ -1057,7 +1005,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>49</v>
       </c>
@@ -1065,7 +1013,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>59</v>
       </c>
@@ -1073,7 +1021,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>74</v>
       </c>
@@ -1081,7 +1029,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>86</v>
       </c>
@@ -1089,7 +1037,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>87</v>
       </c>
@@ -1097,7 +1045,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>88</v>
       </c>
@@ -1105,7 +1053,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>89</v>
       </c>
@@ -1113,7 +1061,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>90</v>
       </c>
@@ -1121,7 +1069,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -1129,7 +1077,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>41</v>
       </c>
@@ -1137,7 +1085,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>42</v>
       </c>
@@ -1145,7 +1093,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -1153,7 +1101,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>64</v>
       </c>
@@ -1161,7 +1109,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>65</v>
       </c>
@@ -1169,7 +1117,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>67</v>
       </c>
@@ -1177,7 +1125,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>68</v>
       </c>
@@ -1185,7 +1133,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>69</v>
       </c>
@@ -1193,7 +1141,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>91</v>
       </c>
@@ -1201,7 +1149,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>92</v>
       </c>
@@ -1209,7 +1157,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>93</v>
       </c>
@@ -1217,7 +1165,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>94</v>
       </c>
@@ -1225,7 +1173,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>95</v>
       </c>
@@ -1233,7 +1181,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>96</v>
       </c>
@@ -1241,7 +1189,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>97</v>
       </c>
@@ -1249,7 +1197,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>98</v>
       </c>
@@ -1257,7 +1205,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>100</v>
       </c>
@@ -1265,7 +1213,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>101</v>
       </c>
@@ -1273,7 +1221,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>102</v>
       </c>
@@ -1281,7 +1229,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>103</v>
       </c>
@@ -1289,7 +1237,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -1297,7 +1245,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>54</v>
       </c>
@@ -1305,7 +1253,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>55</v>
       </c>
@@ -1313,7 +1261,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>66</v>
       </c>
@@ -1321,7 +1269,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>73</v>
       </c>
@@ -1329,7 +1277,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>75</v>
       </c>
@@ -1337,7 +1285,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>76</v>
       </c>
@@ -1345,7 +1293,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>77</v>
       </c>
@@ -1353,7 +1301,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>78</v>
       </c>
@@ -1361,7 +1309,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>79</v>
       </c>
@@ -1369,7 +1317,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>80</v>
       </c>
@@ -1377,7 +1325,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>82</v>
       </c>
@@ -1385,7 +1333,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>83</v>
       </c>
@@ -1393,7 +1341,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>84</v>
       </c>
@@ -1401,7 +1349,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>85</v>
       </c>
@@ -1415,12 +1363,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7257C8B-1D24-4D66-A83C-B8897642E3C4}">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>33</v>
       </c>
@@ -1428,7 +1376,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -1436,7 +1384,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>37</v>
       </c>
@@ -1449,16 +1397,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6610AEAF-E772-4D88-8C2B-5DD0E0FA07BD}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>29</v>
       </c>
@@ -1470,7 +1418,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -1478,7 +1426,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -1486,7 +1434,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -1494,7 +1442,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -1510,16 +1458,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C5481AA-55DD-41F0-8076-D4F5ED7BA00E}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -1527,7 +1475,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1535,12 +1483,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1548,7 +1496,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1556,7 +1504,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1564,7 +1512,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1572,7 +1520,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1580,7 +1528,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1588,7 +1536,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1596,7 +1544,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1604,7 +1552,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -1612,7 +1560,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -1620,7 +1568,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -1641,13 +1589,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DADB64C-1560-4418-AEF8-AFB915F63B31}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1658,14 +1606,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1846,21 +1792,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
-    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1885,9 +1830,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
+    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68DC9A48-5432-4257-B9CF-FA8FD505A66A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEA3BE22-81B4-4E1A-AAB1-BA9DE4CB7050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26265" yWindow="825" windowWidth="10545" windowHeight="13170" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="20985" yWindow="4005" windowWidth="13680" windowHeight="13170" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="112">
   <si>
     <t>Child</t>
   </si>
@@ -375,28 +375,10 @@
     <t>THS1OF0110</t>
   </si>
   <si>
-    <t>2057GLE006</t>
-  </si>
-  <si>
     <t>KR03GLE005</t>
   </si>
   <si>
-    <t>TW10GLE106</t>
-  </si>
-  <si>
-    <t>TW91GLE106</t>
-  </si>
-  <si>
-    <t>DE10620801</t>
-  </si>
-  <si>
-    <t>G000001104</t>
-  </si>
-  <si>
     <t>G000001103</t>
-  </si>
-  <si>
-    <t>G000000432</t>
   </si>
   <si>
     <t>GNMI000720</t>
@@ -758,7 +740,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -776,66 +758,34 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B3" t="s">
         <v>111</v>
-      </c>
-      <c r="B3" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B5" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>107</v>
-      </c>
-      <c r="B7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>108</v>
-      </c>
-      <c r="B8" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>107</v>
-      </c>
-      <c r="B9" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -855,10 +805,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" t="s">
         <v>110</v>
-      </c>
-      <c r="B1" t="s">
-        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -1606,12 +1556,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1792,20 +1744,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
+    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1830,12 +1783,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
-    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEA3BE22-81B4-4E1A-AAB1-BA9DE4CB7050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9939EAB9-7A6B-40D5-9F2B-2414C0456DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20985" yWindow="4005" windowWidth="13680" windowHeight="13170" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="122">
   <si>
     <t>Child</t>
   </si>
@@ -360,28 +360,58 @@
     <t>JP01Z03725</t>
   </si>
   <si>
-    <t>CNS1OF0144</t>
-  </si>
-  <si>
     <t>DES1OFCX20</t>
   </si>
   <si>
     <t>DES1OFCX21</t>
   </si>
   <si>
-    <t>MYS1OF0110</t>
-  </si>
-  <si>
-    <t>THS1OF0110</t>
-  </si>
-  <si>
     <t>KR03GLE005</t>
   </si>
   <si>
     <t>G000001103</t>
   </si>
   <si>
-    <t>GNMI000720</t>
+    <t>TW91PD1010</t>
+  </si>
+  <si>
+    <t>US10C05025</t>
+  </si>
+  <si>
+    <t>KR15C01027</t>
+  </si>
+  <si>
+    <t>KR16C01027</t>
+  </si>
+  <si>
+    <t>CN09C05003</t>
+  </si>
+  <si>
+    <t>NL10C05001</t>
+  </si>
+  <si>
+    <t>MY10C05000</t>
+  </si>
+  <si>
+    <t>TW02C00311</t>
+  </si>
+  <si>
+    <t>P000000801</t>
+  </si>
+  <si>
+    <t>P000000533</t>
+  </si>
+  <si>
+    <t>P000000802</t>
+  </si>
+  <si>
+    <t>P000000829</t>
+  </si>
+  <si>
+    <t>P000000534</t>
+  </si>
+  <si>
+    <t>P000000954</t>
   </si>
 </sst>
 </file>
@@ -740,7 +770,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -758,34 +788,66 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>114</v>
+      </c>
+      <c r="B8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -805,10 +867,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -823,7 +885,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B1" t="s">
         <v>57</v>
@@ -831,7 +893,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B2" t="s">
         <v>57</v>
@@ -1556,14 +1618,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1744,21 +1804,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
-    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1783,9 +1842,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
+    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9939EAB9-7A6B-40D5-9F2B-2414C0456DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E1E3EF9-8014-414D-B5F2-4299DB167888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="116">
   <si>
     <t>Child</t>
   </si>
@@ -372,46 +372,28 @@
     <t>G000001103</t>
   </si>
   <si>
-    <t>TW91PD1010</t>
-  </si>
-  <si>
-    <t>US10C05025</t>
-  </si>
-  <si>
-    <t>KR15C01027</t>
-  </si>
-  <si>
-    <t>KR16C01027</t>
-  </si>
-  <si>
-    <t>CN09C05003</t>
-  </si>
-  <si>
-    <t>NL10C05001</t>
-  </si>
-  <si>
-    <t>MY10C05000</t>
-  </si>
-  <si>
-    <t>TW02C00311</t>
-  </si>
-  <si>
-    <t>P000000801</t>
-  </si>
-  <si>
-    <t>P000000533</t>
-  </si>
-  <si>
-    <t>P000000802</t>
-  </si>
-  <si>
-    <t>P000000829</t>
-  </si>
-  <si>
-    <t>P000000534</t>
-  </si>
-  <si>
-    <t>P000000954</t>
+    <t>DE65GIT032</t>
+  </si>
+  <si>
+    <t>SG09GBT020</t>
+  </si>
+  <si>
+    <t>2128GIT020</t>
+  </si>
+  <si>
+    <t>G000000256</t>
+  </si>
+  <si>
+    <t>G000000279</t>
+  </si>
+  <si>
+    <t>G000000218</t>
+  </si>
+  <si>
+    <t>G000000199</t>
+  </si>
+  <si>
+    <t>P000001045</t>
   </si>
 </sst>
 </file>
@@ -770,11 +752,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -788,66 +769,82 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>108</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B4" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B5" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="B6" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="B7" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="B8" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>115</v>
+        <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>121</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B11" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1618,12 +1615,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1804,20 +1803,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
+    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1842,12 +1842,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
-    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDFDDF24-56F7-4999-9265-02E8144C1363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33A401D4-73E2-4200-AAAC-77FC5E2957B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <definedName name="ID" localSheetId="0" hidden="1">"a5f5822f-2145-4cc3-aa32-d164ed237772"</definedName>
     <definedName name="ID" localSheetId="1" hidden="1">"2b5e4bcf-a0bb-4962-aef7-0fa656cb902f"</definedName>
   </definedNames>
-  <calcPr calcId="181029" calcOnSave="0" concurrentCalc="0"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
   <si>
     <t>Child</t>
   </si>
@@ -42,34 +42,52 @@
     <t>Parent</t>
   </si>
   <si>
-    <t>JP01C0M825</t>
-  </si>
-  <si>
-    <t>JP01GBT305</t>
-  </si>
-  <si>
-    <t>JP01GHR301</t>
-  </si>
-  <si>
-    <t>CH50L95005</t>
-  </si>
-  <si>
-    <t>CH50L95009</t>
-  </si>
-  <si>
-    <t>DE50OF0124</t>
-  </si>
-  <si>
-    <t>H000001095</t>
-  </si>
-  <si>
-    <t>P000000742</t>
-  </si>
-  <si>
-    <t>G000000244</t>
-  </si>
-  <si>
-    <t>G000000198</t>
+    <t>DE10Z01000</t>
+  </si>
+  <si>
+    <t>CN90Z01000</t>
+  </si>
+  <si>
+    <t>ES50Z01000</t>
+  </si>
+  <si>
+    <t>CN03Z01000</t>
+  </si>
+  <si>
+    <t>IN01Z01000</t>
+  </si>
+  <si>
+    <t>SG09Z01000</t>
+  </si>
+  <si>
+    <t>CN01Z01000</t>
+  </si>
+  <si>
+    <t>DE04Z01000</t>
+  </si>
+  <si>
+    <t>G000000242</t>
+  </si>
+  <si>
+    <t>G000000759</t>
+  </si>
+  <si>
+    <t>H000000887</t>
+  </si>
+  <si>
+    <t>O000000006</t>
+  </si>
+  <si>
+    <t>P000001045</t>
+  </si>
+  <si>
+    <t>US01Z01000</t>
+  </si>
+  <si>
+    <t>TW02Z01000</t>
+  </si>
+  <si>
+    <t>P000000534</t>
   </si>
 </sst>
 </file>
@@ -428,7 +446,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="12" bestFit="1" customWidth="1"/>
@@ -445,50 +463,82 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -518,12 +568,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -704,20 +756,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
+    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -742,12 +795,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
-    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33A401D4-73E2-4200-AAAC-77FC5E2957B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D53B6C33-BDED-4FAD-863D-D18593FF936C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="19065" yWindow="4620" windowWidth="19185" windowHeight="13170" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
   <si>
     <t>Child</t>
   </si>
@@ -42,52 +42,79 @@
     <t>Parent</t>
   </si>
   <si>
-    <t>DE10Z01000</t>
-  </si>
-  <si>
-    <t>CN90Z01000</t>
-  </si>
-  <si>
-    <t>ES50Z01000</t>
-  </si>
-  <si>
-    <t>CN03Z01000</t>
-  </si>
-  <si>
-    <t>IN01Z01000</t>
-  </si>
-  <si>
-    <t>SG09Z01000</t>
-  </si>
-  <si>
-    <t>CN01Z01000</t>
-  </si>
-  <si>
-    <t>DE04Z01000</t>
-  </si>
-  <si>
-    <t>G000000242</t>
-  </si>
-  <si>
-    <t>G000000759</t>
-  </si>
-  <si>
-    <t>H000000887</t>
-  </si>
-  <si>
-    <t>O000000006</t>
-  </si>
-  <si>
-    <t>P000001045</t>
-  </si>
-  <si>
-    <t>US01Z01000</t>
-  </si>
-  <si>
-    <t>TW02Z01000</t>
-  </si>
-  <si>
-    <t>P000000534</t>
+    <t>DE65GIT032</t>
+  </si>
+  <si>
+    <t>DE10695300</t>
+  </si>
+  <si>
+    <t>DE10GMS070</t>
+  </si>
+  <si>
+    <t>DE10669638</t>
+  </si>
+  <si>
+    <t>1937OF0002</t>
+  </si>
+  <si>
+    <t>2123GMS080</t>
+  </si>
+  <si>
+    <t>2123GMS050</t>
+  </si>
+  <si>
+    <t>US10GIT050</t>
+  </si>
+  <si>
+    <t>2034L81000</t>
+  </si>
+  <si>
+    <t>2102TMCZ91</t>
+  </si>
+  <si>
+    <t>DE10B04453</t>
+  </si>
+  <si>
+    <t>DE10B14453</t>
+  </si>
+  <si>
+    <t>2102TMCZ90</t>
+  </si>
+  <si>
+    <t>1937TMCZ95</t>
+  </si>
+  <si>
+    <t>G000000256</t>
+  </si>
+  <si>
+    <t>L000013894</t>
+  </si>
+  <si>
+    <t>G000001442</t>
+  </si>
+  <si>
+    <t>G000001441</t>
+  </si>
+  <si>
+    <t>L000013395</t>
+  </si>
+  <si>
+    <t>G000001443</t>
+  </si>
+  <si>
+    <t>P000000765</t>
+  </si>
+  <si>
+    <t>L000012735</t>
+  </si>
+  <si>
+    <t>L000013454</t>
+  </si>
+  <si>
+    <t>L000013866</t>
+  </si>
+  <si>
+    <t>L000013867</t>
   </si>
 </sst>
 </file>
@@ -446,7 +473,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="12" bestFit="1" customWidth="1"/>
@@ -466,7 +493,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -474,7 +501,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -482,7 +509,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -490,7 +517,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -498,7 +525,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -506,7 +533,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -514,7 +541,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -522,23 +549,55 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -579,6 +638,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -755,15 +823,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>
@@ -776,6 +835,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -792,12 +859,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D53B6C33-BDED-4FAD-863D-D18593FF936C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE7B6A1B-B913-4FAA-86C2-A97765CFED3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19065" yWindow="4620" windowWidth="19185" windowHeight="13170" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
   <si>
     <t>Child</t>
   </si>
@@ -42,79 +42,40 @@
     <t>Parent</t>
   </si>
   <si>
-    <t>DE65GIT032</t>
-  </si>
-  <si>
-    <t>DE10695300</t>
-  </si>
-  <si>
-    <t>DE10GMS070</t>
-  </si>
-  <si>
-    <t>DE10669638</t>
-  </si>
-  <si>
-    <t>1937OF0002</t>
-  </si>
-  <si>
-    <t>2123GMS080</t>
-  </si>
-  <si>
-    <t>2123GMS050</t>
-  </si>
-  <si>
-    <t>US10GIT050</t>
-  </si>
-  <si>
-    <t>2034L81000</t>
-  </si>
-  <si>
-    <t>2102TMCZ91</t>
-  </si>
-  <si>
-    <t>DE10B04453</t>
-  </si>
-  <si>
-    <t>DE10B14453</t>
-  </si>
-  <si>
-    <t>2102TMCZ90</t>
-  </si>
-  <si>
-    <t>1937TMCZ95</t>
-  </si>
-  <si>
-    <t>G000000256</t>
-  </si>
-  <si>
-    <t>L000013894</t>
-  </si>
-  <si>
-    <t>G000001442</t>
-  </si>
-  <si>
-    <t>G000001441</t>
-  </si>
-  <si>
-    <t>L000013395</t>
-  </si>
-  <si>
-    <t>G000001443</t>
-  </si>
-  <si>
-    <t>P000000765</t>
-  </si>
-  <si>
-    <t>L000012735</t>
-  </si>
-  <si>
-    <t>L000013454</t>
-  </si>
-  <si>
-    <t>L000013866</t>
-  </si>
-  <si>
-    <t>L000013867</t>
+    <t>DE10Z01000</t>
+  </si>
+  <si>
+    <t>CN90Z01000</t>
+  </si>
+  <si>
+    <t>ES50Z01000</t>
+  </si>
+  <si>
+    <t>CN03Z01000</t>
+  </si>
+  <si>
+    <t>IN01Z01000</t>
+  </si>
+  <si>
+    <t>SG09Z01000</t>
+  </si>
+  <si>
+    <t>CN01Z01000</t>
+  </si>
+  <si>
+    <t>DE04Z01000</t>
+  </si>
+  <si>
+    <t>KR03Z01000</t>
+  </si>
+  <si>
+    <t>US01Z01000</t>
+  </si>
+  <si>
+    <t>TW02Z01000</t>
+  </si>
+  <si>
+    <t>P000000427</t>
   </si>
 </sst>
 </file>
@@ -473,7 +434,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="12" bestFit="1" customWidth="1"/>
@@ -493,7 +454,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -501,7 +462,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -509,7 +470,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -517,7 +478,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -525,7 +486,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -533,7 +494,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -541,7 +502,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -549,55 +510,31 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -638,15 +575,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -823,6 +751,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>
@@ -835,14 +772,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -859,4 +788,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M346157\Documents\GCOH-Tickets-for-Processing\GCOH-Tickets-for-Processing\GCOH-Tickets-for-Processing\GCOH-Tickets-for-Processing\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE7B6A1B-B913-4FAA-86C2-A97765CFED3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C31AD03-844F-4F2C-9BDF-CCC6DCAD7D27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="17280" windowHeight="8880" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -21,10 +21,21 @@
     <definedName name="ID" localSheetId="0" hidden="1">"a5f5822f-2145-4cc3-aa32-d164ed237772"</definedName>
     <definedName name="ID" localSheetId="1" hidden="1">"2b5e4bcf-a0bb-4962-aef7-0fa656cb902f"</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -34,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Child</t>
   </si>
@@ -42,40 +53,16 @@
     <t>Parent</t>
   </si>
   <si>
-    <t>DE10Z01000</t>
+    <t>FI50R00004</t>
   </si>
   <si>
-    <t>CN90Z01000</t>
+    <t>FI50R00009</t>
   </si>
   <si>
-    <t>ES50Z01000</t>
+    <t>H000000729</t>
   </si>
   <si>
-    <t>CN03Z01000</t>
-  </si>
-  <si>
-    <t>IN01Z01000</t>
-  </si>
-  <si>
-    <t>SG09Z01000</t>
-  </si>
-  <si>
-    <t>CN01Z01000</t>
-  </si>
-  <si>
-    <t>DE04Z01000</t>
-  </si>
-  <si>
-    <t>KR03Z01000</t>
-  </si>
-  <si>
-    <t>US01Z01000</t>
-  </si>
-  <si>
-    <t>TW02Z01000</t>
-  </si>
-  <si>
-    <t>P000000427</t>
+    <t>H000000803</t>
   </si>
 </sst>
 </file>
@@ -137,9 +124,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -177,7 +164,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -283,7 +270,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -425,7 +412,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -434,14 +421,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -449,92 +436,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
         <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -551,9 +466,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DADB64C-1560-4418-AEF8-AFB915F63B31}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -564,17 +479,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -751,6 +655,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -761,17 +676,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
-    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -790,6 +694,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
+    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
   <ds:schemaRefs>

--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M346157\Documents\GCOH-Tickets-for-Processing\GCOH-Tickets-for-Processing\GCOH-Tickets-for-Processing\GCOH-Tickets-for-Processing\GCOH Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C31AD03-844F-4F2C-9BDF-CCC6DCAD7D27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EDD60AD-1848-4DD8-BD1B-40FA5EA58458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="732" windowWidth="17280" windowHeight="8880" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="32">
   <si>
     <t>Child</t>
   </si>
@@ -53,16 +53,94 @@
     <t>Parent</t>
   </si>
   <si>
-    <t>FI50R00004</t>
-  </si>
-  <si>
-    <t>FI50R00009</t>
-  </si>
-  <si>
-    <t>H000000729</t>
-  </si>
-  <si>
-    <t>H000000803</t>
+    <t>2053R00001</t>
+  </si>
+  <si>
+    <t>2123R00004</t>
+  </si>
+  <si>
+    <t>DE01TAWA03</t>
+  </si>
+  <si>
+    <t>DE01TAWA04</t>
+  </si>
+  <si>
+    <t>DE01TAWA10</t>
+  </si>
+  <si>
+    <t>DE01TAWA20</t>
+  </si>
+  <si>
+    <t>DE01TAWA31</t>
+  </si>
+  <si>
+    <t>DE01TAWA32</t>
+  </si>
+  <si>
+    <t>DE01TAWA40</t>
+  </si>
+  <si>
+    <t>DE01TAWA50</t>
+  </si>
+  <si>
+    <t>DE01TAWA53</t>
+  </si>
+  <si>
+    <t>DE01TAWA61</t>
+  </si>
+  <si>
+    <t>DE01TAWA62</t>
+  </si>
+  <si>
+    <t>DE01TAWA63</t>
+  </si>
+  <si>
+    <t>DE01TAWA64</t>
+  </si>
+  <si>
+    <t>DE01TAWA70</t>
+  </si>
+  <si>
+    <t>DE01TAWA73</t>
+  </si>
+  <si>
+    <t>DE01TAWA74</t>
+  </si>
+  <si>
+    <t>DE01TAWA80</t>
+  </si>
+  <si>
+    <t>DE01TAWA84</t>
+  </si>
+  <si>
+    <t>DE01TAWA90</t>
+  </si>
+  <si>
+    <t>DE01TAWA93</t>
+  </si>
+  <si>
+    <t>PL10K01000</t>
+  </si>
+  <si>
+    <t>PL10K02000</t>
+  </si>
+  <si>
+    <t>PL10K03000</t>
+  </si>
+  <si>
+    <t>L000009171</t>
+  </si>
+  <si>
+    <t>P000000240</t>
+  </si>
+  <si>
+    <t>H000004594</t>
+  </si>
+  <si>
+    <t>H000004593</t>
+  </si>
+  <si>
+    <t>H000004605</t>
   </si>
 </sst>
 </file>
@@ -124,9 +202,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -164,7 +242,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -270,7 +348,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -412,7 +490,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -421,14 +499,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -436,20 +514,204 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -466,9 +728,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DADB64C-1560-4418-AEF8-AFB915F63B31}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -656,6 +918,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
@@ -664,15 +935,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -695,6 +957,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -703,12 +973,4 @@
     <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,34 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EDD60AD-1848-4DD8-BD1B-40FA5EA58458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F58EC4-1518-42AB-B0EA-F792FA6EBFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="25140" yWindow="1650" windowWidth="12060" windowHeight="13170" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
-    <sheet name="Pierre to do" sheetId="8" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="9" r:id="rId2"/>
+    <sheet name="Pierre to do" sheetId="8" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MDGF!$A$1:$B$1</definedName>
     <definedName name="ID" localSheetId="0" hidden="1">"a5f5822f-2145-4cc3-aa32-d164ed237772"</definedName>
-    <definedName name="ID" localSheetId="1" hidden="1">"2b5e4bcf-a0bb-4962-aef7-0fa656cb902f"</definedName>
+    <definedName name="ID" localSheetId="2" hidden="1">"2b5e4bcf-a0bb-4962-aef7-0fa656cb902f"</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -45,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
   <si>
     <t>Child</t>
   </si>
@@ -53,94 +43,49 @@
     <t>Parent</t>
   </si>
   <si>
-    <t>2053R00001</t>
-  </si>
-  <si>
-    <t>2123R00004</t>
-  </si>
-  <si>
-    <t>DE01TAWA03</t>
-  </si>
-  <si>
-    <t>DE01TAWA04</t>
-  </si>
-  <si>
-    <t>DE01TAWA10</t>
-  </si>
-  <si>
-    <t>DE01TAWA20</t>
-  </si>
-  <si>
-    <t>DE01TAWA31</t>
-  </si>
-  <si>
-    <t>DE01TAWA32</t>
-  </si>
-  <si>
-    <t>DE01TAWA40</t>
-  </si>
-  <si>
-    <t>DE01TAWA50</t>
-  </si>
-  <si>
-    <t>DE01TAWA53</t>
-  </si>
-  <si>
-    <t>DE01TAWA61</t>
-  </si>
-  <si>
-    <t>DE01TAWA62</t>
-  </si>
-  <si>
-    <t>DE01TAWA63</t>
-  </si>
-  <si>
-    <t>DE01TAWA64</t>
-  </si>
-  <si>
-    <t>DE01TAWA70</t>
-  </si>
-  <si>
-    <t>DE01TAWA73</t>
-  </si>
-  <si>
-    <t>DE01TAWA74</t>
-  </si>
-  <si>
-    <t>DE01TAWA80</t>
-  </si>
-  <si>
-    <t>DE01TAWA84</t>
-  </si>
-  <si>
-    <t>DE01TAWA90</t>
-  </si>
-  <si>
-    <t>DE01TAWA93</t>
-  </si>
-  <si>
-    <t>PL10K01000</t>
-  </si>
-  <si>
-    <t>PL10K02000</t>
-  </si>
-  <si>
-    <t>PL10K03000</t>
-  </si>
-  <si>
-    <t>L000009171</t>
-  </si>
-  <si>
-    <t>P000000240</t>
-  </si>
-  <si>
-    <t>H000004594</t>
-  </si>
-  <si>
-    <t>H000004593</t>
-  </si>
-  <si>
-    <t>H000004605</t>
+    <t>DE10TM2000</t>
+  </si>
+  <si>
+    <t>DE10TM4000</t>
+  </si>
+  <si>
+    <t>DE10DB3600</t>
+  </si>
+  <si>
+    <t>DE10TQ1001</t>
+  </si>
+  <si>
+    <t>DE10TQ1002</t>
+  </si>
+  <si>
+    <t>DE10TQ1003</t>
+  </si>
+  <si>
+    <t>GB10TQ1000</t>
+  </si>
+  <si>
+    <t>IT07TQ1001</t>
+  </si>
+  <si>
+    <t>IT07TQ1002</t>
+  </si>
+  <si>
+    <t>NL10TQ1000</t>
+  </si>
+  <si>
+    <t>DE04TQHQ19</t>
+  </si>
+  <si>
+    <t>DE04TQHQ23</t>
+  </si>
+  <si>
+    <t>NL10TM3000</t>
+  </si>
+  <si>
+    <t>P000001333</t>
+  </si>
+  <si>
+    <t>P000001334</t>
   </si>
 </sst>
 </file>
@@ -499,7 +444,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="12" bestFit="1" customWidth="1"/>
@@ -516,202 +461,58 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
         <v>16</v>
-      </c>
-      <c r="B16" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -725,6 +526,51 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D90D0C8-3F43-4D3D-BF40-FECE7407BA39}">
+  <dimension ref="A1:A7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DADB64C-1560-4418-AEF8-AFB915F63B31}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1"/>
@@ -918,15 +764,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
@@ -935,6 +772,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -957,14 +803,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -973,4 +811,12 @@
     <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M346157\Documents\GCOH-Tickets-for-Processing\GCOH-Tickets-for-Processing\GCOH-Tickets-for-Processing\GCOH-Tickets-for-Processing\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EDD60AD-1848-4DD8-BD1B-40FA5EA58458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B18B109A-3313-4194-87DF-82ED46F10D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
   <si>
     <t>Child</t>
   </si>
@@ -53,94 +53,79 @@
     <t>Parent</t>
   </si>
   <si>
-    <t>2053R00001</t>
-  </si>
-  <si>
-    <t>2123R00004</t>
-  </si>
-  <si>
-    <t>DE01TAWA03</t>
-  </si>
-  <si>
-    <t>DE01TAWA04</t>
-  </si>
-  <si>
-    <t>DE01TAWA10</t>
-  </si>
-  <si>
-    <t>DE01TAWA20</t>
-  </si>
-  <si>
-    <t>DE01TAWA31</t>
-  </si>
-  <si>
-    <t>DE01TAWA32</t>
-  </si>
-  <si>
-    <t>DE01TAWA40</t>
-  </si>
-  <si>
-    <t>DE01TAWA50</t>
-  </si>
-  <si>
-    <t>DE01TAWA53</t>
-  </si>
-  <si>
-    <t>DE01TAWA61</t>
-  </si>
-  <si>
-    <t>DE01TAWA62</t>
-  </si>
-  <si>
-    <t>DE01TAWA63</t>
-  </si>
-  <si>
-    <t>DE01TAWA64</t>
-  </si>
-  <si>
-    <t>DE01TAWA70</t>
-  </si>
-  <si>
-    <t>DE01TAWA73</t>
-  </si>
-  <si>
-    <t>DE01TAWA74</t>
-  </si>
-  <si>
-    <t>DE01TAWA80</t>
-  </si>
-  <si>
-    <t>DE01TAWA84</t>
-  </si>
-  <si>
-    <t>DE01TAWA90</t>
-  </si>
-  <si>
-    <t>DE01TAWA93</t>
-  </si>
-  <si>
-    <t>PL10K01000</t>
-  </si>
-  <si>
-    <t>PL10K02000</t>
-  </si>
-  <si>
-    <t>PL10K03000</t>
-  </si>
-  <si>
-    <t>L000009171</t>
-  </si>
-  <si>
-    <t>P000000240</t>
-  </si>
-  <si>
-    <t>H000004594</t>
-  </si>
-  <si>
-    <t>H000004593</t>
-  </si>
-  <si>
-    <t>H000004605</t>
+    <t>DE01TQWI03</t>
+  </si>
+  <si>
+    <t>DE04TQHQ15</t>
+  </si>
+  <si>
+    <t>DE04TQHQ16</t>
+  </si>
+  <si>
+    <t>DE10TM2000</t>
+  </si>
+  <si>
+    <t>IL10TM2000</t>
+  </si>
+  <si>
+    <t>IT07TM2000</t>
+  </si>
+  <si>
+    <t>NL10TM2000</t>
+  </si>
+  <si>
+    <t>P000001329</t>
+  </si>
+  <si>
+    <t>DE10TM4000</t>
+  </si>
+  <si>
+    <t>DE01TKWI01</t>
+  </si>
+  <si>
+    <t>DE01TQWIGH</t>
+  </si>
+  <si>
+    <t>DE10DB3600</t>
+  </si>
+  <si>
+    <t>DE10TQ1001</t>
+  </si>
+  <si>
+    <t>DE10TQ1002</t>
+  </si>
+  <si>
+    <t>DE10TQ1003</t>
+  </si>
+  <si>
+    <t>GB10TQ1000</t>
+  </si>
+  <si>
+    <t>IT07TQ1001</t>
+  </si>
+  <si>
+    <t>IT07TQ1002</t>
+  </si>
+  <si>
+    <t>NL10TQ1000</t>
+  </si>
+  <si>
+    <t>DE04TQHQ19</t>
+  </si>
+  <si>
+    <t>DE04TQHQ23</t>
+  </si>
+  <si>
+    <t>NL10TM3000</t>
+  </si>
+  <si>
+    <t>P000001331</t>
+  </si>
+  <si>
+    <t>P000001333</t>
+  </si>
+  <si>
+    <t>P000001334</t>
   </si>
 </sst>
 </file>
@@ -202,9 +187,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -242,7 +227,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -348,7 +333,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -490,7 +475,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -499,14 +484,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -514,204 +499,172 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
         <v>26</v>
-      </c>
-      <c r="B26" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -728,9 +681,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DADB64C-1560-4418-AEF8-AFB915F63B31}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -918,15 +871,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
@@ -935,6 +879,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -957,14 +910,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -973,4 +918,12 @@
     <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M346157\Documents\GCOH-Tickets-for-Processing\GCOH-Tickets-for-Processing\GCOH-Tickets-for-Processing\GCOH-Tickets-for-Processing\GCOH Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B18B109A-3313-4194-87DF-82ED46F10D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E1BB881-EDE9-41CB-92A4-485669F2A17B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -187,9 +187,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -227,7 +227,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -333,7 +333,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -475,7 +475,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -485,13 +485,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -499,7 +499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -507,7 +507,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -515,7 +515,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -523,7 +523,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -531,7 +531,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -539,7 +539,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -547,7 +547,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -555,7 +555,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -563,7 +563,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -571,7 +571,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -579,7 +579,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -587,7 +587,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -595,7 +595,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -603,7 +603,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -611,7 +611,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -619,7 +619,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -627,7 +627,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -635,7 +635,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -643,7 +643,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -651,7 +651,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -659,7 +659,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -681,9 +681,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DADB64C-1560-4418-AEF8-AFB915F63B31}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -694,6 +694,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -870,27 +890,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
+    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -907,23 +926,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
-    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E1BB881-EDE9-41CB-92A4-485669F2A17B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E88C24F-F235-42F1-9DD0-BA1999224166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="22050" yWindow="4890" windowWidth="12060" windowHeight="13170" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="30">
   <si>
     <t>Child</t>
   </si>
@@ -53,79 +53,88 @@
     <t>Parent</t>
   </si>
   <si>
-    <t>DE01TQWI03</t>
-  </si>
-  <si>
-    <t>DE04TQHQ15</t>
-  </si>
-  <si>
-    <t>DE04TQHQ16</t>
-  </si>
-  <si>
-    <t>DE10TM2000</t>
-  </si>
-  <si>
-    <t>IL10TM2000</t>
-  </si>
-  <si>
-    <t>IT07TM2000</t>
-  </si>
-  <si>
-    <t>NL10TM2000</t>
-  </si>
-  <si>
-    <t>P000001329</t>
-  </si>
-  <si>
-    <t>DE10TM4000</t>
-  </si>
-  <si>
-    <t>DE01TKWI01</t>
-  </si>
-  <si>
-    <t>DE01TQWIGH</t>
-  </si>
-  <si>
-    <t>DE10DB3600</t>
-  </si>
-  <si>
-    <t>DE10TQ1001</t>
-  </si>
-  <si>
-    <t>DE10TQ1002</t>
-  </si>
-  <si>
-    <t>DE10TQ1003</t>
-  </si>
-  <si>
-    <t>GB10TQ1000</t>
-  </si>
-  <si>
-    <t>IT07TQ1001</t>
-  </si>
-  <si>
-    <t>IT07TQ1002</t>
-  </si>
-  <si>
-    <t>NL10TQ1000</t>
-  </si>
-  <si>
-    <t>DE04TQHQ19</t>
-  </si>
-  <si>
-    <t>DE04TQHQ23</t>
-  </si>
-  <si>
-    <t>NL10TM3000</t>
-  </si>
-  <si>
-    <t>P000001331</t>
-  </si>
-  <si>
-    <t>P000001333</t>
-  </si>
-  <si>
-    <t>P000001334</t>
+    <t>IT50YIT001</t>
+  </si>
+  <si>
+    <t>DE10GIT04K</t>
+  </si>
+  <si>
+    <t>DE10638210</t>
+  </si>
+  <si>
+    <t>DE10GIT101</t>
+  </si>
+  <si>
+    <t>DE10GIT02K</t>
+  </si>
+  <si>
+    <t>DE10669638</t>
+  </si>
+  <si>
+    <t>DE10669636</t>
+  </si>
+  <si>
+    <t>CH65GIT20H</t>
+  </si>
+  <si>
+    <t>2123C00103</t>
+  </si>
+  <si>
+    <t>2123GM1110</t>
+  </si>
+  <si>
+    <t>2123GMS050</t>
+  </si>
+  <si>
+    <t>2123GMS080</t>
+  </si>
+  <si>
+    <t>2123L50005</t>
+  </si>
+  <si>
+    <t>2123OF0010</t>
+  </si>
+  <si>
+    <t>2123TPSZ93</t>
+  </si>
+  <si>
+    <t>2123TQJZ94</t>
+  </si>
+  <si>
+    <t>2123GIT134</t>
+  </si>
+  <si>
+    <t>2123YIT004</t>
+  </si>
+  <si>
+    <t>2123YIT005</t>
+  </si>
+  <si>
+    <t>DE10YIT016</t>
+  </si>
+  <si>
+    <t>2123YIT008</t>
+  </si>
+  <si>
+    <t>2123YIT009</t>
+  </si>
+  <si>
+    <t>G000001378</t>
+  </si>
+  <si>
+    <t>G000001446</t>
+  </si>
+  <si>
+    <t>G000001449</t>
+  </si>
+  <si>
+    <t>G000001447</t>
+  </si>
+  <si>
+    <t>G000001445</t>
+  </si>
+  <si>
+    <t>G000001448</t>
   </si>
 </sst>
 </file>
@@ -484,7 +493,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="12" bestFit="1" customWidth="1"/>
@@ -504,7 +513,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -512,7 +521,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -520,7 +529,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -528,7 +537,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -536,7 +545,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -544,7 +553,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -552,12 +561,12 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>24</v>
@@ -565,71 +574,71 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
         <v>25</v>
@@ -637,33 +646,41 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>23</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B23" t="s">
         <v>26</v>
       </c>
     </row>
@@ -694,15 +711,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
@@ -711,6 +719,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -891,20 +908,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
     <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,18 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E767145A-48B4-40DC-8F31-E7DF93D822A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63975777-44B3-4DB0-A435-D14ADE7D8E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25755" yWindow="6165" windowWidth="12060" windowHeight="13170" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
-    <sheet name="Pierre to do" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MDGF!$A$1:$B$1</definedName>
     <definedName name="ID" localSheetId="0" hidden="1">"a5f5822f-2145-4cc3-aa32-d164ed237772"</definedName>
-    <definedName name="ID" localSheetId="1" hidden="1">"2b5e4bcf-a0bb-4962-aef7-0fa656cb902f"</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -34,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="34">
   <si>
     <t>Child</t>
   </si>
@@ -42,61 +40,100 @@
     <t>Parent</t>
   </si>
   <si>
-    <t>CH01GFO001</t>
-  </si>
-  <si>
-    <t>CH50GIT040</t>
-  </si>
-  <si>
-    <t>CH50GM2100</t>
-  </si>
-  <si>
-    <t>CH50GM2200</t>
-  </si>
-  <si>
-    <t>CH50GM2201</t>
-  </si>
-  <si>
-    <t>CH50L98043</t>
-  </si>
-  <si>
-    <t>CH65GIT022</t>
-  </si>
-  <si>
-    <t>CH65GM2100</t>
-  </si>
-  <si>
-    <t>CH65GM2201</t>
-  </si>
-  <si>
-    <t>CH65GM4100</t>
-  </si>
-  <si>
-    <t>CH75GIT040</t>
-  </si>
-  <si>
-    <t>CH75GM2100</t>
-  </si>
-  <si>
-    <t>CH75GM2200</t>
-  </si>
-  <si>
-    <t>CH81GM2100</t>
-  </si>
-  <si>
-    <t>CH82GM2100</t>
-  </si>
-  <si>
-    <t>CH82GM2200</t>
-  </si>
-  <si>
-    <t>CH01GFO000</t>
-  </si>
-  <si>
-    <t>CH65GM2200</t>
-  </si>
-  <si>
-    <t>G000000631</t>
+    <t>DE10GIT101</t>
+  </si>
+  <si>
+    <t>DE65GIT032</t>
+  </si>
+  <si>
+    <t>DE10YIT014</t>
+  </si>
+  <si>
+    <t>CN01TPAZ08</t>
+  </si>
+  <si>
+    <t>CN01OF0161</t>
+  </si>
+  <si>
+    <t>CN01TPAZ06</t>
+  </si>
+  <si>
+    <t>CN02TPZZ05</t>
+  </si>
+  <si>
+    <t>CN02TPZZ08</t>
+  </si>
+  <si>
+    <t>CN03TPZZ01</t>
+  </si>
+  <si>
+    <t>CN03TPZZ03</t>
+  </si>
+  <si>
+    <t>CN02TPZZ02</t>
+  </si>
+  <si>
+    <t>CN02TQ1001</t>
+  </si>
+  <si>
+    <t>CN02TQ1002</t>
+  </si>
+  <si>
+    <t>CN02TQ1003</t>
+  </si>
+  <si>
+    <t>CN03TPZZ02</t>
+  </si>
+  <si>
+    <t>CN10DB1001</t>
+  </si>
+  <si>
+    <t>CN10DB1002</t>
+  </si>
+  <si>
+    <t>CN10DB1004</t>
+  </si>
+  <si>
+    <t>CN09DB3303</t>
+  </si>
+  <si>
+    <t>CN09DB3305</t>
+  </si>
+  <si>
+    <t>CN09TQ1001</t>
+  </si>
+  <si>
+    <t>CN09TQ1002</t>
+  </si>
+  <si>
+    <t>CN09TQ1003</t>
+  </si>
+  <si>
+    <t>CN09DB3309</t>
+  </si>
+  <si>
+    <t>CN09DB3300</t>
+  </si>
+  <si>
+    <t>CN09TM3000</t>
+  </si>
+  <si>
+    <t>CN09DB3301</t>
+  </si>
+  <si>
+    <t>CN09DB3307</t>
+  </si>
+  <si>
+    <t>G000001446</t>
+  </si>
+  <si>
+    <t>G000000256</t>
+  </si>
+  <si>
+    <t>G000001444</t>
+  </si>
+  <si>
+    <t>P000000571</t>
   </si>
 </sst>
 </file>
@@ -455,7 +492,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="12" bestFit="1" customWidth="1"/>
@@ -475,7 +512,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -483,135 +520,223 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>19</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B20" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -624,43 +749,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DADB64C-1560-4418-AEF8-AFB915F63B31}">
-  <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <customProperties>
-    <customPr name="_pios_id" r:id="rId1"/>
-  </customProperties>
-</worksheet>
-</file>
-
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -837,26 +926,27 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
-    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -873,4 +963,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
+    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63975777-44B3-4DB0-A435-D14ADE7D8E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D0F02C-E31E-47CF-8C2C-D7DF78BA9144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="10275" windowHeight="12330" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MDGF!$A$1:$B$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MDGF!$A$1:$B$34</definedName>
     <definedName name="ID" localSheetId="0" hidden="1">"a5f5822f-2145-4cc3-aa32-d164ed237772"</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="42">
   <si>
     <t>Child</t>
   </si>
@@ -40,100 +41,124 @@
     <t>Parent</t>
   </si>
   <si>
-    <t>DE10GIT101</t>
-  </si>
-  <si>
-    <t>DE65GIT032</t>
-  </si>
-  <si>
-    <t>DE10YIT014</t>
-  </si>
-  <si>
-    <t>CN01TPAZ08</t>
-  </si>
-  <si>
-    <t>CN01OF0161</t>
-  </si>
-  <si>
-    <t>CN01TPAZ06</t>
-  </si>
-  <si>
-    <t>CN02TPZZ05</t>
-  </si>
-  <si>
-    <t>CN02TPZZ08</t>
-  </si>
-  <si>
-    <t>CN03TPZZ01</t>
-  </si>
-  <si>
-    <t>CN03TPZZ03</t>
-  </si>
-  <si>
-    <t>CN02TPZZ02</t>
-  </si>
-  <si>
-    <t>CN02TQ1001</t>
-  </si>
-  <si>
-    <t>CN02TQ1002</t>
-  </si>
-  <si>
-    <t>CN02TQ1003</t>
-  </si>
-  <si>
-    <t>CN03TPZZ02</t>
-  </si>
-  <si>
-    <t>CN10DB1001</t>
-  </si>
-  <si>
-    <t>CN10DB1002</t>
-  </si>
-  <si>
-    <t>CN10DB1004</t>
-  </si>
-  <si>
-    <t>CN09DB3303</t>
-  </si>
-  <si>
-    <t>CN09DB3305</t>
-  </si>
-  <si>
-    <t>CN09TQ1001</t>
-  </si>
-  <si>
-    <t>CN09TQ1002</t>
-  </si>
-  <si>
-    <t>CN09TQ1003</t>
-  </si>
-  <si>
-    <t>CN09DB3309</t>
-  </si>
-  <si>
-    <t>CN09DB3300</t>
-  </si>
-  <si>
-    <t>CN09TM3000</t>
-  </si>
-  <si>
-    <t>CN09DB3301</t>
-  </si>
-  <si>
-    <t>CN09DB3307</t>
-  </si>
-  <si>
-    <t>G000001446</t>
-  </si>
-  <si>
-    <t>G000000256</t>
-  </si>
-  <si>
-    <t>G000001444</t>
-  </si>
-  <si>
-    <t>P000000571</t>
+    <t>DE07Z02182</t>
+  </si>
+  <si>
+    <t>HK01Z02181</t>
+  </si>
+  <si>
+    <t>HK01Z02182</t>
+  </si>
+  <si>
+    <t>HK01Z02183</t>
+  </si>
+  <si>
+    <t>HK01Z02184</t>
+  </si>
+  <si>
+    <t>HK01Z02185</t>
+  </si>
+  <si>
+    <t>IN01Z02181</t>
+  </si>
+  <si>
+    <t>IN01Z02182</t>
+  </si>
+  <si>
+    <t>IN01Z02183</t>
+  </si>
+  <si>
+    <t>IN01Z02184</t>
+  </si>
+  <si>
+    <t>JP01Z02181</t>
+  </si>
+  <si>
+    <t>JP01Z02184</t>
+  </si>
+  <si>
+    <t>JP01Z02185</t>
+  </si>
+  <si>
+    <t>JP02Z02181</t>
+  </si>
+  <si>
+    <t>JP02Z02182</t>
+  </si>
+  <si>
+    <t>JP02Z02183</t>
+  </si>
+  <si>
+    <t>JP02Z02184</t>
+  </si>
+  <si>
+    <t>JP02Z02185</t>
+  </si>
+  <si>
+    <t>KR02Z02181</t>
+  </si>
+  <si>
+    <t>KR02Z02182</t>
+  </si>
+  <si>
+    <t>KR02Z02183</t>
+  </si>
+  <si>
+    <t>KR02Z02184</t>
+  </si>
+  <si>
+    <t>SG09Z02181</t>
+  </si>
+  <si>
+    <t>SG09Z02182</t>
+  </si>
+  <si>
+    <t>SG09Z02183</t>
+  </si>
+  <si>
+    <t>SG09Z02184</t>
+  </si>
+  <si>
+    <t>TW02Z02183</t>
+  </si>
+  <si>
+    <t>TW02Z02184</t>
+  </si>
+  <si>
+    <t>TW03Z02184</t>
+  </si>
+  <si>
+    <t>KR03Z02181</t>
+  </si>
+  <si>
+    <t>KR03Z02182</t>
+  </si>
+  <si>
+    <t>KR03Z02183</t>
+  </si>
+  <si>
+    <t>KR03Z02184</t>
+  </si>
+  <si>
+    <t>CN01OF0083</t>
+  </si>
+  <si>
+    <t>US01OF0103</t>
+  </si>
+  <si>
+    <t>KR03L80000</t>
+  </si>
+  <si>
+    <t>TW10OF6016</t>
+  </si>
+  <si>
+    <t>US10OF6070</t>
+  </si>
+  <si>
+    <t>P000001335</t>
+  </si>
+  <si>
+    <t>P000001336</t>
   </si>
 </sst>
 </file>
@@ -492,7 +517,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="12" bestFit="1" customWidth="1"/>
@@ -512,7 +537,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -520,223 +545,255 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -749,7 +806,69 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A7505E0-223A-4D54-9F54-03644F32A7EE}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -926,15 +1045,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -947,6 +1057,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -965,14 +1083,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>

--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -1,29 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre\Downloads\GCOH\GCOHFilesTicketsEtc\GCOH Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M346157\Documents\GCOH-Tickets-for-Processing\GCOH-Tickets-for-Processing\GCOH-Tickets-for-Processing\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D0F02C-E31E-47CF-8C2C-D7DF78BA9144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F5BA8A7-922F-4C7F-9930-6F06ECFFA596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="10275" windowHeight="12330" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MDGF!$A$1:$B$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MDGF!$A$1:$B$1</definedName>
     <definedName name="ID" localSheetId="0" hidden="1">"a5f5822f-2145-4cc3-aa32-d164ed237772"</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -33,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="42">
   <si>
     <t>Child</t>
   </si>
@@ -220,9 +231,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -260,7 +271,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -366,7 +377,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -508,7 +519,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -517,14 +528,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E39"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -532,7 +543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -540,7 +551,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -548,7 +559,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -556,7 +567,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -564,7 +575,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -572,7 +583,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -580,7 +591,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -588,7 +599,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -596,7 +607,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -604,7 +615,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -612,7 +623,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -620,7 +631,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -628,7 +639,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -636,7 +647,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -644,7 +655,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -652,7 +663,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -660,7 +671,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -668,7 +679,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -676,7 +687,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -684,7 +695,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -692,7 +703,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -700,7 +711,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -708,7 +719,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -716,7 +727,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -724,7 +735,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -732,7 +743,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -740,7 +751,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>28</v>
       </c>
@@ -748,51 +759,87 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>29</v>
       </c>
       <c r="B29" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D29" t="s">
+        <v>31</v>
+      </c>
+      <c r="E29" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>30</v>
       </c>
       <c r="B30" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="D30" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D31" t="s">
+        <v>33</v>
+      </c>
+      <c r="E31" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D32" t="s">
+        <v>34</v>
+      </c>
+      <c r="E32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D33" t="s">
+        <v>37</v>
+      </c>
+      <c r="E33" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>35</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B35" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>36</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B36" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>38</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B38" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>39</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B39" t="s">
         <v>41</v>
       </c>
     </row>
@@ -809,12 +856,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A7505E0-223A-4D54-9F54-03644F32A7EE}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>31</v>
       </c>
@@ -822,7 +869,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -830,7 +877,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -838,7 +885,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>34</v>
       </c>
@@ -846,7 +893,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -860,15 +907,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -1045,6 +1083,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1057,14 +1104,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1083,6 +1122,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>

--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M346157\Documents\GCOH-Tickets-for-Processing\GCOH-Tickets-for-Processing\GCOH-Tickets-for-Processing\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F5BA8A7-922F-4C7F-9930-6F06ECFFA596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D3D954-5BAB-4ECB-AB45-76DB26FE3BD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
   <si>
     <t>Child</t>
   </si>
@@ -52,93 +52,6 @@
     <t>Parent</t>
   </si>
   <si>
-    <t>DE07Z02182</t>
-  </si>
-  <si>
-    <t>HK01Z02181</t>
-  </si>
-  <si>
-    <t>HK01Z02182</t>
-  </si>
-  <si>
-    <t>HK01Z02183</t>
-  </si>
-  <si>
-    <t>HK01Z02184</t>
-  </si>
-  <si>
-    <t>HK01Z02185</t>
-  </si>
-  <si>
-    <t>IN01Z02181</t>
-  </si>
-  <si>
-    <t>IN01Z02182</t>
-  </si>
-  <si>
-    <t>IN01Z02183</t>
-  </si>
-  <si>
-    <t>IN01Z02184</t>
-  </si>
-  <si>
-    <t>JP01Z02181</t>
-  </si>
-  <si>
-    <t>JP01Z02184</t>
-  </si>
-  <si>
-    <t>JP01Z02185</t>
-  </si>
-  <si>
-    <t>JP02Z02181</t>
-  </si>
-  <si>
-    <t>JP02Z02182</t>
-  </si>
-  <si>
-    <t>JP02Z02183</t>
-  </si>
-  <si>
-    <t>JP02Z02184</t>
-  </si>
-  <si>
-    <t>JP02Z02185</t>
-  </si>
-  <si>
-    <t>KR02Z02181</t>
-  </si>
-  <si>
-    <t>KR02Z02182</t>
-  </si>
-  <si>
-    <t>KR02Z02183</t>
-  </si>
-  <si>
-    <t>KR02Z02184</t>
-  </si>
-  <si>
-    <t>SG09Z02181</t>
-  </si>
-  <si>
-    <t>SG09Z02182</t>
-  </si>
-  <si>
-    <t>SG09Z02183</t>
-  </si>
-  <si>
-    <t>SG09Z02184</t>
-  </si>
-  <si>
-    <t>TW02Z02183</t>
-  </si>
-  <si>
-    <t>TW02Z02184</t>
-  </si>
-  <si>
-    <t>TW03Z02184</t>
-  </si>
-  <si>
     <t>KR03Z02181</t>
   </si>
   <si>
@@ -151,25 +64,25 @@
     <t>KR03Z02184</t>
   </si>
   <si>
-    <t>CN01OF0083</t>
-  </si>
-  <si>
-    <t>US01OF0103</t>
-  </si>
-  <si>
     <t>KR03L80000</t>
   </si>
   <si>
-    <t>TW10OF6016</t>
-  </si>
-  <si>
-    <t>US10OF6070</t>
-  </si>
-  <si>
     <t>P000001335</t>
   </si>
   <si>
     <t>P000001336</t>
+  </si>
+  <si>
+    <t>ES50Y54321</t>
+  </si>
+  <si>
+    <t>IT50Y54321</t>
+  </si>
+  <si>
+    <t>2123Y54321</t>
+  </si>
+  <si>
+    <t>G000001450</t>
   </si>
 </sst>
 </file>
@@ -528,7 +441,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="12" bestFit="1" customWidth="1"/>
@@ -545,302 +458,26 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
         <v>12</v>
-      </c>
-      <c r="B12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" t="s">
-        <v>40</v>
-      </c>
-      <c r="D29" t="s">
-        <v>31</v>
-      </c>
-      <c r="E29" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" t="s">
-        <v>40</v>
-      </c>
-      <c r="D30" t="s">
-        <v>32</v>
-      </c>
-      <c r="E30" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D31" t="s">
-        <v>33</v>
-      </c>
-      <c r="E31" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D32" t="s">
-        <v>34</v>
-      </c>
-      <c r="E32" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D33" t="s">
-        <v>37</v>
-      </c>
-      <c r="E33" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>36</v>
-      </c>
-      <c r="B36" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -863,42 +500,42 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -907,6 +544,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -1083,15 +729,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1104,6 +741,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1122,14 +767,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>

--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M346157\Documents\GCOH-Tickets-for-Processing\GCOH-Tickets-for-Processing\GCOH-Tickets-for-Processing\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D3D954-5BAB-4ECB-AB45-76DB26FE3BD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD3F8253-8658-47CF-898A-3C84ABFDC350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MDGF!$A$1:$B$1</definedName>
     <definedName name="ID" localSheetId="0" hidden="1">"a5f5822f-2145-4cc3-aa32-d164ed237772"</definedName>
+    <definedName name="ID" localSheetId="1" hidden="1">"c430d0f8-521d-4d46-9b72-5e46847abf00"</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="46">
   <si>
     <t>Child</t>
   </si>
@@ -73,16 +74,115 @@
     <t>P000001336</t>
   </si>
   <si>
-    <t>ES50Y54321</t>
-  </si>
-  <si>
-    <t>IT50Y54321</t>
-  </si>
-  <si>
-    <t>2123Y54321</t>
-  </si>
-  <si>
-    <t>G000001450</t>
+    <t>DE10F27300</t>
+  </si>
+  <si>
+    <t>DE10566115</t>
+  </si>
+  <si>
+    <t>DE10566116</t>
+  </si>
+  <si>
+    <t>DE10566118</t>
+  </si>
+  <si>
+    <t>DE10566120</t>
+  </si>
+  <si>
+    <t>DE10566121</t>
+  </si>
+  <si>
+    <t>DE10566122</t>
+  </si>
+  <si>
+    <t>DE10566125</t>
+  </si>
+  <si>
+    <t>DE10566127</t>
+  </si>
+  <si>
+    <t>DE10E16300</t>
+  </si>
+  <si>
+    <t>DE10E16600</t>
+  </si>
+  <si>
+    <t>DE10E38020</t>
+  </si>
+  <si>
+    <t>DE10E38800</t>
+  </si>
+  <si>
+    <t>DE10E38810</t>
+  </si>
+  <si>
+    <t>DE10E61000</t>
+  </si>
+  <si>
+    <t>DE10E61100</t>
+  </si>
+  <si>
+    <t>DE10E61200</t>
+  </si>
+  <si>
+    <t>DE10E61900</t>
+  </si>
+  <si>
+    <t>DE10F11900</t>
+  </si>
+  <si>
+    <t>DE10F16000</t>
+  </si>
+  <si>
+    <t>DE10F16010</t>
+  </si>
+  <si>
+    <t>DE10F16100</t>
+  </si>
+  <si>
+    <t>DE10F16200</t>
+  </si>
+  <si>
+    <t>DE10F16300</t>
+  </si>
+  <si>
+    <t>DE10F16500</t>
+  </si>
+  <si>
+    <t>DE10F16600</t>
+  </si>
+  <si>
+    <t>DE10F16700</t>
+  </si>
+  <si>
+    <t>DE10F27301</t>
+  </si>
+  <si>
+    <t>DE10E09200</t>
+  </si>
+  <si>
+    <t>DE10E47200</t>
+  </si>
+  <si>
+    <t>DE10F10600</t>
+  </si>
+  <si>
+    <t>DE10F10900</t>
+  </si>
+  <si>
+    <t>DE10F15400</t>
+  </si>
+  <si>
+    <t>DE10F15410</t>
+  </si>
+  <si>
+    <t>G000000847</t>
+  </si>
+  <si>
+    <t>G000000431</t>
+  </si>
+  <si>
+    <t>G000000848</t>
   </si>
 </sst>
 </file>
@@ -441,7 +541,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="12" bestFit="1" customWidth="1"/>
@@ -461,7 +561,7 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -469,7 +569,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -477,7 +577,255 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -553,6 +901,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -729,17 +1088,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
   <ds:schemaRefs>
@@ -749,6 +1097,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
+    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -765,15 +1124,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e6028c0-cacb-4ef6-8532-444dfe1b79a8"/>
-    <ds:schemaRef ds:uri="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M346157\Documents\GCOH-Tickets-for-Processing\GCOH-Tickets-for-Processing\GCOH-Tickets-for-Processing\GCOH Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M346157\Documents\GCOH-Tickets-for-Processing\GCOH-Tickets-for-Processing\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD3F8253-8658-47CF-898A-3C84ABFDC350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{88262AE3-B111-4F7E-8228-E5FA59415467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
   <si>
     <t>Child</t>
   </si>
@@ -74,115 +74,31 @@
     <t>P000001336</t>
   </si>
   <si>
-    <t>DE10F27300</t>
-  </si>
-  <si>
-    <t>DE10566115</t>
-  </si>
-  <si>
-    <t>DE10566116</t>
-  </si>
-  <si>
-    <t>DE10566118</t>
-  </si>
-  <si>
-    <t>DE10566120</t>
-  </si>
-  <si>
-    <t>DE10566121</t>
-  </si>
-  <si>
-    <t>DE10566122</t>
-  </si>
-  <si>
-    <t>DE10566125</t>
-  </si>
-  <si>
-    <t>DE10566127</t>
-  </si>
-  <si>
-    <t>DE10E16300</t>
-  </si>
-  <si>
-    <t>DE10E16600</t>
-  </si>
-  <si>
-    <t>DE10E38020</t>
-  </si>
-  <si>
-    <t>DE10E38800</t>
-  </si>
-  <si>
-    <t>DE10E38810</t>
-  </si>
-  <si>
-    <t>DE10E61000</t>
-  </si>
-  <si>
-    <t>DE10E61100</t>
-  </si>
-  <si>
-    <t>DE10E61200</t>
-  </si>
-  <si>
-    <t>DE10E61900</t>
-  </si>
-  <si>
-    <t>DE10F11900</t>
-  </si>
-  <si>
-    <t>DE10F16000</t>
-  </si>
-  <si>
-    <t>DE10F16010</t>
-  </si>
-  <si>
-    <t>DE10F16100</t>
-  </si>
-  <si>
-    <t>DE10F16200</t>
-  </si>
-  <si>
-    <t>DE10F16300</t>
-  </si>
-  <si>
-    <t>DE10F16500</t>
-  </si>
-  <si>
-    <t>DE10F16600</t>
-  </si>
-  <si>
-    <t>DE10F16700</t>
-  </si>
-  <si>
-    <t>DE10F27301</t>
-  </si>
-  <si>
-    <t>DE10E09200</t>
-  </si>
-  <si>
-    <t>DE10E47200</t>
-  </si>
-  <si>
-    <t>DE10F10600</t>
-  </si>
-  <si>
-    <t>DE10F10900</t>
-  </si>
-  <si>
-    <t>DE10F15400</t>
-  </si>
-  <si>
-    <t>DE10F15410</t>
-  </si>
-  <si>
-    <t>G000000847</t>
-  </si>
-  <si>
-    <t>G000000431</t>
-  </si>
-  <si>
-    <t>G000000848</t>
+    <t>DE10B08450</t>
+  </si>
+  <si>
+    <t>DE10A48610</t>
+  </si>
+  <si>
+    <t>DE10A48607</t>
+  </si>
+  <si>
+    <t>DE10538392</t>
+  </si>
+  <si>
+    <t>DE20700060</t>
+  </si>
+  <si>
+    <t>L000013429</t>
+  </si>
+  <si>
+    <t>G000000877</t>
+  </si>
+  <si>
+    <t>G000001084</t>
+  </si>
+  <si>
+    <t>G000000544</t>
   </si>
 </sst>
 </file>
@@ -541,11 +457,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -561,7 +477,7 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -569,7 +485,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -577,7 +493,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -585,7 +501,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -593,239 +509,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
         <v>17</v>
-      </c>
-      <c r="B10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" t="s">
-        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -892,15 +576,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" xsi:nil="true"/>
@@ -911,7 +586,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -1088,15 +763,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -1107,7 +783,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1124,4 +800,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M346157\Documents\GCOH-Tickets-for-Processing\GCOH-Tickets-for-Processing\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{88262AE3-B111-4F7E-8228-E5FA59415467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3278E4C-3902-4739-BC98-B9CC726C44A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="17052" yWindow="1152" windowWidth="6684" windowHeight="11784" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -572,6 +572,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <customProperties>
+    <customPr name="_pios_id" r:id="rId1"/>
+  </customProperties>
 </worksheet>
 </file>
 

--- a/GCOH Resources/GCOHPost.xlsx
+++ b/GCOH Resources/GCOHPost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M346157\Documents\GCOH-Tickets-for-Processing\GCOH-Tickets-for-Processing\GCOH Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3278E4C-3902-4739-BC98-B9CC726C44A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{456011BF-08CD-40ED-97BF-1E526176B89A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17052" yWindow="1152" windowWidth="6684" windowHeight="11784" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9D4B8E05-E149-4A97-BE17-9860CFEAED05}"/>
   </bookViews>
   <sheets>
     <sheet name="MDGF" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
   <si>
     <t>Child</t>
   </si>
@@ -74,31 +74,25 @@
     <t>P000001336</t>
   </si>
   <si>
-    <t>DE10B08450</t>
-  </si>
-  <si>
-    <t>DE10A48610</t>
-  </si>
-  <si>
-    <t>DE10A48607</t>
-  </si>
-  <si>
-    <t>DE10538392</t>
-  </si>
-  <si>
-    <t>DE20700060</t>
-  </si>
-  <si>
-    <t>L000013429</t>
-  </si>
-  <si>
-    <t>G000000877</t>
-  </si>
-  <si>
-    <t>G000001084</t>
-  </si>
-  <si>
-    <t>G000000544</t>
+    <t>G000001457</t>
+  </si>
+  <si>
+    <t>CN90GM4004</t>
+  </si>
+  <si>
+    <t>G000001459</t>
+  </si>
+  <si>
+    <t>DE10GMS041</t>
+  </si>
+  <si>
+    <t>G000001460</t>
+  </si>
+  <si>
+    <t>DE10GMS070</t>
+  </si>
+  <si>
+    <t>DE10669632</t>
   </si>
 </sst>
 </file>
@@ -457,11 +451,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C8BCB-C2B7-4B24-AC50-E6BDF8320BBE}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.88671875" customWidth="1"/>
+    <col min="5" max="5" width="21.44140625" customWidth="1"/>
+    <col min="6" max="6" width="22.5546875" customWidth="1"/>
+    <col min="7" max="7" width="10.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -474,42 +472,34 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
         <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -590,6 +580,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007ED8CFF7E4A8C54DB0FB6A701E4396A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0054764cec7dc7c93b4af6049901bbd5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01" xmlns:ns3="6e6028c0-cacb-4ef6-8532-444dfe1b79a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df68a8a9c021719e783243c7bc54c348" ns2:_="" ns3:_="">
     <xsd:import namespace="e8dd6ffc-3db2-45ec-9c01-73bc56a45b01"/>
@@ -766,15 +765,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85123729-9994-4A95-BAA7-D1009B81DC0A}">
   <ds:schemaRefs>
@@ -787,6 +777,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEDEB69F-AD4A-4DDF-9F03-7CB95A56DF88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -803,12 +801,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D3C4D-1EB0-4D9D-8D89-5C2B1DF0074E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>